--- a/outputs/validation_frame_fab_error.xlsx
+++ b/outputs/validation_frame_fab_error.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000497800553184697</v>
+        <v>-0.0004978005531852484</v>
       </c>
       <c r="F6" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.521497120175572e-16</v>
+        <v>-1.662109234779601e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004978005910997909</v>
+        <v>0.0004978005911003423</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="F7" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004978005910979412</v>
+        <v>0.0004978005910984314</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004978005910979412</v>
+        <v>0.0004978005910984314</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000497800591099791</v>
+        <v>0.0004978005911003422</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="F10" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.513191775452895e-16</v>
+        <v>-1.837675371856052e-16</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01085745034258018</v>
+        <v>0.0108574503425808</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="F11" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01085745034257829</v>
+        <v>0.01085745034257883</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004231960616782613</v>
+        <v>0.004231960616784009</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004231960616787453</v>
+        <v>0.004231960616789025</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="F14" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.957666828069171e-17</v>
+        <v>-1.579633952279717e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01496611148061224</v>
+        <v>0.01496611148061477</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="F15" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="G15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01496611148060666</v>
+        <v>0.01496611148060856</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01113611796550427</v>
+        <v>0.01113611796550682</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01113611796551176</v>
+        <v>0.01113611796551515</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191545</v>
       </c>
       <c r="F18" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.180501003454598e-17</v>
+        <v>-8.702157183110913e-17</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02106255232993836</v>
+        <v>0.02106255232994397</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190386</v>
       </c>
       <c r="F19" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.187830652248113e-17</v>
+        <v>-8.72061823187002e-17</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="K19" t="n">
-        <v>0.021062552329931</v>
+        <v>0.02106255232993375</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01853807592919061</v>
+        <v>0.01853807592919373</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>4.277158646686195e-17</v>
+        <v>8.998391004434036e-17</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01853807592919897</v>
+        <v>0.01853807592920534</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02106255232993836</v>
+        <v>0.02106255232994397</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191545</v>
       </c>
       <c r="E2" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="E5" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.311312169960388e-13</v>
+        <v>-6.929504713093504e-14</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.056826096416637e-13</v>
+        <v>-1.113145175800432e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03069770078073537</v>
+        <v>-0.0306977007800977</v>
       </c>
       <c r="E2" t="n">
-        <v>4.296386158179834e-13</v>
+        <v>4.569396361138198e-13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1227908031186297</v>
+        <v>0.1227908031188893</v>
       </c>
       <c r="G2" t="n">
-        <v>6.448418222140104e-16</v>
+        <v>6.793077920818111e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-3.441136264825673e-13</v>
+        <v>-2.90072761817417e-13</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.056301890213897e-13</v>
+        <v>-1.113132344405785e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03069770078123084</v>
+        <v>-0.03069770078136342</v>
       </c>
       <c r="E3" t="n">
-        <v>4.295338792934306e-13</v>
+        <v>4.569368345576162e-13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1227908031177474</v>
+        <v>0.1227908031179764</v>
       </c>
       <c r="G3" t="n">
-        <v>6.44768254624497e-16</v>
+        <v>6.792862188998355e-16</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-3.440719931191438e-13</v>
+        <v>-2.900326463370351e-13</v>
       </c>
       <c r="C4" t="n">
-        <v>1.060312698528079e-13</v>
+        <v>1.118832211966489e-13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03069770078125075</v>
+        <v>0.03069770078081126</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.31381983041816e-13</v>
+        <v>-4.598491472941029e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1227908031177475</v>
+        <v>0.1227908031179765</v>
       </c>
       <c r="G4" t="n">
-        <v>6.447799049403346e-16</v>
+        <v>6.792836862529862e-16</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.312283615106935e-13</v>
+        <v>-6.938297592712361e-14</v>
       </c>
       <c r="C5" t="n">
-        <v>1.06028662285421e-13</v>
+        <v>1.118830786238024e-13</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03069770078120492</v>
+        <v>0.03069770078063009</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.313767609041526e-13</v>
+        <v>-4.598489149359651e-13</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1227908031186295</v>
+        <v>0.1227908031188891</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4461311945537e-16</v>
+        <v>6.793499579772974e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.23815409079487e-08</v>
+        <v>3.238154090727605e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03069770078073537</v>
+        <v>0.03069770078009769</v>
       </c>
       <c r="I2" t="n">
-        <v>6.476308181589739</v>
+        <v>6.476308181455209</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03069770078073537</v>
+        <v>-0.0306977007800977</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.056826096416637e-13</v>
+        <v>-1.113145175800432e-13</v>
       </c>
       <c r="L2" t="n">
-        <v>1.311312169960388e-13</v>
+        <v>6.929179452441758e-14</v>
       </c>
       <c r="M2" t="n">
-        <v>6.448418222140104e-16</v>
+        <v>6.793077920818111e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1227908031186297</v>
+        <v>0.1227908031188893</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.296386158179834e-13</v>
+        <v>-4.569396361138199e-13</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03069770078073537</v>
+        <v>0.0306977007800977</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.056826096416637e-13</v>
+        <v>1.113145175800432e-13</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.311312169960388e-13</v>
+        <v>-6.929179452441758e-14</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.448418222140104e-16</v>
+        <v>-6.793077920818111e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1227908031194165</v>
+        <v>-0.1227908031193052</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.044570420319988e-13</v>
+        <v>-2.10947469366439e-13</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>3.238154090847134e-08</v>
+        <v>3.238154090861119e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03069770078123083</v>
+        <v>0.03069770078136341</v>
       </c>
       <c r="I3" t="n">
-        <v>6.476308181694269</v>
+        <v>6.476308181722239</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03069770078123084</v>
+        <v>-0.03069770078136342</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.056301890213897e-13</v>
+        <v>-1.113132344405785e-13</v>
       </c>
       <c r="L3" t="n">
-        <v>3.441136264825673e-13</v>
+        <v>2.900735207589378e-13</v>
       </c>
       <c r="M3" t="n">
-        <v>6.44768254624497e-16</v>
+        <v>6.792862188998355e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1227908031177474</v>
+        <v>0.1227908031179764</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.295338792934306e-13</v>
+        <v>-4.569368345576162e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03069770078123084</v>
+        <v>0.03069770078136342</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.056301890213897e-13</v>
+        <v>1.113132344405785e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.441136264825673e-13</v>
+        <v>-2.900735207589378e-13</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.44768254624497e-16</v>
+        <v>-6.792862188998355e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1227908031198122</v>
+        <v>-0.1227908031197169</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.042472548349078e-13</v>
+        <v>-2.109425720858546e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.238154090849235e-08</v>
+        <v>-3.238154090802875e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03069770078125074</v>
+        <v>-0.03069770078081126</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.476308181698468</v>
+        <v>-6.47630818160575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03069770078125075</v>
+        <v>0.03069770078081126</v>
       </c>
       <c r="K4" t="n">
-        <v>1.060312698528079e-13</v>
+        <v>1.118832211966489e-13</v>
       </c>
       <c r="L4" t="n">
-        <v>3.440719931191438e-13</v>
+        <v>2.900318873955143e-13</v>
       </c>
       <c r="M4" t="n">
-        <v>6.447799049403346e-16</v>
+        <v>6.792836862529862e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1227908031177475</v>
+        <v>0.1227908031179765</v>
       </c>
       <c r="O4" t="n">
-        <v>4.31381983041816e-13</v>
+        <v>4.598491472941029e-13</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.03069770078125075</v>
+        <v>-0.03069770078081126</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.060312698528079e-13</v>
+        <v>-1.118832211966489e-13</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.440719931191438e-13</v>
+        <v>-2.900318873955143e-13</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.447799049403346e-16</v>
+        <v>-6.792836862529862e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.122790803119812</v>
+        <v>-0.1227908031197167</v>
       </c>
       <c r="U4" t="n">
-        <v>2.048056360750312e-13</v>
+        <v>2.114501798857903e-13</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2381540908444e-08</v>
+        <v>-3.238154090783764e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03069770078120491</v>
+        <v>-0.03069770078063009</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.4763081816888</v>
+        <v>-6.476308181567529</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03069770078120492</v>
+        <v>0.03069770078063009</v>
       </c>
       <c r="K5" t="n">
-        <v>1.06028662285421e-13</v>
+        <v>1.118830786238024e-13</v>
       </c>
       <c r="L5" t="n">
-        <v>1.312283615106935e-13</v>
+        <v>6.938893903907228e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>6.4461311945537e-16</v>
+        <v>6.793499579772974e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1227908031186295</v>
+        <v>0.1227908031188891</v>
       </c>
       <c r="O5" t="n">
-        <v>4.313767609041526e-13</v>
+        <v>4.598489149359651e-13</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03069770078120492</v>
+        <v>-0.03069770078063009</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.06028662285421e-13</v>
+        <v>-1.118830786238024e-13</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.312283615106935e-13</v>
+        <v>-6.938893903907228e-14</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.4461311945537e-16</v>
+        <v>-6.793499579772974e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1227908031194169</v>
+        <v>-0.1227908031193055</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04795212808373e-13</v>
+        <v>2.11449556806849e-13</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009998931153223171</v>
+        <v>-0.009998931153223175</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001666488525537195</v>
+        <v>-0.001666488525537196</v>
       </c>
       <c r="H6" t="n">
-        <v>-1579.831122209261</v>
+        <v>-1579.831122209262</v>
       </c>
       <c r="I6" t="n">
-        <v>-333297.705107439</v>
+        <v>-333297.7051074391</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1688777907386338</v>
+        <v>-0.1688777907381791</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.016589946586002e-13</v>
+        <v>-1.111710482853654e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>1.297850715786808e-13</v>
+        <v>7.138734048339757e-14</v>
       </c>
       <c r="M6" t="n">
-        <v>1.003947125286698e-15</v>
+        <v>1.088707853982457e-15</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6755111629518569</v>
+        <v>0.6755111629520767</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.043623884663222e-13</v>
+        <v>-3.465050389997536e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1688777907386338</v>
+        <v>0.1688777907381791</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.016589946586002e-13</v>
+        <v>1.111710482853654e-13</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.297850715786808e-13</v>
+        <v>-7.138734048339757e-14</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.003947125286698e-15</v>
+        <v>-1.088707853982457e-15</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6755111629526356</v>
+        <v>-0.6755111629525059</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.055915794852785e-13</v>
+        <v>-3.205212507124386e-13</v>
       </c>
     </row>
     <row r="7">
@@ -1953,40 +1953,40 @@
         <v>-333297.7051074389</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1688777907390886</v>
+        <v>-0.1688777907395433</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.016964272859168e-13</v>
+        <v>-1.109572406080648e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.533839887381873e-13</v>
+        <v>2.959854583650667e-13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.003662332591825e-15</v>
+        <v>1.089089653757695e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6755111629511585</v>
+        <v>0.6755111629513628</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.043323765989816e-13</v>
+        <v>-3.46075886313227e-13</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1688777907390886</v>
+        <v>0.1688777907395433</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.016964272859168e-13</v>
+        <v>1.109572406080648e-13</v>
       </c>
       <c r="R7" t="n">
-        <v>-3.533839887381873e-13</v>
+        <v>-2.959854583650667e-13</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.003662332591825e-15</v>
+        <v>-1.089089653757695e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6755111629532795</v>
+        <v>-0.6755111629531396</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.058461871165189e-13</v>
+        <v>-3.196675573351616e-13</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.068846776830474e-06</v>
+        <v>-1.068846776828246e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.781411294717457e-07</v>
+        <v>-1.781411294713743e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.168877790739215</v>
+        <v>-0.1688777907388628</v>
       </c>
       <c r="I8" t="n">
-        <v>-35.62822589434915</v>
+        <v>-35.62822589427485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.168877790739215</v>
+        <v>0.1688777907388629</v>
       </c>
       <c r="K8" t="n">
-        <v>1.020563685019457e-13</v>
+        <v>1.116118975923458e-13</v>
       </c>
       <c r="L8" t="n">
-        <v>3.534950110406498e-13</v>
+        <v>2.955413691552167e-13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.004399389143434e-15</v>
+        <v>1.088220089750561e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6755111629511581</v>
+        <v>0.6755111629513639</v>
       </c>
       <c r="O8" t="n">
-        <v>3.057675499107009e-13</v>
+        <v>3.486380836536046e-13</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.168877790739215</v>
+        <v>-0.1688777907388629</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.020563685019457e-13</v>
+        <v>-1.116118975923458e-13</v>
       </c>
       <c r="R8" t="n">
-        <v>-3.534950110406498e-13</v>
+        <v>-2.955413691552167e-13</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.004399389143434e-15</v>
+        <v>-1.088220089750561e-15</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6755111629532804</v>
+        <v>-0.6755111629531383</v>
       </c>
       <c r="U8" t="n">
-        <v>3.065706611009732e-13</v>
+        <v>3.210333019004703e-13</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.068846776830301e-06</v>
+        <v>-1.068846776827107e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.781411294717168e-07</v>
+        <v>-1.781411294711845e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1688777907391875</v>
+        <v>-0.1688777907386829</v>
       </c>
       <c r="I9" t="n">
-        <v>-35.62822589434336</v>
+        <v>-35.62822589423689</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1688777907391875</v>
+        <v>0.1688777907386829</v>
       </c>
       <c r="K9" t="n">
-        <v>1.020658017410055e-13</v>
+        <v>1.116125327618011e-13</v>
       </c>
       <c r="L9" t="n">
-        <v>1.294520046712933e-13</v>
+        <v>7.149836278586008e-14</v>
       </c>
       <c r="M9" t="n">
-        <v>1.00316870126798e-15</v>
+        <v>1.088622777137711e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6755111629518573</v>
+        <v>0.6755111629520767</v>
       </c>
       <c r="O9" t="n">
-        <v>3.057815917171203e-13</v>
+        <v>3.486385285113655e-13</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1688777907391875</v>
+        <v>-0.1688777907386829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.020658017410055e-13</v>
+        <v>-1.116125327618011e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.294520046712933e-13</v>
+        <v>-7.149836278586008e-14</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.00316870126798e-15</v>
+        <v>-1.088622777137711e-15</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6755111629526342</v>
+        <v>-0.6755111629525063</v>
       </c>
       <c r="U9" t="n">
-        <v>3.06613218728913e-13</v>
+        <v>3.21036668059441e-13</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.683885617314446e-07</v>
+        <v>1.683885617262404e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.806476028857409e-08</v>
+        <v>2.806476028770673e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02660539275356824</v>
+        <v>0.02660539275274598</v>
       </c>
       <c r="I10" t="n">
-        <v>5.612952057714819</v>
+        <v>5.612952057541346</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02660539275348128</v>
+        <v>-0.02660539275257179</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.004421522552583e-14</v>
+        <v>-1.062459638123764e-13</v>
       </c>
       <c r="L10" t="n">
-        <v>1.729727472365994e-13</v>
+        <v>7.593925488436071e-14</v>
       </c>
       <c r="M10" t="n">
-        <v>8.564708730707019e-16</v>
+        <v>1.111852555817223e-15</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1064215710118925</v>
+        <v>0.1064215710122962</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.018431888207753e-13</v>
+        <v>-2.996428263884806e-13</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02660539275348128</v>
+        <v>0.02660539275257179</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.004421522552583e-14</v>
+        <v>1.062459638123764e-13</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.729727472365994e-13</v>
+        <v>-7.593925488436071e-14</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.564708730707019e-16</v>
+        <v>-1.111852555817223e-15</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1064215710129304</v>
+        <v>-0.1064215710127527</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.784221025323803e-13</v>
+        <v>-3.378329564857779e-13</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.68388561734914e-07</v>
+        <v>1.683885617331793e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>2.806476028915234e-08</v>
+        <v>2.806476028886322e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02660539275411641</v>
+        <v>0.02660539275384233</v>
       </c>
       <c r="I11" t="n">
-        <v>5.612952057830467</v>
+        <v>5.612952057772643</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0266053927541634</v>
+        <v>-0.02660539275370866</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.013368217045158e-14</v>
+        <v>-1.062191727345148e-13</v>
       </c>
       <c r="L11" t="n">
-        <v>3.987921104453562e-13</v>
+        <v>2.928768338961163e-13</v>
       </c>
       <c r="M11" t="n">
-        <v>8.550105194513328e-16</v>
+        <v>1.107938535796261e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1064215710113263</v>
+        <v>0.1064215710116265</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.022001209684786e-13</v>
+        <v>-2.991587646272846e-13</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0266053927541634</v>
+        <v>0.02660539275370866</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.013368217045158e-14</v>
+        <v>1.062191727345148e-13</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.987921104453562e-13</v>
+        <v>-2.928768338961163e-13</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.550105194513328e-16</v>
+        <v>-1.107938535796261e-15</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1064215710137209</v>
+        <v>-0.1064215710133851</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.786019720542305e-13</v>
+        <v>-3.381562717798038e-13</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.683885617332492e-07</v>
+        <v>-1.683885617318994e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.806476028887486e-08</v>
+        <v>-2.80647602886499e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02660539275385337</v>
+        <v>-0.02660539275364011</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.612952057774971</v>
+        <v>-5.61295205772998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02660539275385337</v>
+        <v>0.0266053927536401</v>
       </c>
       <c r="K12" t="n">
-        <v>8.020341599304231e-14</v>
+        <v>1.069749663333046e-13</v>
       </c>
       <c r="L12" t="n">
-        <v>3.983480212355062e-13</v>
+        <v>2.928768338961163e-13</v>
       </c>
       <c r="M12" t="n">
-        <v>8.557517805408608e-16</v>
+        <v>1.110346483951892e-15</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1064215710113285</v>
+        <v>0.1064215710116274</v>
       </c>
       <c r="O12" t="n">
-        <v>2.022708440431196e-13</v>
+        <v>3.016785702947814e-13</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.02660539275385337</v>
+        <v>-0.0266053927536401</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.020341599304231e-14</v>
+        <v>-1.069749663333046e-13</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.983480212355062e-13</v>
+        <v>-2.928768338961163e-13</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.557517805408608e-16</v>
+        <v>-1.110346483951892e-15</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1064215710137182</v>
+        <v>-0.1064215710133851</v>
       </c>
       <c r="U12" t="n">
-        <v>2.789496519151347e-13</v>
+        <v>3.401712277050454e-13</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.683885617333849e-07</v>
+        <v>-1.68388561730854e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.806476028889748e-08</v>
+        <v>-2.806476028847566e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02660539275387482</v>
+        <v>-0.02660539275347493</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.612952057779497</v>
+        <v>-5.612952057695132</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02660539275387483</v>
+        <v>0.02660539275347493</v>
       </c>
       <c r="K13" t="n">
-        <v>8.017778624435488e-14</v>
+        <v>1.069827612644598e-13</v>
       </c>
       <c r="L13" t="n">
-        <v>1.73749903353837e-13</v>
+        <v>7.749356711883593e-14</v>
       </c>
       <c r="M13" t="n">
-        <v>8.569012298343786e-16</v>
+        <v>1.108175038367591e-15</v>
       </c>
       <c r="N13" t="n">
-        <v>0.106421571011891</v>
+        <v>0.1064215710122927</v>
       </c>
       <c r="O13" t="n">
-        <v>2.022430901330703e-13</v>
+        <v>3.016968591146563e-13</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.02660539275387483</v>
+        <v>-0.02660539275347493</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.017778624435488e-14</v>
+        <v>-1.069827612644598e-13</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.73749903353837e-13</v>
+        <v>-7.749356711883593e-14</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.569012298343786e-16</v>
+        <v>-1.108175038367591e-15</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1064215710129344</v>
+        <v>-0.1064215710127581</v>
       </c>
       <c r="U13" t="n">
-        <v>2.788236273330586e-13</v>
+        <v>3.401997084721029e-13</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.59006837140946e-08</v>
+        <v>2.590068371235987e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>4.316780619015766e-09</v>
+        <v>4.316780618726646e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004092308026826946</v>
+        <v>0.00409230802655286</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8633561238031532</v>
+        <v>0.8633561237453291</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.004092308026883984</v>
+        <v>-0.00409230802665661</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.362018027011895e-14</v>
+        <v>-8.343190697023063e-14</v>
       </c>
       <c r="L14" t="n">
-        <v>3.466116282879739e-13</v>
+        <v>5.151434834260726e-14</v>
       </c>
       <c r="M14" t="n">
-        <v>3.51193307424836e-16</v>
+        <v>9.659056027357996e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01636923210568808</v>
+        <v>0.01636923210654651</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.810951370820892e-14</v>
+        <v>-1.977987715970128e-13</v>
       </c>
       <c r="P14" t="n">
-        <v>0.004092308026883984</v>
+        <v>0.00409230802665661</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.362018027011895e-14</v>
+        <v>8.343190697023063e-14</v>
       </c>
       <c r="R14" t="n">
-        <v>-3.466116282879739e-13</v>
+        <v>-5.151434834260726e-14</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.51193307424836e-16</v>
+        <v>-9.659056027357996e-16</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01636923210776953</v>
+        <v>-0.01636923210685914</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.436115679125046e-13</v>
+        <v>-3.027926702243698e-13</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>2.59006837140946e-08</v>
+        <v>2.590068371756404e-08</v>
       </c>
       <c r="G15" t="n">
-        <v>4.316780619015766e-09</v>
+        <v>4.316780619594007e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004092308026826946</v>
+        <v>0.004092308027375119</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8633561238031532</v>
+        <v>0.8633561239188015</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.004092308026883984</v>
+        <v>-0.004092308027338731</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.35688615624581e-14</v>
+        <v>-8.34905568022101e-14</v>
       </c>
       <c r="L15" t="n">
-        <v>3.634870182622763e-13</v>
+        <v>3.348432642269472e-13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.582742029919923e-16</v>
+        <v>9.702846761431884e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01636923210576091</v>
+        <v>0.01636923210579333</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.801105008639339e-14</v>
+        <v>-1.983017031738155e-13</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004092308026883984</v>
+        <v>0.004092308027338731</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35688615624581e-14</v>
+        <v>8.34905568022101e-14</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.634870182622763e-13</v>
+        <v>-3.348432642269472e-13</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.582742029919923e-16</v>
+        <v>-9.702846761431884e-16</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01636923210794006</v>
+        <v>-0.01636923210780417</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.434021192883554e-13</v>
+        <v>-3.026416376394475e-13</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.590068371486095e-08</v>
+        <v>-2.590068371440567e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.316780619143492e-09</v>
+        <v>-4.316780619067612e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.00409230802694803</v>
+        <v>-0.004092308026876096</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8633561238286983</v>
+        <v>-0.8633561238135223</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004092308026948044</v>
+        <v>0.004092308026876101</v>
       </c>
       <c r="K16" t="n">
-        <v>3.32663270766845e-14</v>
+        <v>8.282471645885687e-14</v>
       </c>
       <c r="L16" t="n">
-        <v>3.629319067499637e-13</v>
+        <v>3.352873534367973e-13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.536236808885884e-16</v>
+        <v>9.685082054614662e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01636923210576025</v>
+        <v>0.01636923210579155</v>
       </c>
       <c r="O16" t="n">
-        <v>5.70921169700583e-14</v>
+        <v>1.962785953793687e-13</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.004092308026948044</v>
+        <v>-0.004092308026876101</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.32663270766845e-14</v>
+        <v>-8.282471645885687e-14</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.629319067499637e-13</v>
+        <v>-3.352873534367973e-13</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.536236808885884e-16</v>
+        <v>-9.685082054614662e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01636923210793961</v>
+        <v>-0.01636923210780417</v>
       </c>
       <c r="U16" t="n">
-        <v>1.425058454900481e-13</v>
+        <v>3.006697033737733e-13</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.590068371506487e-08</v>
+        <v>-2.590068371385616e-08</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.316780619177479e-09</v>
+        <v>-4.316780618976026e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00409230802698025</v>
+        <v>-0.004092308026789272</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8633561238354956</v>
+        <v>-0.8633561237952051</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00409230802698024</v>
+        <v>0.004092308026789282</v>
       </c>
       <c r="K17" t="n">
-        <v>3.341636523803729e-14</v>
+        <v>8.280285128504592e-14</v>
       </c>
       <c r="L17" t="n">
-        <v>3.465006059855114e-13</v>
+        <v>5.10702591327572e-14</v>
       </c>
       <c r="M17" t="n">
-        <v>3.547861404194171e-16</v>
+        <v>9.693603322947123e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01636923210568919</v>
+        <v>0.01636923210655006</v>
       </c>
       <c r="O17" t="n">
-        <v>5.73153777575905e-14</v>
+        <v>1.962474626761518e-13</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.00409230802698024</v>
+        <v>-0.004092308026789282</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.341636523803729e-14</v>
+        <v>-8.280285128504592e-14</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.465006059855114e-13</v>
+        <v>-5.10702591327572e-14</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.547861404194171e-16</v>
+        <v>-9.693603322947123e-16</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01636923210776908</v>
+        <v>-0.01636923210685737</v>
       </c>
       <c r="U17" t="n">
-        <v>1.431828136706332e-13</v>
+        <v>3.005696450341222e-13</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>4.245243044716826e-22</v>
+        <v>-9.538267877460151e-22</v>
       </c>
       <c r="G18" t="n">
-        <v>5.306553805896032e-23</v>
+        <v>-1.192283484682519e-22</v>
       </c>
       <c r="H18" t="n">
-        <v>5.030613007989438e-17</v>
+        <v>-1.130284743479028e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>1.061310761179206e-14</v>
+        <v>-2.384566969365038e-14</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.030613008684149e-17</v>
+        <v>1.130284743554885e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>3.885780586188048e-15</v>
+        <v>1.595945597898663e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.270205090833757e-13</v>
+        <v>-1.392048131767468e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>-7.01804066249867e-16</v>
+        <v>-7.228375883960858e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>5.0804263836559e-13</v>
+        <v>5.568184802129394e-13</v>
       </c>
       <c r="O18" t="n">
-        <v>1.551536676913656e-14</v>
+        <v>6.38378239159465e-16</v>
       </c>
       <c r="P18" t="n">
-        <v>5.030613008684149e-17</v>
+        <v>-1.130284743554885e-16</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.885780586188048e-15</v>
+        <v>-1.595945597898663e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.270205090833757e-13</v>
+        <v>1.392048131767468e-13</v>
       </c>
       <c r="S18" t="n">
-        <v>7.01804066249867e-16</v>
+        <v>7.228375883960858e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>5.081214343014151e-13</v>
+        <v>5.568200387535624e-13</v>
       </c>
       <c r="U18" t="n">
-        <v>1.554312234475219e-14</v>
+        <v>6.38378239159465e-16</v>
       </c>
     </row>
     <row r="19">
@@ -2760,37 +2760,37 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.986894838778718e-15</v>
+        <v>-2.437719788167601e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1381800899578367</v>
+        <v>0.1381800899579118</v>
       </c>
       <c r="M19" t="n">
-        <v>-6.517254395557321e-16</v>
+        <v>-7.130671584808762e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5527203598313468</v>
+        <v>-0.552720359831647</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.594530754352647e-14</v>
+        <v>-9.755817814025407e-16</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.986894838778718e-15</v>
+        <v>2.437719788167601e-16</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1381800899578367</v>
+        <v>-0.1381800899579118</v>
       </c>
       <c r="S19" t="n">
-        <v>6.517254395557321e-16</v>
+        <v>7.130671584808762e-16</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5527203598313467</v>
+        <v>-0.552720359831647</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.594985116670313e-14</v>
+        <v>-9.745940491313308e-16</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.839009265922372e-23</v>
+        <v>2.14003602373681e-22</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.548761582402965e-24</v>
+        <v>2.675045029671012e-23</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.364225980118011e-18</v>
+        <v>2.535942688128119e-17</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.09752316480593e-16</v>
+        <v>5.350090059342024e-15</v>
       </c>
       <c r="J20" t="n">
-        <v>3.364225984971083e-18</v>
+        <v>-2.535942688962734e-17</v>
       </c>
       <c r="K20" t="n">
-        <v>3.934352843515398e-15</v>
+        <v>1.387778780781446e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.274808412077357e-13</v>
+        <v>-1.398438521016052e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>-7.022919572274855e-16</v>
+        <v>-7.231086389392072e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>5.099214167321203e-13</v>
+        <v>5.593752593286219e-13</v>
       </c>
       <c r="O20" t="n">
-        <v>1.568190022283034e-14</v>
+        <v>5.551115123125783e-16</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.364225984971083e-18</v>
+        <v>2.535942688962734e-17</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.934352843515398e-15</v>
+        <v>-1.387778780781446e-16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.274808412077357e-13</v>
+        <v>1.398438521016052e-13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.022919572274855e-16</v>
+        <v>7.231086389392072e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>5.099253264822925e-13</v>
+        <v>5.593755439316922e-13</v>
       </c>
       <c r="U20" t="n">
-        <v>1.576516694967722e-14</v>
+        <v>5.551115123125783e-16</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.284779574395323e-14</v>
+        <v>1.284779574395323e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.710505431213761e-12</v>
+        <v>2.710505431213761e-12</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.973308852973428e-15</v>
+        <v>2.564977690112228e-16</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1381800899581102</v>
+        <v>0.1381800899581928</v>
       </c>
       <c r="M21" t="n">
-        <v>-6.515814257910062e-16</v>
+        <v>-7.130646993411015e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5527203598324407</v>
+        <v>-0.552720359832771</v>
       </c>
       <c r="O21" t="n">
-        <v>1.584863837395873e-14</v>
+        <v>1.034213425664638e-15</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.973308852973428e-15</v>
+        <v>-2.564977690112228e-16</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.1381800899581102</v>
+        <v>-0.1381800899581928</v>
       </c>
       <c r="S21" t="n">
-        <v>6.515814257910062e-16</v>
+        <v>7.130646993411015e-16</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5527203598324405</v>
+        <v>-0.552720359832771</v>
       </c>
       <c r="U21" t="n">
-        <v>1.593783244982845e-14</v>
+        <v>1.017768726424953e-15</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.128107672762931e-21</v>
+        <v>1.309926410085742e-21</v>
       </c>
       <c r="G22" t="n">
-        <v>1.410134590953663e-22</v>
+        <v>1.637408012607177e-22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.336807592224073e-16</v>
+        <v>1.552262795951604e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>2.820269181907326e-14</v>
+        <v>3.274816025214354e-14</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.336807591937417e-16</v>
+        <v>-1.552262795659536e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>2.142730437526552e-14</v>
+        <v>4.773959005888173e-15</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.266629055343862e-13</v>
+        <v>-1.547650896327468e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.80191883320569e-16</v>
+        <v>-8.387388006347862e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>5.062255883614868e-13</v>
+        <v>6.190603585309873e-13</v>
       </c>
       <c r="O22" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.909583602355269e-14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.336807591937417e-16</v>
+        <v>1.552262795659536e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.142730437526552e-14</v>
+        <v>-4.773959005888173e-15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.266629055343862e-13</v>
+        <v>1.547650896327468e-13</v>
       </c>
       <c r="S22" t="n">
-        <v>7.80191883320569e-16</v>
+        <v>8.387388006347862e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>5.061894774939023e-13</v>
+        <v>6.190603585309873e-13</v>
       </c>
       <c r="U22" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.909583602355269e-14</v>
       </c>
     </row>
     <row r="23">
@@ -3028,37 +3028,37 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.156674552224533e-14</v>
+        <v>-4.813432388082148e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1422723979854889</v>
+        <v>-0.1422723979853778</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.483837255540837e-16</v>
+        <v>-7.909706835739527e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5690895919419561</v>
+        <v>0.5690895919415118</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.612098424982906e-14</v>
+        <v>-1.942378839985497e-14</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.156674552224533e-14</v>
+        <v>4.813432388082148e-15</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1422723979854889</v>
+        <v>0.1422723979853778</v>
       </c>
       <c r="S23" t="n">
-        <v>6.483837255540837e-16</v>
+        <v>7.909706835739527e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5690895919419559</v>
+        <v>0.569089591941512</v>
       </c>
       <c r="U23" t="n">
-        <v>-8.641297992813301e-14</v>
+        <v>-1.908367070480167e-14</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.497788127626146e-21</v>
+        <v>-1.548538341043327e-21</v>
       </c>
       <c r="G24" t="n">
-        <v>1.872235159532683e-22</v>
+        <v>-1.935672926304159e-22</v>
       </c>
       <c r="H24" t="n">
-        <v>1.774878931236983e-16</v>
+        <v>-1.835017934136342e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.744470319065365e-14</v>
+        <v>-3.871345852608317e-14</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.774878931412836e-16</v>
+        <v>1.83501793410878e-16</v>
       </c>
       <c r="K24" t="n">
-        <v>2.148281552649678e-14</v>
+        <v>4.884981308350689e-15</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.270391248829942e-13</v>
+        <v>-1.554892282637499e-13</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.784571598445922e-16</v>
+        <v>-8.400398432417688e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>5.081653015142231e-13</v>
+        <v>6.219577804167375e-13</v>
       </c>
       <c r="O24" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.976196983832779e-14</v>
       </c>
       <c r="P24" t="n">
-        <v>1.774878931412836e-16</v>
+        <v>-1.83501793410878e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.148281552649678e-14</v>
+        <v>-4.884981308350689e-15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.270391248829942e-13</v>
+        <v>1.554892282637499e-13</v>
       </c>
       <c r="S24" t="n">
-        <v>7.784571598445922e-16</v>
+        <v>8.400398432417688e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>5.081478059699478e-13</v>
+        <v>6.219559372730443e-13</v>
       </c>
       <c r="U24" t="n">
-        <v>8.615330671091215e-14</v>
+        <v>1.953992523340276e-14</v>
       </c>
     </row>
     <row r="25">
@@ -3162,37 +3162,37 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2.141473676500339e-14</v>
+        <v>4.829631977857021e-15</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1422723979851855</v>
+        <v>-0.1422723979850524</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.486090920928102e-16</v>
+        <v>-7.903516927150042e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5690895919407426</v>
+        <v>0.5690895919402106</v>
       </c>
       <c r="O25" t="n">
-        <v>8.54625573384283e-14</v>
+        <v>1.931016027632206e-14</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.141473676500339e-14</v>
+        <v>-4.829631977857021e-15</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1422723979851855</v>
+        <v>0.1422723979850524</v>
       </c>
       <c r="S25" t="n">
-        <v>6.486090920928102e-16</v>
+        <v>7.903516927150042e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5690895919407422</v>
+        <v>0.5690895919402106</v>
       </c>
       <c r="U25" t="n">
-        <v>8.585533678159801e-14</v>
+        <v>1.932689554653355e-14</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.239060668061288e-21</v>
+        <v>-1.427057497211222e-20</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.54882583507661e-22</v>
+        <v>-1.783821871514027e-21</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.208286891652626e-16</v>
+        <v>-1.691063134195298e-15</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.309765167015322e-13</v>
+        <v>-3.567643743028054e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>6.208286892050575e-16</v>
+        <v>1.691063134224552e-15</v>
       </c>
       <c r="K26" t="n">
-        <v>4.729550084903167e-14</v>
+        <v>2.509104035652854e-14</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.408064744864054e-14</v>
+        <v>-1.338928967697939e-13</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.566659550508945e-16</v>
+        <v>-8.92081547521073e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>3.361255407452572e-13</v>
+        <v>5.355715870791755e-13</v>
       </c>
       <c r="O26" t="n">
-        <v>1.891820033961267e-13</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.208286892050575e-16</v>
+        <v>-1.691063134224552e-15</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.729550084903167e-14</v>
+        <v>-2.509104035652854e-14</v>
       </c>
       <c r="R26" t="n">
-        <v>8.408064744864054e-14</v>
+        <v>1.338928967697939e-13</v>
       </c>
       <c r="S26" t="n">
-        <v>4.566659550508945e-16</v>
+        <v>8.92081547521073e-16</v>
       </c>
       <c r="T26" t="n">
-        <v>3.356314604241669e-13</v>
+        <v>5.346834086594754e-13</v>
       </c>
       <c r="U26" t="n">
-        <v>1.891820033961267e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.055647319032516e-13</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.336808689942018e-11</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.676173038271414e-14</v>
+        <v>-2.428299574909421e-14</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.02251308472698921</v>
+        <v>-0.02251308472689817</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.275943135957665e-16</v>
+        <v>-6.792060231468612e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.09005233890795705</v>
+        <v>0.09005233890759357</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.867563777792461e-13</v>
+        <v>-9.683249195355488e-14</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.676173038271414e-14</v>
+        <v>2.428299574909421e-14</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02251308472698921</v>
+        <v>0.02251308472689817</v>
       </c>
       <c r="S27" t="n">
-        <v>4.275943135957665e-16</v>
+        <v>6.792060231468612e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>0.09005233890795727</v>
+        <v>0.09005233890759312</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.87337465282466e-13</v>
+        <v>-9.743147403919787e-14</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>2.271685965345289e-21</v>
+        <v>-8.659282406385243e-22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.839607456681611e-22</v>
+        <v>-1.082410300798155e-22</v>
       </c>
       <c r="H28" t="n">
-        <v>2.691947868934167e-16</v>
+        <v>-1.026124965156651e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>5.679214913363221e-14</v>
+        <v>-2.164820601596311e-14</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.691947868883633e-16</v>
+        <v>1.026124964512247e-16</v>
       </c>
       <c r="K28" t="n">
-        <v>4.662936703425657e-14</v>
+        <v>2.509104035652854e-14</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.392083454423743e-14</v>
+        <v>-1.339430682253256e-13</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.597017211338539e-16</v>
+        <v>-8.946836327350383e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>3.356551736916173e-13</v>
+        <v>5.357769349706443e-13</v>
       </c>
       <c r="O28" t="n">
-        <v>1.865174681370263e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
       <c r="P28" t="n">
-        <v>2.691947868883633e-16</v>
+        <v>-1.026124964512247e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>-4.662936703425657e-14</v>
+        <v>-2.509104035652854e-14</v>
       </c>
       <c r="R28" t="n">
-        <v>8.392083454423743e-14</v>
+        <v>1.339430682253256e-13</v>
       </c>
       <c r="S28" t="n">
-        <v>4.597017211338539e-16</v>
+        <v>8.946836327350383e-16</v>
       </c>
       <c r="T28" t="n">
-        <v>3.357113942420649e-13</v>
+        <v>5.357675024117436e-13</v>
       </c>
       <c r="U28" t="n">
-        <v>1.865174681370263e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
     </row>
     <row r="29">
@@ -3427,40 +3427,40 @@
         <v>4.336808689942018e-11</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>4.699066218428263e-14</v>
+        <v>2.455235447019222e-14</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.02251308472681168</v>
+        <v>-0.02251308472655245</v>
       </c>
       <c r="M29" t="n">
-        <v>-4.277060378933975e-16</v>
+        <v>-6.79736818501431e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>0.09005233890724629</v>
+        <v>0.09005233890620934</v>
       </c>
       <c r="O29" t="n">
-        <v>1.878501785844625e-13</v>
+        <v>9.748393434298417e-14</v>
       </c>
       <c r="P29" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4.699066218428263e-14</v>
+        <v>-2.455235447019222e-14</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02251308472681168</v>
+        <v>0.02251308472655245</v>
       </c>
       <c r="S29" t="n">
-        <v>4.277060378933975e-16</v>
+        <v>6.79736818501431e-16</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09005233890724762</v>
+        <v>0.09005233890621112</v>
       </c>
       <c r="U29" t="n">
-        <v>1.880751188897983e-13</v>
+        <v>9.893490141855262e-14</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>1.521452776224584e-21</v>
+        <v>5.558909158194926e-21</v>
       </c>
       <c r="G30" t="n">
-        <v>1.90181597028073e-22</v>
+        <v>6.948636447743658e-22</v>
       </c>
       <c r="H30" t="n">
-        <v>1.802921539826132e-16</v>
+        <v>6.587307352460988e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>3.80363194056146e-14</v>
+        <v>1.389727289548732e-13</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.802921540148587e-16</v>
+        <v>-6.587307352355628e-16</v>
       </c>
       <c r="K30" t="n">
-        <v>3.308464613382966e-14</v>
+        <v>8.149037000748649e-14</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.586154729876037e-14</v>
+        <v>-7.549516567451064e-14</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.071191746415678e-16</v>
+        <v>-6.149594722337781e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>1.432963679872677e-13</v>
+        <v>3.019806626980426e-13</v>
       </c>
       <c r="O30" t="n">
-        <v>1.323385845353187e-13</v>
+        <v>3.268496584496461e-13</v>
       </c>
       <c r="P30" t="n">
-        <v>1.802921540148587e-16</v>
+        <v>6.587307352355628e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>-3.308464613382966e-14</v>
+        <v>-8.149037000748649e-14</v>
       </c>
       <c r="R30" t="n">
-        <v>3.586154729876037e-14</v>
+        <v>7.549516567451064e-14</v>
       </c>
       <c r="S30" t="n">
-        <v>1.071191746415678e-16</v>
+        <v>6.149594722337781e-16</v>
       </c>
       <c r="T30" t="n">
-        <v>1.435960104028153e-13</v>
+        <v>3.019806626980426e-13</v>
       </c>
       <c r="U30" t="n">
-        <v>1.314504061156185e-13</v>
+        <v>3.25961480029946e-13</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4.111294638065033e-13</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-11</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.363850098582328e-14</v>
+        <v>-8.302864127521905e-14</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.004092308026984459</v>
+        <v>-0.004092308026951263</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.812412399583363e-16</v>
+        <v>-3.781516349833479e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>0.01636923210793761</v>
+        <v>0.01636923210780461</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.351703120018463e-13</v>
+        <v>-3.321614858409899e-13</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.363850098582328e-14</v>
+        <v>8.302864127521905e-14</v>
       </c>
       <c r="R31" t="n">
-        <v>0.004092308026984459</v>
+        <v>0.004092308026951263</v>
       </c>
       <c r="S31" t="n">
-        <v>1.812412399583363e-16</v>
+        <v>3.781516349833479e-16</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01636923210793872</v>
+        <v>0.01636923210780616</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.339376958847387e-13</v>
+        <v>-3.320676443607612e-13</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.267053248582775e-21</v>
+        <v>-1.37221141352895e-21</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.583816560728468e-22</v>
+        <v>-1.715264266911187e-22</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.241458099570588e-16</v>
+        <v>-1.626070525031805e-16</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.316763312145694e-13</v>
+        <v>-3.430528533822374e-14</v>
       </c>
       <c r="J32" t="n">
-        <v>6.241458099166313e-16</v>
+        <v>1.62607052525906e-16</v>
       </c>
       <c r="K32" t="n">
-        <v>3.352873534367973e-14</v>
+        <v>8.304468224196171e-14</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.572678161051504e-14</v>
+        <v>-7.529960270764857e-14</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.101549407245273e-16</v>
+        <v>-6.205973235307027e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>1.430490993232485e-13</v>
+        <v>3.011773773084481e-13</v>
       </c>
       <c r="O32" t="n">
-        <v>1.341149413747189e-13</v>
+        <v>3.312905505481467e-13</v>
       </c>
       <c r="P32" t="n">
-        <v>-6.241458099166313e-16</v>
+        <v>-1.62607052525906e-16</v>
       </c>
       <c r="Q32" t="n">
-        <v>-3.352873534367973e-14</v>
+        <v>-8.304468224196171e-14</v>
       </c>
       <c r="R32" t="n">
-        <v>3.572678161051504e-14</v>
+        <v>7.529960270764857e-14</v>
       </c>
       <c r="S32" t="n">
-        <v>1.101549407245273e-16</v>
+        <v>6.205973235307027e-16</v>
       </c>
       <c r="T32" t="n">
-        <v>1.427650451406545e-13</v>
+        <v>3.012195527729578e-13</v>
       </c>
       <c r="U32" t="n">
-        <v>1.341149413747189e-13</v>
+        <v>3.321787289678468e-13</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.469446951953614e-18</v>
+        <v>-1.040834085586084e-17</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.336808689942018e-19</v>
+        <v>-1.301042606982605e-18</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.111294638065033e-13</v>
+        <v>-1.23338839141951e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>-8.673617379884035e-11</v>
+        <v>-2.602085213965211e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="K33" t="n">
-        <v>3.300334953305864e-14</v>
+        <v>8.278430025063367e-14</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.004092308026943159</v>
+        <v>-0.004092308026713454</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.805385040703131e-16</v>
+        <v>-3.778386247725941e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0163692321077733</v>
+        <v>0.01636923210685359</v>
       </c>
       <c r="O33" t="n">
-        <v>1.326015304135093e-13</v>
+        <v>3.310853897287379e-13</v>
       </c>
       <c r="P33" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3.300334953305864e-14</v>
+        <v>-8.278430025063367e-14</v>
       </c>
       <c r="R33" t="n">
-        <v>0.004092308026943159</v>
+        <v>0.004092308026713454</v>
       </c>
       <c r="S33" t="n">
-        <v>1.805385040703131e-16</v>
+        <v>3.778386247725941e-16</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01636923210777352</v>
+        <v>0.01636923210685604</v>
       </c>
       <c r="U33" t="n">
-        <v>1.314252658509586e-13</v>
+        <v>3.311890122763301e-13</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.23815409079487e-08</v>
+        <v>3.238154090727605e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03069770078073537</v>
+        <v>0.03069770078009769</v>
       </c>
       <c r="I2" t="n">
-        <v>6.476308181589739</v>
+        <v>6.476308181455209</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.000497800553184697</v>
+        <v>-0.0004978005531852484</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.521497120175572e-16</v>
+        <v>-1.662109234779601e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.000497800553184697</v>
+        <v>0.0004978005531852484</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.521497120175572e-16</v>
+        <v>1.662109234779601e-16</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.03069770078073537</v>
+        <v>-0.0306977007800977</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.056826096416637e-13</v>
+        <v>-1.113145175800432e-13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.311312169960388e-13</v>
+        <v>6.929179452441758e-14</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.448418222140104e-16</v>
+        <v>6.793077920818111e-16</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1227908031186297</v>
+        <v>0.1227908031188893</v>
       </c>
       <c r="AM2" t="n">
-        <v>-4.296386158179834e-13</v>
+        <v>-4.569396361138199e-13</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03069770078073537</v>
+        <v>0.0306977007800977</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.056826096416637e-13</v>
+        <v>1.113145175800432e-13</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.311312169960388e-13</v>
+        <v>-6.929179452441758e-14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-6.448418222140104e-16</v>
+        <v>-6.793077920818111e-16</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.1227908031194165</v>
+        <v>-0.1227908031193052</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2.044570420319988e-13</v>
+        <v>-2.10947469366439e-13</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>3.238154090847134e-08</v>
+        <v>3.238154090861119e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03069770078123083</v>
+        <v>0.03069770078136341</v>
       </c>
       <c r="I3" t="n">
-        <v>6.476308181694269</v>
+        <v>6.476308181722239</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0004978005531828473</v>
+        <v>0.0004978005531833375</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.522206922017046e-16</v>
+        <v>1.66212339507947e-16</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.03069770078123084</v>
+        <v>-0.03069770078136342</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.056301890213897e-13</v>
+        <v>-1.113132344405785e-13</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.441136264825673e-13</v>
+        <v>2.900735207589378e-13</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.44768254624497e-16</v>
+        <v>6.792862188998355e-16</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1227908031177474</v>
+        <v>0.1227908031179764</v>
       </c>
       <c r="AM3" t="n">
-        <v>-4.295338792934306e-13</v>
+        <v>-4.569368345576162e-13</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.03069770078123084</v>
+        <v>0.03069770078136342</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.056301890213897e-13</v>
+        <v>1.113132344405785e-13</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3.441136264825673e-13</v>
+        <v>-2.900735207589378e-13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6.44768254624497e-16</v>
+        <v>-6.792862188998355e-16</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.1227908031198122</v>
+        <v>-0.1227908031197169</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2.042472548349078e-13</v>
+        <v>-2.109425720858546e-13</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.238154090849235e-08</v>
+        <v>-3.238154090802875e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03069770078125074</v>
+        <v>-0.03069770078081126</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.476308181698468</v>
+        <v>-6.47630818160575</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="AC4" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004978005531828473</v>
+        <v>0.0004978005531833375</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.530921263289087e-16</v>
+        <v>-1.678371401407517e-16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03069770078125075</v>
+        <v>0.03069770078081126</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.060312698528079e-13</v>
+        <v>1.118832211966489e-13</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.440719931191438e-13</v>
+        <v>2.900318873955143e-13</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.447799049403346e-16</v>
+        <v>6.792836862529862e-16</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1227908031177475</v>
+        <v>0.1227908031179765</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.31381983041816e-13</v>
+        <v>4.598491472941029e-13</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03069770078125075</v>
+        <v>-0.03069770078081126</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.060312698528079e-13</v>
+        <v>-1.118832211966489e-13</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3.440719931191438e-13</v>
+        <v>-2.900318873955143e-13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-6.447799049403346e-16</v>
+        <v>-6.792836862529862e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.122790803119812</v>
+        <v>-0.1227908031197167</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.048056360750312e-13</v>
+        <v>2.114501798857903e-13</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2381540908444e-08</v>
+        <v>-3.238154090783764e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03069770078120491</v>
+        <v>-0.03069770078063009</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.4763081816888</v>
+        <v>-6.476308181567529</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004978005531846971</v>
+        <v>0.0004978005531852483</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.530956406052565e-16</v>
+        <v>-1.678374041412947e-16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.03069770078120492</v>
+        <v>0.03069770078063009</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06028662285421e-13</v>
+        <v>1.118830786238024e-13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.312283615106935e-13</v>
+        <v>6.938893903907228e-14</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.4461311945537e-16</v>
+        <v>6.793499579772974e-16</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1227908031186295</v>
+        <v>0.1227908031188891</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.313767609041526e-13</v>
+        <v>4.598489149359651e-13</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03069770078120492</v>
+        <v>-0.03069770078063009</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.06028662285421e-13</v>
+        <v>-1.118830786238024e-13</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.312283615106935e-13</v>
+        <v>-6.938893903907228e-14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-6.4461311945537e-16</v>
+        <v>-6.793499579772974e-16</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.1227908031194169</v>
+        <v>-0.1227908031193055</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.04795212808373e-13</v>
+        <v>2.11449556806849e-13</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009998931153223171</v>
+        <v>-0.009998931153223175</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001666488525537195</v>
+        <v>-0.001666488525537196</v>
       </c>
       <c r="H6" t="n">
-        <v>-1579.831122209261</v>
+        <v>-1579.831122209262</v>
       </c>
       <c r="I6" t="n">
-        <v>-333297.705107439</v>
+        <v>-333297.7051074391</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.000497800553184697</v>
+        <v>-0.0004978005531852484</v>
       </c>
       <c r="K6" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.521497120175572e-16</v>
+        <v>-1.662109234779601e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.513191775452895e-16</v>
+        <v>-1.837675371856052e-16</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000497800553184697</v>
+        <v>0.0004978005531852484</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.521497120175572e-16</v>
+        <v>1.662109234779601e-16</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="AE6" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.513191775452895e-16</v>
+        <v>1.837675371856052e-16</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.1688777907386338</v>
+        <v>-0.1688777907381791</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.016589946586002e-13</v>
+        <v>-1.111710482853654e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.297850715786808e-13</v>
+        <v>7.138734048339757e-14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.003947125286698e-15</v>
+        <v>1.088707853982457e-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6755111629518569</v>
+        <v>0.6755111629520767</v>
       </c>
       <c r="AM6" t="n">
-        <v>-3.043623884663222e-13</v>
+        <v>-3.465050389997536e-13</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.1688777907386338</v>
+        <v>0.1688777907381791</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.016589946586002e-13</v>
+        <v>1.111710482853654e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1.297850715786808e-13</v>
+        <v>-7.138734048339757e-14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.003947125286698e-15</v>
+        <v>-1.088707853982457e-15</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.6755111629526356</v>
+        <v>-0.6755111629525059</v>
       </c>
       <c r="AS6" t="n">
-        <v>-3.055915794852785e-13</v>
+        <v>-3.205212507124386e-13</v>
       </c>
     </row>
     <row r="7">
@@ -4698,112 +4698,112 @@
         <v>-333297.7051074389</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="K7" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0004978005531828473</v>
+        <v>0.0004978005531833375</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.522206922017046e-16</v>
+        <v>1.66212339507947e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.004231960428275111</v>
+        <v>0.004231960428276507</v>
       </c>
       <c r="AE7" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.511978472574226e-16</v>
+        <v>1.84055805033667e-16</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1688777907390886</v>
+        <v>-0.1688777907395433</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.016964272859168e-13</v>
+        <v>-1.109572406080648e-13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.533839887381873e-13</v>
+        <v>2.959854583650667e-13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.003662332591825e-15</v>
+        <v>1.089089653757695e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.6755111629511585</v>
+        <v>0.6755111629513628</v>
       </c>
       <c r="AM7" t="n">
-        <v>-3.043323765989816e-13</v>
+        <v>-3.46075886313227e-13</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1688777907390886</v>
+        <v>0.1688777907395433</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.016964272859168e-13</v>
+        <v>1.109572406080648e-13</v>
       </c>
       <c r="AP7" t="n">
-        <v>-3.533839887381873e-13</v>
+        <v>-2.959854583650667e-13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.003662332591825e-15</v>
+        <v>-1.089089653757695e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.6755111629532795</v>
+        <v>-0.6755111629531396</v>
       </c>
       <c r="AS7" t="n">
-        <v>-3.058461871165189e-13</v>
+        <v>-3.196675573351616e-13</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.068846776830474e-06</v>
+        <v>-1.068846776828246e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.781411294717457e-07</v>
+        <v>-1.781411294713743e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.168877790739215</v>
+        <v>-0.1688777907388628</v>
       </c>
       <c r="I8" t="n">
-        <v>-35.62822589434915</v>
+        <v>-35.62822589427485</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0004978005531828473</v>
+        <v>0.0004978005531833375</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.530921263289087e-16</v>
+        <v>-1.678371401407517e-16</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004231960428275111</v>
+        <v>0.004231960428276507</v>
       </c>
       <c r="AE8" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.525494836327788e-16</v>
+        <v>-1.864890197036802e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.168877790739215</v>
+        <v>0.1688777907388629</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.020563685019457e-13</v>
+        <v>1.116118975923458e-13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.534950110406498e-13</v>
+        <v>2.955413691552167e-13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.004399389143434e-15</v>
+        <v>1.088220089750561e-15</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6755111629511581</v>
+        <v>0.6755111629513639</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.057675499107009e-13</v>
+        <v>3.486380836536046e-13</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.168877790739215</v>
+        <v>-0.1688777907388629</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1.020563685019457e-13</v>
+        <v>-1.116118975923458e-13</v>
       </c>
       <c r="AP8" t="n">
-        <v>-3.534950110406498e-13</v>
+        <v>-2.955413691552167e-13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.004399389143434e-15</v>
+        <v>-1.088220089750561e-15</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.6755111629532804</v>
+        <v>-0.6755111629531383</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.065706611009732e-13</v>
+        <v>3.210333019004703e-13</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.068846776830301e-06</v>
+        <v>-1.068846776827107e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.781411294717168e-07</v>
+        <v>-1.781411294711845e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1688777907391875</v>
+        <v>-0.1688777907386829</v>
       </c>
       <c r="I9" t="n">
-        <v>-35.62822589434336</v>
+        <v>-35.62822589423689</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0004978005531846971</v>
+        <v>0.0004978005531852483</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.530956406052565e-16</v>
+        <v>-1.678374041412947e-16</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="AE9" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.525337304621532e-16</v>
+        <v>-1.864873098520545e-16</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1688777907391875</v>
+        <v>0.1688777907386829</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.020658017410055e-13</v>
+        <v>1.116125327618011e-13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.294520046712933e-13</v>
+        <v>7.149836278586008e-14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.00316870126798e-15</v>
+        <v>1.088622777137711e-15</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6755111629518573</v>
+        <v>0.6755111629520767</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.057815917171203e-13</v>
+        <v>3.486385285113655e-13</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1688777907391875</v>
+        <v>-0.1688777907386829</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1.020658017410055e-13</v>
+        <v>-1.116125327618011e-13</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1.294520046712933e-13</v>
+        <v>-7.149836278586008e-14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.00316870126798e-15</v>
+        <v>-1.088622777137711e-15</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.6755111629526342</v>
+        <v>-0.6755111629525063</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.06613218728913e-13</v>
+        <v>3.21036668059441e-13</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.683885617314446e-07</v>
+        <v>1.683885617262404e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.806476028857409e-08</v>
+        <v>2.806476028770673e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02660539275356824</v>
+        <v>0.02660539275274598</v>
       </c>
       <c r="I10" t="n">
-        <v>5.612952057714819</v>
+        <v>5.612952057541346</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="K10" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.513191775452895e-16</v>
+        <v>-1.837675371856052e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="S10" t="n">
-        <v>-9.957666828069171e-17</v>
+        <v>-1.579633952279717e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="U10" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="W10" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.513191775452895e-16</v>
+        <v>1.837675371856052e-16</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="AE10" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.957666828069171e-17</v>
+        <v>1.579633952279717e-16</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.02660539275348128</v>
+        <v>-0.02660539275257179</v>
       </c>
       <c r="AI10" t="n">
-        <v>-8.004421522552583e-14</v>
+        <v>-1.062459638123764e-13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.729727472365994e-13</v>
+        <v>7.593925488436071e-14</v>
       </c>
       <c r="AK10" t="n">
-        <v>8.564708730707019e-16</v>
+        <v>1.111852555817223e-15</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1064215710118925</v>
+        <v>0.1064215710122962</v>
       </c>
       <c r="AM10" t="n">
-        <v>-2.018431888207753e-13</v>
+        <v>-2.996428263884806e-13</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02660539275348128</v>
+        <v>0.02660539275257179</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.004421522552583e-14</v>
+        <v>1.062459638123764e-13</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1.729727472365994e-13</v>
+        <v>-7.593925488436071e-14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-8.564708730707019e-16</v>
+        <v>-1.111852555817223e-15</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1064215710129304</v>
+        <v>-0.1064215710127527</v>
       </c>
       <c r="AS10" t="n">
-        <v>-2.784221025323803e-13</v>
+        <v>-3.378329564857779e-13</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.68388561734914e-07</v>
+        <v>1.683885617331793e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>2.806476028915234e-08</v>
+        <v>2.806476028886322e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02660539275411641</v>
+        <v>0.02660539275384233</v>
       </c>
       <c r="I11" t="n">
-        <v>5.612952057830467</v>
+        <v>5.612952057772643</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="K11" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="R11" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="U11" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="W11" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004231960428275111</v>
+        <v>0.004231960428276507</v>
       </c>
       <c r="Y11" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.511978472574226e-16</v>
+        <v>1.84055805033667e-16</v>
       </c>
       <c r="AB11" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01113611787349452</v>
+        <v>0.01113611787349708</v>
       </c>
       <c r="AE11" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AG11" t="n">
-        <v>9.957497490218503e-17</v>
+        <v>1.577061380387217e-16</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.0266053927541634</v>
+        <v>-0.02660539275370866</v>
       </c>
       <c r="AI11" t="n">
-        <v>-8.013368217045158e-14</v>
+        <v>-1.062191727345148e-13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.987921104453562e-13</v>
+        <v>2.928768338961163e-13</v>
       </c>
       <c r="AK11" t="n">
-        <v>8.550105194513328e-16</v>
+        <v>1.107938535796261e-15</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1064215710113263</v>
+        <v>0.1064215710116265</v>
       </c>
       <c r="AM11" t="n">
-        <v>-2.022001209684786e-13</v>
+        <v>-2.991587646272846e-13</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0266053927541634</v>
+        <v>0.02660539275370866</v>
       </c>
       <c r="AO11" t="n">
-        <v>8.013368217045158e-14</v>
+        <v>1.062191727345148e-13</v>
       </c>
       <c r="AP11" t="n">
-        <v>-3.987921104453562e-13</v>
+        <v>-2.928768338961163e-13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-8.550105194513328e-16</v>
+        <v>-1.107938535796261e-15</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.1064215710137209</v>
+        <v>-0.1064215710133851</v>
       </c>
       <c r="AS11" t="n">
-        <v>-2.786019720542305e-13</v>
+        <v>-3.381562717798038e-13</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.683885617332492e-07</v>
+        <v>-1.683885617318994e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.806476028887486e-08</v>
+        <v>-2.80647602886499e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02660539275385337</v>
+        <v>-0.02660539275364011</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.612952057774971</v>
+        <v>-5.61295205772998</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004231960428275111</v>
+        <v>0.004231960428276507</v>
       </c>
       <c r="Y12" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.525494836327788e-16</v>
+        <v>-1.864890197036802e-16</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="AC12" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01113611787349453</v>
+        <v>0.01113611787349708</v>
       </c>
       <c r="AE12" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.007394783138497e-16</v>
+        <v>-1.604804673994475e-16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.02660539275385337</v>
+        <v>0.0266053927536401</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.020341599304231e-14</v>
+        <v>1.069749663333046e-13</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.983480212355062e-13</v>
+        <v>2.928768338961163e-13</v>
       </c>
       <c r="AK12" t="n">
-        <v>8.557517805408608e-16</v>
+        <v>1.110346483951892e-15</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1064215710113285</v>
+        <v>0.1064215710116274</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.022708440431196e-13</v>
+        <v>3.016785702947814e-13</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02660539275385337</v>
+        <v>-0.0266053927536401</v>
       </c>
       <c r="AO12" t="n">
-        <v>-8.020341599304231e-14</v>
+        <v>-1.069749663333046e-13</v>
       </c>
       <c r="AP12" t="n">
-        <v>-3.983480212355062e-13</v>
+        <v>-2.928768338961163e-13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-8.557517805408608e-16</v>
+        <v>-1.110346483951892e-15</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.1064215710137182</v>
+        <v>-0.1064215710133851</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.789496519151347e-13</v>
+        <v>3.401712277050454e-13</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.683885617333849e-07</v>
+        <v>-1.68388561730854e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.806476028889748e-08</v>
+        <v>-2.806476028847566e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02660539275387482</v>
+        <v>-0.02660539275347493</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.612952057779497</v>
+        <v>-5.612952057695132</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="Y13" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.525337304621532e-16</v>
+        <v>-1.864873098520545e-16</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="AC13" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="AE13" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.007901242459449e-16</v>
+        <v>-1.60471871097023e-16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.02660539275387483</v>
+        <v>0.02660539275347493</v>
       </c>
       <c r="AI13" t="n">
-        <v>8.017778624435488e-14</v>
+        <v>1.069827612644598e-13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.73749903353837e-13</v>
+        <v>7.749356711883593e-14</v>
       </c>
       <c r="AK13" t="n">
-        <v>8.569012298343786e-16</v>
+        <v>1.108175038367591e-15</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.106421571011891</v>
+        <v>0.1064215710122927</v>
       </c>
       <c r="AM13" t="n">
-        <v>2.022430901330703e-13</v>
+        <v>3.016968591146563e-13</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.02660539275387483</v>
+        <v>-0.02660539275347493</v>
       </c>
       <c r="AO13" t="n">
-        <v>-8.017778624435488e-14</v>
+        <v>-1.069827612644598e-13</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1.73749903353837e-13</v>
+        <v>-7.749356711883593e-14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-8.569012298343786e-16</v>
+        <v>-1.108175038367591e-15</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.1064215710129344</v>
+        <v>-0.1064215710127581</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.788236273330586e-13</v>
+        <v>3.401997084721029e-13</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.59006837140946e-08</v>
+        <v>2.590068371235987e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>4.316780619015766e-09</v>
+        <v>4.316780618726646e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004092308026826946</v>
+        <v>0.00409230802655286</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8633561238031532</v>
+        <v>0.8633561237453291</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="K14" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.957666828069171e-17</v>
+        <v>-1.579633952279717e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191545</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.180501003454598e-17</v>
+        <v>-8.702157183110913e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="W14" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="Y14" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.957666828069171e-17</v>
+        <v>1.579633952279717e-16</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01853807587190909</v>
+        <v>0.01853807587191545</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.180501003454598e-17</v>
+        <v>8.702157183110913e-17</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.004092308026883984</v>
+        <v>-0.00409230802665661</v>
       </c>
       <c r="AI14" t="n">
-        <v>-3.362018027011895e-14</v>
+        <v>-8.343190697023063e-14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.466116282879739e-13</v>
+        <v>5.151434834260726e-14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.51193307424836e-16</v>
+        <v>9.659056027357996e-16</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01636923210568808</v>
+        <v>0.01636923210654651</v>
       </c>
       <c r="AM14" t="n">
-        <v>-5.810951370820892e-14</v>
+        <v>-1.977987715970128e-13</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.004092308026883984</v>
+        <v>0.00409230802665661</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.362018027011895e-14</v>
+        <v>8.343190697023063e-14</v>
       </c>
       <c r="AP14" t="n">
-        <v>-3.466116282879739e-13</v>
+        <v>-5.151434834260726e-14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-3.51193307424836e-16</v>
+        <v>-9.659056027357996e-16</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.01636923210776953</v>
+        <v>-0.01636923210685914</v>
       </c>
       <c r="AS14" t="n">
-        <v>-1.436115679125046e-13</v>
+        <v>-3.027926702243698e-13</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>2.59006837140946e-08</v>
+        <v>2.590068371756404e-08</v>
       </c>
       <c r="G15" t="n">
-        <v>4.316780619015766e-09</v>
+        <v>4.316780619594007e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004092308026826946</v>
+        <v>0.004092308027375119</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8633561238031532</v>
+        <v>0.8633561239188015</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="K15" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="L15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190386</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.187830652248113e-17</v>
+        <v>-8.72061823187002e-17</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="V15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="W15" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01113611787349452</v>
+        <v>0.01113611787349708</v>
       </c>
       <c r="Y15" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.957497490218503e-17</v>
+        <v>1.577061380387217e-16</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01853807587190073</v>
+        <v>0.01853807587190386</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.187830652248113e-17</v>
+        <v>8.72061823187002e-17</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.004092308026883984</v>
+        <v>-0.004092308027338731</v>
       </c>
       <c r="AI15" t="n">
-        <v>-3.35688615624581e-14</v>
+        <v>-8.34905568022101e-14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.634870182622763e-13</v>
+        <v>3.348432642269472e-13</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.582742029919923e-16</v>
+        <v>9.702846761431884e-16</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01636923210576091</v>
+        <v>0.01636923210579333</v>
       </c>
       <c r="AM15" t="n">
-        <v>-5.801105008639339e-14</v>
+        <v>-1.983017031738155e-13</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.004092308026883984</v>
+        <v>0.004092308027338731</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.35688615624581e-14</v>
+        <v>8.34905568022101e-14</v>
       </c>
       <c r="AP15" t="n">
-        <v>-3.634870182622763e-13</v>
+        <v>-3.348432642269472e-13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-3.582742029919923e-16</v>
+        <v>-9.702846761431884e-16</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.01636923210794006</v>
+        <v>-0.01636923210780417</v>
       </c>
       <c r="AS15" t="n">
-        <v>-1.434021192883554e-13</v>
+        <v>-3.026416376394475e-13</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.590068371486095e-08</v>
+        <v>-2.590068371440567e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.316780619143492e-09</v>
+        <v>-4.316780619067612e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.00409230802694803</v>
+        <v>-0.004092308026876096</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8633561238286983</v>
+        <v>-0.8633561238135223</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01113611787349453</v>
+        <v>0.01113611787349708</v>
       </c>
       <c r="Y16" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.007394783138497e-16</v>
+        <v>-1.604804673994475e-16</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.01853807587190073</v>
+        <v>0.01853807587190385</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="AG16" t="n">
-        <v>-4.302749958412686e-17</v>
+        <v>-8.994593497079611e-17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.004092308026948044</v>
+        <v>0.004092308026876101</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.32663270766845e-14</v>
+        <v>8.282471645885687e-14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.629319067499637e-13</v>
+        <v>3.352873534367973e-13</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.536236808885884e-16</v>
+        <v>9.685082054614662e-16</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01636923210576025</v>
+        <v>0.01636923210579155</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.70921169700583e-14</v>
+        <v>1.962785953793687e-13</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.004092308026948044</v>
+        <v>-0.004092308026876101</v>
       </c>
       <c r="AO16" t="n">
-        <v>-3.32663270766845e-14</v>
+        <v>-8.282471645885687e-14</v>
       </c>
       <c r="AP16" t="n">
-        <v>-3.629319067499637e-13</v>
+        <v>-3.352873534367973e-13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-3.536236808885884e-16</v>
+        <v>-9.685082054614662e-16</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.01636923210793961</v>
+        <v>-0.01636923210780417</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.425058454900481e-13</v>
+        <v>3.006697033737733e-13</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.590068371506487e-08</v>
+        <v>-2.590068371385616e-08</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.316780619177479e-09</v>
+        <v>-4.316780618976026e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00409230802698025</v>
+        <v>-0.004092308026789272</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8633561238354956</v>
+        <v>-0.8633561237952051</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="S17" t="n">
-        <v>4.277158646686195e-17</v>
+        <v>8.998391004434036e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="W17" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="Y17" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.007901242459449e-16</v>
+        <v>-1.60471871097023e-16</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01853807587190909</v>
+        <v>0.01853807587191546</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="AG17" t="n">
-        <v>-4.277158646686195e-17</v>
+        <v>-8.998391004434036e-17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.00409230802698024</v>
+        <v>0.004092308026789282</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.341636523803729e-14</v>
+        <v>8.280285128504592e-14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.465006059855114e-13</v>
+        <v>5.10702591327572e-14</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.547861404194171e-16</v>
+        <v>9.693603322947123e-16</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01636923210568919</v>
+        <v>0.01636923210655006</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.73153777575905e-14</v>
+        <v>1.962474626761518e-13</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.00409230802698024</v>
+        <v>-0.004092308026789282</v>
       </c>
       <c r="AO17" t="n">
-        <v>-3.341636523803729e-14</v>
+        <v>-8.280285128504592e-14</v>
       </c>
       <c r="AP17" t="n">
-        <v>-3.465006059855114e-13</v>
+        <v>-5.10702591327572e-14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-3.547861404194171e-16</v>
+        <v>-9.693603322947123e-16</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.01636923210776908</v>
+        <v>-0.01636923210685737</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.431828136706332e-13</v>
+        <v>3.005696450341222e-13</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>4.245243044716826e-22</v>
+        <v>-9.538267877460151e-22</v>
       </c>
       <c r="G18" t="n">
-        <v>5.306553805896032e-23</v>
+        <v>-1.192283484682519e-22</v>
       </c>
       <c r="H18" t="n">
-        <v>5.030613007989438e-17</v>
+        <v>-1.130284743479028e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>1.061310761179206e-14</v>
+        <v>-2.384566969365038e-14</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.000497800553184697</v>
+        <v>-0.0004978005531852484</v>
       </c>
       <c r="K18" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.521497120175572e-16</v>
+        <v>-1.662109234779601e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="V18" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="W18" t="n">
-        <v>0.000497800553184697</v>
+        <v>0.0004978005531852484</v>
       </c>
       <c r="X18" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.521497120175572e-16</v>
+        <v>1.662109234779601e-16</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0004978005531828473</v>
+        <v>0.0004978005531833375</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.522206922017046e-16</v>
+        <v>1.66212339507947e-16</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="AH18" t="n">
-        <v>-5.030613008684149e-17</v>
+        <v>1.130284743554885e-16</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.885780586188048e-15</v>
+        <v>1.595945597898663e-16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-1.270205090833757e-13</v>
+        <v>-1.392048131767468e-13</v>
       </c>
       <c r="AK18" t="n">
-        <v>-7.01804066249867e-16</v>
+        <v>-7.228375883960858e-16</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.0804263836559e-13</v>
+        <v>5.568184802129394e-13</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.551536676913656e-14</v>
+        <v>6.38378239159465e-16</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.030613008684149e-17</v>
+        <v>-1.130284743554885e-16</v>
       </c>
       <c r="AO18" t="n">
-        <v>-3.885780586188048e-15</v>
+        <v>-1.595945597898663e-16</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.270205090833757e-13</v>
+        <v>1.392048131767468e-13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.01804066249867e-16</v>
+        <v>7.228375883960858e-16</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.081214343014151e-13</v>
+        <v>5.568200387535624e-13</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.554312234475219e-14</v>
+        <v>6.38378239159465e-16</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="K19" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="Q19" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="S19" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="W19" t="n">
-        <v>8.848925726377748e-16</v>
+        <v>9.499068878775376e-16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.942892454508281e-07</v>
+        <v>1.942892454516672e-07</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.522206922017046e-16</v>
+        <v>-1.66212339507947e-16</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0001659335177280808</v>
+        <v>-0.0001659335177281712</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.265401975707692e-16</v>
+        <v>-2.386681309648071e-16</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="AD19" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="AG19" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>-3.986894838778718e-15</v>
+        <v>-2.437719788167601e-16</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1381800899578367</v>
+        <v>0.1381800899579118</v>
       </c>
       <c r="AK19" t="n">
-        <v>-6.517254395557321e-16</v>
+        <v>-7.130671584808762e-16</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.5527203598313468</v>
+        <v>-0.552720359831647</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1.594530754352647e-14</v>
+        <v>-9.755817814025407e-16</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>3.986894838778718e-15</v>
+        <v>2.437719788167601e-16</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.1381800899578367</v>
+        <v>-0.1381800899579118</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.517254395557321e-16</v>
+        <v>7.130671584808762e-16</v>
       </c>
       <c r="AR19" t="n">
-        <v>-0.5527203598313467</v>
+        <v>-0.552720359831647</v>
       </c>
       <c r="AS19" t="n">
-        <v>-1.594985116670313e-14</v>
+        <v>-9.745940491313308e-16</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.839009265922372e-23</v>
+        <v>2.14003602373681e-22</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.548761582402965e-24</v>
+        <v>2.675045029671012e-23</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.364225980118011e-18</v>
+        <v>2.535942688128119e-17</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.09752316480593e-16</v>
+        <v>5.350090059342024e-15</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.891328783900011e-16</v>
+        <v>-9.570920468951561e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="M20" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0001659335177280807</v>
+        <v>-0.0001659335177281711</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="Q20" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="S20" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="V20" t="n">
-        <v>8.891328783900011e-16</v>
+        <v>9.570920468951561e-16</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0004978005531828473</v>
+        <v>-0.0004978005531833375</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.942892454509541e-07</v>
+        <v>-1.942892454481725e-07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0001659335177280807</v>
+        <v>0.0001659335177281711</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.530921263289087e-16</v>
+        <v>1.678371401407517e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.265442909249824e-16</v>
+        <v>-2.386672411159141e-16</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.891328499999085e-16</v>
+        <v>9.570922608987584e-16</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0001659335177284097</v>
+        <v>0.0001659335177285099</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="AG20" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.364225984971083e-18</v>
+        <v>-2.535942688962734e-17</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.934352843515398e-15</v>
+        <v>1.387778780781446e-16</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-1.274808412077357e-13</v>
+        <v>-1.398438521016052e-13</v>
       </c>
       <c r="AK20" t="n">
-        <v>-7.022919572274855e-16</v>
+        <v>-7.231086389392072e-16</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.099214167321203e-13</v>
+        <v>5.593752593286219e-13</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.568190022283034e-14</v>
+        <v>5.551115123125783e-16</v>
       </c>
       <c r="AN20" t="n">
-        <v>-3.364225984971083e-18</v>
+        <v>2.535942688962734e-17</v>
       </c>
       <c r="AO20" t="n">
-        <v>-3.934352843515398e-15</v>
+        <v>-1.387778780781446e-16</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.274808412077357e-13</v>
+        <v>1.398438521016052e-13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.022919572274855e-16</v>
+        <v>7.231086389392072e-16</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.099253264822925e-13</v>
+        <v>5.593755439316922e-13</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.576516694967722e-14</v>
+        <v>5.551115123125783e-16</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.284779574395323e-14</v>
+        <v>1.284779574395323e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.710505431213761e-12</v>
+        <v>2.710505431213761e-12</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0004978005531846971</v>
+        <v>-0.0004978005531852483</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.94289245450664e-07</v>
+        <v>-1.942892454470259e-07</v>
       </c>
       <c r="M21" t="n">
-        <v>1.530956406052565e-16</v>
+        <v>1.678374041412947e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.264856906194544e-16</v>
+        <v>-2.386905257758072e-16</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.000497800553184697</v>
+        <v>-0.0004978005531852484</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.942892454476922e-07</v>
+        <v>1.942892454436563e-07</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.521497120175572e-16</v>
+        <v>-1.662109234779601e-16</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.265660456427604e-16</v>
+        <v>-2.386757107314472e-16</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0004978005531846971</v>
+        <v>0.0004978005531852483</v>
       </c>
       <c r="W21" t="n">
-        <v>-8.891328499999085e-16</v>
+        <v>-9.570922608987584e-16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.94289245450664e-07</v>
+        <v>1.942892454470259e-07</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.530956406052565e-16</v>
+        <v>-1.678374041412947e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.0001659335177284097</v>
+        <v>-0.0001659335177285099</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.264856906194544e-16</v>
+        <v>2.386905257758072e-16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.000497800553184697</v>
+        <v>0.0004978005531852484</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.848921481134703e-16</v>
+        <v>9.499078417043254e-16</v>
       </c>
       <c r="AD21" t="n">
-        <v>-1.942892454476922e-07</v>
+        <v>-1.942892454436563e-07</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.521497120175572e-16</v>
+        <v>1.662109234779601e-16</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.0001659335177284096</v>
+        <v>-0.0001659335177285098</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.265660456427604e-16</v>
+        <v>2.386757107314472e-16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.973308852973428e-15</v>
+        <v>2.564977690112228e-16</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1381800899581102</v>
+        <v>0.1381800899581928</v>
       </c>
       <c r="AK21" t="n">
-        <v>-6.515814257910062e-16</v>
+        <v>-7.130646993411015e-16</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.5527203598324407</v>
+        <v>-0.552720359832771</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.584863837395873e-14</v>
+        <v>1.034213425664638e-15</v>
       </c>
       <c r="AN21" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="AO21" t="n">
-        <v>-3.973308852973428e-15</v>
+        <v>-2.564977690112228e-16</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.1381800899581102</v>
+        <v>-0.1381800899581928</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.515814257910062e-16</v>
+        <v>7.130646993411015e-16</v>
       </c>
       <c r="AR21" t="n">
-        <v>-0.5527203598324405</v>
+        <v>-0.552720359832771</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.593783244982845e-14</v>
+        <v>1.017768726424953e-15</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.128107672762931e-21</v>
+        <v>1.309926410085742e-21</v>
       </c>
       <c r="G22" t="n">
-        <v>1.410134590953663e-22</v>
+        <v>1.637408012607177e-22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.336807592224073e-16</v>
+        <v>1.552262795951604e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>2.820269181907326e-14</v>
+        <v>3.274816025214354e-14</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="K22" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.513191775452895e-16</v>
+        <v>-1.837675371856052e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="W22" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.513191775452895e-16</v>
+        <v>1.837675371856052e-16</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.004231960428275111</v>
+        <v>0.004231960428276507</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.511978472574226e-16</v>
+        <v>1.84055805033667e-16</v>
       </c>
       <c r="AG22" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="AH22" t="n">
-        <v>-1.336807591937417e-16</v>
+        <v>-1.552262795659536e-16</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.142730437526552e-14</v>
+        <v>4.773959005888173e-15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-1.266629055343862e-13</v>
+        <v>-1.547650896327468e-13</v>
       </c>
       <c r="AK22" t="n">
-        <v>-7.80191883320569e-16</v>
+        <v>-8.387388006347862e-16</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.062255883614868e-13</v>
+        <v>6.190603585309873e-13</v>
       </c>
       <c r="AM22" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.909583602355269e-14</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.336807591937417e-16</v>
+        <v>1.552262795659536e-16</v>
       </c>
       <c r="AO22" t="n">
-        <v>-2.142730437526552e-14</v>
+        <v>-4.773959005888173e-15</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.266629055343862e-13</v>
+        <v>1.547650896327468e-13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.80191883320569e-16</v>
+        <v>8.387388006347862e-16</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.061894774939023e-13</v>
+        <v>6.190603585309873e-13</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.909583602355269e-14</v>
       </c>
     </row>
     <row r="23">
@@ -6922,112 +6922,112 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="K23" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="S23" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="W23" t="n">
-        <v>2.20743100433644e-15</v>
+        <v>2.450537972616156e-15</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.009998736863977717</v>
+        <v>-0.009998736863977715</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.511978472574226e-16</v>
+        <v>-1.84055805033667e-16</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636619</v>
       </c>
       <c r="AA23" t="n">
-        <v>-5.791783144273565e-16</v>
+        <v>-6.213212525553484e-16</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="AD23" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="AG23" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>-2.156674552224533e-14</v>
+        <v>-4.813432388082148e-15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.1422723979854889</v>
+        <v>-0.1422723979853778</v>
       </c>
       <c r="AK23" t="n">
-        <v>-6.483837255540837e-16</v>
+        <v>-7.909706835739527e-16</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.5690895919419561</v>
+        <v>0.5690895919415118</v>
       </c>
       <c r="AM23" t="n">
-        <v>-8.612098424982906e-14</v>
+        <v>-1.942378839985497e-14</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.156674552224533e-14</v>
+        <v>4.813432388082148e-15</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.1422723979854889</v>
+        <v>0.1422723979853778</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.483837255540837e-16</v>
+        <v>7.909706835739527e-16</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5690895919419559</v>
+        <v>0.569089591941512</v>
       </c>
       <c r="AS23" t="n">
-        <v>-8.641297992813301e-14</v>
+        <v>-1.908367070480167e-14</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.497788127626146e-21</v>
+        <v>-1.548538341043327e-21</v>
       </c>
       <c r="G24" t="n">
-        <v>1.872235159532683e-22</v>
+        <v>-1.935672926304159e-22</v>
       </c>
       <c r="H24" t="n">
-        <v>1.774878931236983e-16</v>
+        <v>-1.835017934136342e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.744470319065365e-14</v>
+        <v>-3.871345852608317e-14</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.219799742742411e-15</v>
+        <v>-2.472551192343367e-15</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.001078786440636485</v>
+        <v>-0.001078786440636618</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="S24" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="V24" t="n">
-        <v>2.219799742742411e-15</v>
+        <v>2.472551192343367e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.004231960428275111</v>
+        <v>-0.004231960428276507</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.263136022281428e-06</v>
+        <v>-1.263136022276418e-06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.001078786440636485</v>
+        <v>0.001078786440636618</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.525494836327788e-16</v>
+        <v>1.864890197036802e-16</v>
       </c>
       <c r="AA24" t="n">
-        <v>-5.794413735969998e-16</v>
+        <v>-6.210148402174625e-16</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.219801240530538e-15</v>
+        <v>2.472549643805026e-15</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="AD24" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.00107878644063685</v>
+        <v>0.001078786440637012</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="AG24" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.774878931412836e-16</v>
+        <v>1.83501793410878e-16</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.148281552649678e-14</v>
+        <v>4.884981308350689e-15</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-1.270391248829942e-13</v>
+        <v>-1.554892282637499e-13</v>
       </c>
       <c r="AK24" t="n">
-        <v>-7.784571598445922e-16</v>
+        <v>-8.400398432417688e-16</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.081653015142231e-13</v>
+        <v>6.219577804167375e-13</v>
       </c>
       <c r="AM24" t="n">
-        <v>8.570921750106208e-14</v>
+        <v>1.976196983832779e-14</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.774878931412836e-16</v>
+        <v>-1.83501793410878e-16</v>
       </c>
       <c r="AO24" t="n">
-        <v>-2.148281552649678e-14</v>
+        <v>-4.884981308350689e-15</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.270391248829942e-13</v>
+        <v>1.554892282637499e-13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.784571598445922e-16</v>
+        <v>8.400398432417688e-16</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.081478059699478e-13</v>
+        <v>6.219559372730443e-13</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.615330671091215e-14</v>
+        <v>1.953992523340276e-14</v>
       </c>
     </row>
     <row r="25">
@@ -7200,112 +7200,112 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.263136022280965e-06</v>
+        <v>-1.263136022274133e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>1.525337304621532e-16</v>
+        <v>1.864873098520545e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.789503694433393e-16</v>
+        <v>-6.21179609635003e-16</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.00423196042827995</v>
+        <v>-0.004231960428281523</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.009998736863977724</v>
+        <v>-0.009998736863977731</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.513191775452895e-16</v>
+        <v>-1.837675371856052e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.793042247975463e-16</v>
+        <v>-6.211946864550133e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.219801240530538e-15</v>
+        <v>-2.472549643805026e-15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.263136022280965e-06</v>
+        <v>1.263136022274133e-06</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.525337304621532e-16</v>
+        <v>-1.864873098520545e-16</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.789503694433393e-16</v>
+        <v>6.21179609635003e-16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.00423196042827995</v>
+        <v>0.004231960428281523</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.207429876228768e-15</v>
+        <v>2.450536662689746e-15</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.009998736863977724</v>
+        <v>0.009998736863977731</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.513191775452895e-16</v>
+        <v>1.837675371856052e-16</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.00107878644063685</v>
+        <v>-0.001078786440637012</v>
       </c>
       <c r="AG25" t="n">
-        <v>5.793042247975463e-16</v>
+        <v>6.211946864550133e-16</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.141473676500339e-14</v>
+        <v>4.829631977857021e-15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0.1422723979851855</v>
+        <v>-0.1422723979850524</v>
       </c>
       <c r="AK25" t="n">
-        <v>-6.486090920928102e-16</v>
+        <v>-7.903516927150042e-16</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.5690895919407426</v>
+        <v>0.5690895919402106</v>
       </c>
       <c r="AM25" t="n">
-        <v>8.54625573384283e-14</v>
+        <v>1.931016027632206e-14</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>-2.141473676500339e-14</v>
+        <v>-4.829631977857021e-15</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1422723979851855</v>
+        <v>0.1422723979850524</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.486090920928102e-16</v>
+        <v>7.903516927150042e-16</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.5690895919407422</v>
+        <v>0.5690895919402106</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.585533678159801e-14</v>
+        <v>1.932689554653355e-14</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.239060668061288e-21</v>
+        <v>-1.427057497211222e-20</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.54882583507661e-22</v>
+        <v>-1.783821871514027e-21</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.208286891652626e-16</v>
+        <v>-1.691063134195298e-15</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.309765167015322e-13</v>
+        <v>-3.567643743028054e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="K26" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.957666828069171e-17</v>
+        <v>-1.579633952279717e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="R26" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="V26" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="Z26" t="n">
-        <v>9.957666828069171e-17</v>
+        <v>1.579633952279717e-16</v>
       </c>
       <c r="AA26" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.01113611787349452</v>
+        <v>0.01113611787349708</v>
       </c>
       <c r="AD26" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.957497490218503e-17</v>
+        <v>1.577061380387217e-16</v>
       </c>
       <c r="AG26" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.208286892050575e-16</v>
+        <v>1.691063134224552e-15</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.729550084903167e-14</v>
+        <v>2.509104035652854e-14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-8.408064744864054e-14</v>
+        <v>-1.338928967697939e-13</v>
       </c>
       <c r="AK26" t="n">
-        <v>-4.566659550508945e-16</v>
+        <v>-8.92081547521073e-16</v>
       </c>
       <c r="AL26" t="n">
-        <v>3.361255407452572e-13</v>
+        <v>5.355715870791755e-13</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.891820033961267e-13</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AN26" t="n">
-        <v>-6.208286892050575e-16</v>
+        <v>-1.691063134224552e-15</v>
       </c>
       <c r="AO26" t="n">
-        <v>-4.729550084903167e-14</v>
+        <v>-2.509104035652854e-14</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.408064744864054e-14</v>
+        <v>1.338928967697939e-13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.566659550508945e-16</v>
+        <v>8.92081547521073e-16</v>
       </c>
       <c r="AR26" t="n">
-        <v>3.356314604241669e-13</v>
+        <v>5.346834086594754e-13</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.891820033961267e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.055647319032516e-13</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.336808689942018e-11</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="K27" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="L27" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="M27" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="S27" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.01113611787349452</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="W27" t="n">
-        <v>3.284615749884662e-15</v>
+        <v>3.906442069675949e-15</v>
       </c>
       <c r="X27" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="Y27" t="n">
-        <v>-9.957497490218503e-17</v>
+        <v>-1.577061380387217e-16</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AA27" t="n">
-        <v>-8.795874158562031e-16</v>
+        <v>-1.010596954321602e-15</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="AG27" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>-4.676173038271414e-14</v>
+        <v>-2.428299574909421e-14</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.02251308472698921</v>
+        <v>-0.02251308472689817</v>
       </c>
       <c r="AK27" t="n">
-        <v>-4.275943135957665e-16</v>
+        <v>-6.792060231468612e-16</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.09005233890795705</v>
+        <v>0.09005233890759357</v>
       </c>
       <c r="AM27" t="n">
-        <v>-1.867563777792461e-13</v>
+        <v>-9.683249195355488e-14</v>
       </c>
       <c r="AN27" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>4.676173038271414e-14</v>
+        <v>2.428299574909421e-14</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.02251308472698921</v>
+        <v>0.02251308472689817</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.275943135957665e-16</v>
+        <v>6.792060231468612e-16</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.09005233890795727</v>
+        <v>0.09005233890759312</v>
       </c>
       <c r="AS27" t="n">
-        <v>-1.87337465282466e-13</v>
+        <v>-9.743147403919787e-14</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>2.271685965345289e-21</v>
+        <v>-8.659282406385243e-22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.839607456681611e-22</v>
+        <v>-1.082410300798155e-22</v>
       </c>
       <c r="H28" t="n">
-        <v>2.691947868934167e-16</v>
+        <v>-1.026124965156651e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>5.679214913363221e-14</v>
+        <v>-2.164820601596311e-14</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.304815612337873e-15</v>
+        <v>-3.94714194959858e-15</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="M28" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.001222599374437192</v>
+        <v>-0.001222599374437302</v>
       </c>
       <c r="O28" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="S28" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="U28" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="V28" t="n">
-        <v>3.304815612337873e-15</v>
+        <v>3.94714194959858e-15</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01113611787349453</v>
+        <v>-0.01113611787349708</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.431524584014678e-06</v>
+        <v>-1.431524584008318e-06</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.001222599374437192</v>
+        <v>0.001222599374437302</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.007394783138497e-16</v>
+        <v>1.604804673994475e-16</v>
       </c>
       <c r="AA28" t="n">
-        <v>-8.801109181113563e-16</v>
+        <v>-1.011136577822181e-15</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.304817884023839e-15</v>
+        <v>3.947141083670339e-15</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.001222599374437407</v>
+        <v>0.001222599374437721</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="AG28" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="AH28" t="n">
-        <v>-2.691947868883633e-16</v>
+        <v>1.026124964512247e-16</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.662936703425657e-14</v>
+        <v>2.509104035652854e-14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-8.392083454423743e-14</v>
+        <v>-1.339430682253256e-13</v>
       </c>
       <c r="AK28" t="n">
-        <v>-4.597017211338539e-16</v>
+        <v>-8.946836327350383e-16</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.356551736916173e-13</v>
+        <v>5.357769349706443e-13</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.865174681370263e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.691947868883633e-16</v>
+        <v>-1.026124964512247e-16</v>
       </c>
       <c r="AO28" t="n">
-        <v>-4.662936703425657e-14</v>
+        <v>-2.509104035652854e-14</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.392083454423743e-14</v>
+        <v>1.339430682253256e-13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.597017211338539e-16</v>
+        <v>8.946836327350383e-16</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.357113942420649e-13</v>
+        <v>5.357675024117436e-13</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.865174681370263e-13</v>
+        <v>1.003641614261142e-13</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>4.336808689942018e-11</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.43152458401435e-06</v>
+        <v>-1.431524584004987e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>1.007901242459449e-16</v>
+        <v>1.60471871097023e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="O29" t="n">
-        <v>-8.800237745202832e-16</v>
+        <v>-1.010538406899292e-15</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.01113611787350202</v>
+        <v>-0.01113611787350541</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.009998568475415992</v>
+        <v>-0.009998568475416005</v>
       </c>
       <c r="S29" t="n">
-        <v>-9.957666828069171e-17</v>
+        <v>-1.579633952279717e-16</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="U29" t="n">
-        <v>-8.802264234440092e-16</v>
+        <v>-1.011845584444849e-15</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="W29" t="n">
-        <v>-3.304817884023839e-15</v>
+        <v>-3.947141083670339e-15</v>
       </c>
       <c r="X29" t="n">
-        <v>1.43152458401435e-06</v>
+        <v>1.431524584004987e-06</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.007901242459449e-16</v>
+        <v>-1.60471871097023e-16</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.001222599374437407</v>
+        <v>-0.001222599374437721</v>
       </c>
       <c r="AA29" t="n">
-        <v>8.800237745202832e-16</v>
+        <v>1.010538406899292e-15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01113611787350202</v>
+        <v>0.01113611787350541</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.28462098894533e-15</v>
+        <v>3.906456340250922e-15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009998568475415992</v>
+        <v>0.009998568475416005</v>
       </c>
       <c r="AE29" t="n">
-        <v>9.957666828069171e-17</v>
+        <v>1.579633952279717e-16</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001222599374437406</v>
+        <v>-0.00122259937443772</v>
       </c>
       <c r="AG29" t="n">
-        <v>8.802264234440092e-16</v>
+        <v>1.011845584444849e-15</v>
       </c>
       <c r="AH29" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.699066218428263e-14</v>
+        <v>2.455235447019222e-14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.02251308472681168</v>
+        <v>-0.02251308472655245</v>
       </c>
       <c r="AK29" t="n">
-        <v>-4.277060378933975e-16</v>
+        <v>-6.79736818501431e-16</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.09005233890724629</v>
+        <v>0.09005233890620934</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.878501785844625e-13</v>
+        <v>9.748393434298417e-14</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>-4.699066218428263e-14</v>
+        <v>-2.455235447019222e-14</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.02251308472681168</v>
+        <v>0.02251308472655245</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.277060378933975e-16</v>
+        <v>6.79736818501431e-16</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.09005233890724762</v>
+        <v>0.09005233890621112</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.880751188897983e-13</v>
+        <v>9.893490141855262e-14</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>1.521452776224584e-21</v>
+        <v>5.558909158194926e-21</v>
       </c>
       <c r="G30" t="n">
-        <v>1.90181597028073e-22</v>
+        <v>6.948636447743658e-22</v>
       </c>
       <c r="H30" t="n">
-        <v>1.802921539826132e-16</v>
+        <v>6.587307352460988e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>3.80363194056146e-14</v>
+        <v>1.389727289548732e-13</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191545</v>
       </c>
       <c r="K30" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.180501003454598e-17</v>
+        <v>-8.702157183110913e-17</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190386</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.187830652248113e-17</v>
+        <v>-8.72061823187002e-17</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="V30" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01853807587190909</v>
+        <v>0.01853807587191545</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.180501003454598e-17</v>
+        <v>8.702157183110913e-17</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.01853807587190073</v>
+        <v>0.01853807587190386</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="AF30" t="n">
-        <v>4.187830652248113e-17</v>
+        <v>8.72061823187002e-17</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.802921540148587e-16</v>
+        <v>-6.587307352355628e-16</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.308464613382966e-14</v>
+        <v>8.149037000748649e-14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3.586154729876037e-14</v>
+        <v>-7.549516567451064e-14</v>
       </c>
       <c r="AK30" t="n">
-        <v>-1.071191746415678e-16</v>
+        <v>-6.149594722337781e-16</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.432963679872677e-13</v>
+        <v>3.019806626980426e-13</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.323385845353187e-13</v>
+        <v>3.268496584496461e-13</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.802921540148587e-16</v>
+        <v>6.587307352355628e-16</v>
       </c>
       <c r="AO30" t="n">
-        <v>-3.308464613382966e-14</v>
+        <v>-8.149037000748649e-14</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.586154729876037e-14</v>
+        <v>7.549516567451064e-14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.071191746415678e-16</v>
+        <v>6.149594722337781e-16</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.435960104028153e-13</v>
+        <v>3.019806626980426e-13</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.314504061156185e-13</v>
+        <v>3.25961480029946e-13</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4.111294638065033e-13</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-11</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190386</v>
       </c>
       <c r="K31" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="M31" t="n">
-        <v>-4.187830652248113e-17</v>
+        <v>-8.72061823187002e-17</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="Q31" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="S31" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190386</v>
       </c>
       <c r="W31" t="n">
-        <v>3.845065573465923e-15</v>
+        <v>4.979654261027446e-15</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.009998542574732268</v>
+        <v>-0.009998542574732264</v>
       </c>
       <c r="Y31" t="n">
-        <v>-4.187830652248113e-17</v>
+        <v>-8.72061823187002e-17</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.001244719958365369</v>
+        <v>-0.001244719958365409</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.005467541231768e-15</v>
+        <v>-1.35150778648002e-15</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="AD31" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="AE31" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AI31" t="n">
-        <v>-3.363850098582328e-14</v>
+        <v>-8.302864127521905e-14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.004092308026984459</v>
+        <v>-0.004092308026951263</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.812412399583363e-16</v>
+        <v>-3.781516349833479e-16</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.01636923210793761</v>
+        <v>0.01636923210780461</v>
       </c>
       <c r="AM31" t="n">
-        <v>-1.351703120018463e-13</v>
+        <v>-3.321614858409899e-13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AO31" t="n">
-        <v>3.363850098582328e-14</v>
+        <v>8.302864127521905e-14</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.004092308026984459</v>
+        <v>0.004092308026951263</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.812412399583363e-16</v>
+        <v>3.781516349833479e-16</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.01636923210793872</v>
+        <v>0.01636923210780616</v>
       </c>
       <c r="AS31" t="n">
-        <v>-1.339376958847387e-13</v>
+        <v>-3.320676443607612e-13</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.267053248582775e-21</v>
+        <v>-1.37221141352895e-21</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.583816560728468e-22</v>
+        <v>-1.715264266911187e-22</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.241458099570588e-16</v>
+        <v>-1.626070525031805e-16</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.316763312145694e-13</v>
+        <v>-3.430528533822374e-14</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.870980034180524e-15</v>
+        <v>-5.034197034245217e-15</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="M32" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.001244719958365368</v>
+        <v>-0.001244719958365408</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="Q32" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="S32" t="n">
-        <v>4.277158646686195e-17</v>
+        <v>8.998391004434036e-17</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="U32" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="V32" t="n">
-        <v>3.870980034180524e-15</v>
+        <v>5.034197034245217e-15</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.01853807587190073</v>
+        <v>-0.01853807587190385</v>
       </c>
       <c r="X32" t="n">
-        <v>-1.457425267729539e-06</v>
+        <v>-1.457425267722723e-06</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001244719958365368</v>
+        <v>0.001244719958365408</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.302749958412686e-17</v>
+        <v>8.994593497079611e-17</v>
       </c>
       <c r="AA32" t="n">
-        <v>-1.004357076261401e-15</v>
+        <v>-1.35142324460594e-15</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.870974767127275e-15</v>
+        <v>5.034195662033804e-15</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="AD32" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001244719958365419</v>
+        <v>0.001244719958365699</v>
       </c>
       <c r="AF32" t="n">
-        <v>4.277158646686195e-17</v>
+        <v>8.998391004434036e-17</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.241458099166313e-16</v>
+        <v>1.62607052525906e-16</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.352873534367973e-14</v>
+        <v>8.304468224196171e-14</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3.572678161051504e-14</v>
+        <v>-7.529960270764857e-14</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.101549407245273e-16</v>
+        <v>-6.205973235307027e-16</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.430490993232485e-13</v>
+        <v>3.011773773084481e-13</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.341149413747189e-13</v>
+        <v>3.312905505481467e-13</v>
       </c>
       <c r="AN32" t="n">
-        <v>-6.241458099166313e-16</v>
+        <v>-1.62607052525906e-16</v>
       </c>
       <c r="AO32" t="n">
-        <v>-3.352873534367973e-14</v>
+        <v>-8.304468224196171e-14</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.572678161051504e-14</v>
+        <v>7.529960270764857e-14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.101549407245273e-16</v>
+        <v>6.205973235307027e-16</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.427650451406545e-13</v>
+        <v>3.012195527729578e-13</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.341149413747189e-13</v>
+        <v>3.321787289678468e-13</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.469446951953614e-18</v>
+        <v>-1.040834085586084e-17</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.336808689942018e-19</v>
+        <v>-1.301042606982605e-18</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.111294638065033e-13</v>
+        <v>-1.23338839141951e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>-8.673617379884035e-11</v>
+        <v>-2.602085213965211e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191546</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.457425267729414e-06</v>
+        <v>-1.457425267718843e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>4.277158646686195e-17</v>
+        <v>8.998391004434036e-17</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.004678364397376e-15</v>
+        <v>-1.351124469597434e-15</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.01853807587190909</v>
+        <v>-0.01853807587191545</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.009998542574732278</v>
+        <v>-0.009998542574732292</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.180501003454598e-17</v>
+        <v>-8.702157183110913e-17</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.003618666593276e-15</v>
+        <v>-1.351217823243913e-15</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01853807587190909</v>
+        <v>0.01853807587191546</v>
       </c>
       <c r="W33" t="n">
-        <v>-3.870974767127275e-15</v>
+        <v>-5.034195662033804e-15</v>
       </c>
       <c r="X33" t="n">
-        <v>1.457425267729414e-06</v>
+        <v>1.457425267718843e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>-4.277158646686195e-17</v>
+        <v>-8.998391004434036e-17</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365699</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.004678364397376e-15</v>
+        <v>1.351124469597434e-15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.01853807587190909</v>
+        <v>0.01853807587191545</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.845064052013146e-15</v>
+        <v>4.979648702118288e-15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.009998542574732278</v>
+        <v>0.009998542574732292</v>
       </c>
       <c r="AE33" t="n">
-        <v>4.180501003454598e-17</v>
+        <v>8.702157183110913e-17</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001244719958365419</v>
+        <v>-0.001244719958365697</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.003618666593276e-15</v>
+        <v>1.351217823243913e-15</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.300334953305864e-14</v>
+        <v>8.278430025063367e-14</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.004092308026943159</v>
+        <v>-0.004092308026713454</v>
       </c>
       <c r="AK33" t="n">
-        <v>-1.805385040703131e-16</v>
+        <v>-3.778386247725941e-16</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.0163692321077733</v>
+        <v>0.01636923210685359</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.326015304135093e-13</v>
+        <v>3.310853897287379e-13</v>
       </c>
       <c r="AN33" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="AO33" t="n">
-        <v>-3.300334953305864e-14</v>
+        <v>-8.278430025063367e-14</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.004092308026943159</v>
+        <v>0.004092308026713454</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.805385040703131e-16</v>
+        <v>3.778386247725941e-16</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.01636923210777352</v>
+        <v>0.01636923210685604</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.314252658509586e-13</v>
+        <v>3.311890122763301e-13</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_fab_error.xlsx
+++ b/outputs/validation_frame_fab_error.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0004978005531852484</v>
+        <v>-0.000497800553184697</v>
       </c>
       <c r="F6" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.662109234779601e-16</v>
+        <v>-1.521497120175572e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004978005911003423</v>
+        <v>0.0004978005910997909</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="F7" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004978005910984314</v>
+        <v>0.0004978005910979412</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004978005910984314</v>
+        <v>0.0004978005910979412</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004978005911003422</v>
+        <v>0.000497800591099791</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="F10" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.837675371856052e-16</v>
+        <v>-1.513191775452895e-16</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0108574503425808</v>
+        <v>0.01085745034258018</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="F11" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01085745034257883</v>
+        <v>0.01085745034257829</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004231960616784009</v>
+        <v>0.004231960616782613</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004231960616789025</v>
+        <v>0.004231960616787453</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="F14" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.579633952279717e-16</v>
+        <v>-9.957666828069171e-17</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01496611148061477</v>
+        <v>0.01496611148061224</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="F15" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="G15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01496611148060856</v>
+        <v>0.01496611148060666</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01113611796550682</v>
+        <v>0.01113611796550427</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01113611796551515</v>
+        <v>0.01113611796551176</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01853807587191545</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="F18" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="H18" t="n">
-        <v>-8.702157183110913e-17</v>
+        <v>-4.180501003454598e-17</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02106255232994397</v>
+        <v>0.02106255232993836</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.01853807587190386</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="F19" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.72061823187002e-17</v>
+        <v>-4.187830652248113e-17</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02106255232993375</v>
+        <v>0.021062552329931</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01853807592919373</v>
+        <v>0.01853807592919061</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>8.998391004434036e-17</v>
+        <v>4.277158646686195e-17</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01853807592920534</v>
+        <v>0.01853807592919897</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02106255232994397</v>
+        <v>0.02106255232993836</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01853807587191545</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="E2" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="E5" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-6.929504713093504e-14</v>
+        <v>-1.311312169960388e-13</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.113145175800432e-13</v>
+        <v>-1.056826096416637e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0306977007800977</v>
+        <v>-0.03069770078073537</v>
       </c>
       <c r="E2" t="n">
-        <v>4.569396361138198e-13</v>
+        <v>4.296386158179834e-13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1227908031188893</v>
+        <v>0.1227908031186297</v>
       </c>
       <c r="G2" t="n">
-        <v>6.793077920818111e-16</v>
+        <v>6.448418222140104e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-2.90072761817417e-13</v>
+        <v>-3.441136264825673e-13</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.113132344405785e-13</v>
+        <v>-1.056301890213897e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03069770078136342</v>
+        <v>-0.03069770078123084</v>
       </c>
       <c r="E3" t="n">
-        <v>4.569368345576162e-13</v>
+        <v>4.295338792934306e-13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1227908031179764</v>
+        <v>0.1227908031177474</v>
       </c>
       <c r="G3" t="n">
-        <v>6.792862188998355e-16</v>
+        <v>6.44768254624497e-16</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.900326463370351e-13</v>
+        <v>-3.440719931191438e-13</v>
       </c>
       <c r="C4" t="n">
-        <v>1.118832211966489e-13</v>
+        <v>1.060312698528079e-13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03069770078081126</v>
+        <v>0.03069770078125075</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.598491472941029e-13</v>
+        <v>-4.31381983041816e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1227908031179765</v>
+        <v>0.1227908031177475</v>
       </c>
       <c r="G4" t="n">
-        <v>6.792836862529862e-16</v>
+        <v>6.447799049403346e-16</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-6.938297592712361e-14</v>
+        <v>-1.312283615106935e-13</v>
       </c>
       <c r="C5" t="n">
-        <v>1.118830786238024e-13</v>
+        <v>1.06028662285421e-13</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03069770078063009</v>
+        <v>0.03069770078120492</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.598489149359651e-13</v>
+        <v>-4.313767609041526e-13</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1227908031188891</v>
+        <v>0.1227908031186295</v>
       </c>
       <c r="G5" t="n">
-        <v>6.793499579772974e-16</v>
+        <v>6.4461311945537e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.238154090727605e-08</v>
+        <v>3.23815409079487e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03069770078009769</v>
+        <v>0.03069770078073537</v>
       </c>
       <c r="I2" t="n">
-        <v>6.476308181455209</v>
+        <v>6.476308181589739</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0306977007800977</v>
+        <v>-0.03069770078073537</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.113145175800432e-13</v>
+        <v>-1.056826096416637e-13</v>
       </c>
       <c r="L2" t="n">
-        <v>6.929179452441758e-14</v>
+        <v>1.311312169960388e-13</v>
       </c>
       <c r="M2" t="n">
-        <v>6.793077920818111e-16</v>
+        <v>6.448418222140104e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1227908031188893</v>
+        <v>0.1227908031186297</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.569396361138199e-13</v>
+        <v>-4.296386158179834e-13</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0306977007800977</v>
+        <v>0.03069770078073537</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.113145175800432e-13</v>
+        <v>1.056826096416637e-13</v>
       </c>
       <c r="R2" t="n">
-        <v>-6.929179452441758e-14</v>
+        <v>-1.311312169960388e-13</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.793077920818111e-16</v>
+        <v>-6.448418222140104e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1227908031193052</v>
+        <v>-0.1227908031194165</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.10947469366439e-13</v>
+        <v>-2.044570420319988e-13</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>3.238154090861119e-08</v>
+        <v>3.238154090847134e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03069770078136341</v>
+        <v>0.03069770078123083</v>
       </c>
       <c r="I3" t="n">
-        <v>6.476308181722239</v>
+        <v>6.476308181694269</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03069770078136342</v>
+        <v>-0.03069770078123084</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.113132344405785e-13</v>
+        <v>-1.056301890213897e-13</v>
       </c>
       <c r="L3" t="n">
-        <v>2.900735207589378e-13</v>
+        <v>3.441136264825673e-13</v>
       </c>
       <c r="M3" t="n">
-        <v>6.792862188998355e-16</v>
+        <v>6.44768254624497e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1227908031179764</v>
+        <v>0.1227908031177474</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.569368345576162e-13</v>
+        <v>-4.295338792934306e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03069770078136342</v>
+        <v>0.03069770078123084</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.113132344405785e-13</v>
+        <v>1.056301890213897e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.900735207589378e-13</v>
+        <v>-3.441136264825673e-13</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.792862188998355e-16</v>
+        <v>-6.44768254624497e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1227908031197169</v>
+        <v>-0.1227908031198122</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.109425720858546e-13</v>
+        <v>-2.042472548349078e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.238154090802875e-08</v>
+        <v>-3.238154090849235e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03069770078081126</v>
+        <v>-0.03069770078125074</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.47630818160575</v>
+        <v>-6.476308181698468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03069770078081126</v>
+        <v>0.03069770078125075</v>
       </c>
       <c r="K4" t="n">
-        <v>1.118832211966489e-13</v>
+        <v>1.060312698528079e-13</v>
       </c>
       <c r="L4" t="n">
-        <v>2.900318873955143e-13</v>
+        <v>3.440719931191438e-13</v>
       </c>
       <c r="M4" t="n">
-        <v>6.792836862529862e-16</v>
+        <v>6.447799049403346e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1227908031179765</v>
+        <v>0.1227908031177475</v>
       </c>
       <c r="O4" t="n">
-        <v>4.598491472941029e-13</v>
+        <v>4.31381983041816e-13</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.03069770078081126</v>
+        <v>-0.03069770078125075</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.118832211966489e-13</v>
+        <v>-1.060312698528079e-13</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.900318873955143e-13</v>
+        <v>-3.440719931191438e-13</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.792836862529862e-16</v>
+        <v>-6.447799049403346e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1227908031197167</v>
+        <v>-0.122790803119812</v>
       </c>
       <c r="U4" t="n">
-        <v>2.114501798857903e-13</v>
+        <v>2.048056360750312e-13</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.238154090783764e-08</v>
+        <v>-3.2381540908444e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03069770078063009</v>
+        <v>-0.03069770078120491</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.476308181567529</v>
+        <v>-6.4763081816888</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03069770078063009</v>
+        <v>0.03069770078120492</v>
       </c>
       <c r="K5" t="n">
-        <v>1.118830786238024e-13</v>
+        <v>1.06028662285421e-13</v>
       </c>
       <c r="L5" t="n">
-        <v>6.938893903907228e-14</v>
+        <v>1.312283615106935e-13</v>
       </c>
       <c r="M5" t="n">
-        <v>6.793499579772974e-16</v>
+        <v>6.4461311945537e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1227908031188891</v>
+        <v>0.1227908031186295</v>
       </c>
       <c r="O5" t="n">
-        <v>4.598489149359651e-13</v>
+        <v>4.313767609041526e-13</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03069770078063009</v>
+        <v>-0.03069770078120492</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.118830786238024e-13</v>
+        <v>-1.06028662285421e-13</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.938893903907228e-14</v>
+        <v>-1.312283615106935e-13</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.793499579772974e-16</v>
+        <v>-6.4461311945537e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1227908031193055</v>
+        <v>-0.1227908031194169</v>
       </c>
       <c r="U5" t="n">
-        <v>2.11449556806849e-13</v>
+        <v>2.04795212808373e-13</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009998931153223175</v>
+        <v>-0.009998931153223171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001666488525537196</v>
+        <v>-0.001666488525537195</v>
       </c>
       <c r="H6" t="n">
-        <v>-1579.831122209262</v>
+        <v>-1579.831122209261</v>
       </c>
       <c r="I6" t="n">
-        <v>-333297.7051074391</v>
+        <v>-333297.705107439</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1688777907381791</v>
+        <v>-0.1688777907386338</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.111710482853654e-13</v>
+        <v>-1.016589946586002e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>7.138734048339757e-14</v>
+        <v>1.297850715786808e-13</v>
       </c>
       <c r="M6" t="n">
-        <v>1.088707853982457e-15</v>
+        <v>1.003947125286698e-15</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6755111629520767</v>
+        <v>0.6755111629518569</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.465050389997536e-13</v>
+        <v>-3.043623884663222e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1688777907381791</v>
+        <v>0.1688777907386338</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.111710482853654e-13</v>
+        <v>1.016589946586002e-13</v>
       </c>
       <c r="R6" t="n">
-        <v>-7.138734048339757e-14</v>
+        <v>-1.297850715786808e-13</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.088707853982457e-15</v>
+        <v>-1.003947125286698e-15</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6755111629525059</v>
+        <v>-0.6755111629526356</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.205212507124386e-13</v>
+        <v>-3.055915794852785e-13</v>
       </c>
     </row>
     <row r="7">
@@ -1953,40 +1953,40 @@
         <v>-333297.7051074389</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1688777907395433</v>
+        <v>-0.1688777907390886</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.109572406080648e-13</v>
+        <v>-1.016964272859168e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>2.959854583650667e-13</v>
+        <v>3.533839887381873e-13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.089089653757695e-15</v>
+        <v>1.003662332591825e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6755111629513628</v>
+        <v>0.6755111629511585</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.46075886313227e-13</v>
+        <v>-3.043323765989816e-13</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1688777907395433</v>
+        <v>0.1688777907390886</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.109572406080648e-13</v>
+        <v>1.016964272859168e-13</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.959854583650667e-13</v>
+        <v>-3.533839887381873e-13</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.089089653757695e-15</v>
+        <v>-1.003662332591825e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6755111629531396</v>
+        <v>-0.6755111629532795</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.196675573351616e-13</v>
+        <v>-3.058461871165189e-13</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.068846776828246e-06</v>
+        <v>-1.068846776830474e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.781411294713743e-07</v>
+        <v>-1.781411294717457e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1688777907388628</v>
+        <v>-0.168877790739215</v>
       </c>
       <c r="I8" t="n">
-        <v>-35.62822589427485</v>
+        <v>-35.62822589434915</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1688777907388629</v>
+        <v>0.168877790739215</v>
       </c>
       <c r="K8" t="n">
-        <v>1.116118975923458e-13</v>
+        <v>1.020563685019457e-13</v>
       </c>
       <c r="L8" t="n">
-        <v>2.955413691552167e-13</v>
+        <v>3.534950110406498e-13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.088220089750561e-15</v>
+        <v>1.004399389143434e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6755111629513639</v>
+        <v>0.6755111629511581</v>
       </c>
       <c r="O8" t="n">
-        <v>3.486380836536046e-13</v>
+        <v>3.057675499107009e-13</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1688777907388629</v>
+        <v>-0.168877790739215</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.116118975923458e-13</v>
+        <v>-1.020563685019457e-13</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.955413691552167e-13</v>
+        <v>-3.534950110406498e-13</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.088220089750561e-15</v>
+        <v>-1.004399389143434e-15</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6755111629531383</v>
+        <v>-0.6755111629532804</v>
       </c>
       <c r="U8" t="n">
-        <v>3.210333019004703e-13</v>
+        <v>3.065706611009732e-13</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.068846776827107e-06</v>
+        <v>-1.068846776830301e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.781411294711845e-07</v>
+        <v>-1.781411294717168e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1688777907386829</v>
+        <v>-0.1688777907391875</v>
       </c>
       <c r="I9" t="n">
-        <v>-35.62822589423689</v>
+        <v>-35.62822589434336</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1688777907386829</v>
+        <v>0.1688777907391875</v>
       </c>
       <c r="K9" t="n">
-        <v>1.116125327618011e-13</v>
+        <v>1.020658017410055e-13</v>
       </c>
       <c r="L9" t="n">
-        <v>7.149836278586008e-14</v>
+        <v>1.294520046712933e-13</v>
       </c>
       <c r="M9" t="n">
-        <v>1.088622777137711e-15</v>
+        <v>1.00316870126798e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6755111629520767</v>
+        <v>0.6755111629518573</v>
       </c>
       <c r="O9" t="n">
-        <v>3.486385285113655e-13</v>
+        <v>3.057815917171203e-13</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1688777907386829</v>
+        <v>-0.1688777907391875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.116125327618011e-13</v>
+        <v>-1.020658017410055e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>-7.149836278586008e-14</v>
+        <v>-1.294520046712933e-13</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.088622777137711e-15</v>
+        <v>-1.00316870126798e-15</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6755111629525063</v>
+        <v>-0.6755111629526342</v>
       </c>
       <c r="U9" t="n">
-        <v>3.21036668059441e-13</v>
+        <v>3.06613218728913e-13</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.683885617262404e-07</v>
+        <v>1.683885617314446e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.806476028770673e-08</v>
+        <v>2.806476028857409e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02660539275274598</v>
+        <v>0.02660539275356824</v>
       </c>
       <c r="I10" t="n">
-        <v>5.612952057541346</v>
+        <v>5.612952057714819</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02660539275257179</v>
+        <v>-0.02660539275348128</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.062459638123764e-13</v>
+        <v>-8.004421522552583e-14</v>
       </c>
       <c r="L10" t="n">
-        <v>7.593925488436071e-14</v>
+        <v>1.729727472365994e-13</v>
       </c>
       <c r="M10" t="n">
-        <v>1.111852555817223e-15</v>
+        <v>8.564708730707019e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1064215710122962</v>
+        <v>0.1064215710118925</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.996428263884806e-13</v>
+        <v>-2.018431888207753e-13</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02660539275257179</v>
+        <v>0.02660539275348128</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.062459638123764e-13</v>
+        <v>8.004421522552583e-14</v>
       </c>
       <c r="R10" t="n">
-        <v>-7.593925488436071e-14</v>
+        <v>-1.729727472365994e-13</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.111852555817223e-15</v>
+        <v>-8.564708730707019e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1064215710127527</v>
+        <v>-0.1064215710129304</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.378329564857779e-13</v>
+        <v>-2.784221025323803e-13</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.683885617331793e-07</v>
+        <v>1.68388561734914e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>2.806476028886322e-08</v>
+        <v>2.806476028915234e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02660539275384233</v>
+        <v>0.02660539275411641</v>
       </c>
       <c r="I11" t="n">
-        <v>5.612952057772643</v>
+        <v>5.612952057830467</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.02660539275370866</v>
+        <v>-0.0266053927541634</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.062191727345148e-13</v>
+        <v>-8.013368217045158e-14</v>
       </c>
       <c r="L11" t="n">
-        <v>2.928768338961163e-13</v>
+        <v>3.987921104453562e-13</v>
       </c>
       <c r="M11" t="n">
-        <v>1.107938535796261e-15</v>
+        <v>8.550105194513328e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1064215710116265</v>
+        <v>0.1064215710113263</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.991587646272846e-13</v>
+        <v>-2.022001209684786e-13</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02660539275370866</v>
+        <v>0.0266053927541634</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.062191727345148e-13</v>
+        <v>8.013368217045158e-14</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.928768338961163e-13</v>
+        <v>-3.987921104453562e-13</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.107938535796261e-15</v>
+        <v>-8.550105194513328e-16</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1064215710133851</v>
+        <v>-0.1064215710137209</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.381562717798038e-13</v>
+        <v>-2.786019720542305e-13</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.683885617318994e-07</v>
+        <v>-1.683885617332492e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.80647602886499e-08</v>
+        <v>-2.806476028887486e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02660539275364011</v>
+        <v>-0.02660539275385337</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.61295205772998</v>
+        <v>-5.612952057774971</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0266053927536401</v>
+        <v>0.02660539275385337</v>
       </c>
       <c r="K12" t="n">
-        <v>1.069749663333046e-13</v>
+        <v>8.020341599304231e-14</v>
       </c>
       <c r="L12" t="n">
-        <v>2.928768338961163e-13</v>
+        <v>3.983480212355062e-13</v>
       </c>
       <c r="M12" t="n">
-        <v>1.110346483951892e-15</v>
+        <v>8.557517805408608e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1064215710116274</v>
+        <v>0.1064215710113285</v>
       </c>
       <c r="O12" t="n">
-        <v>3.016785702947814e-13</v>
+        <v>2.022708440431196e-13</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0266053927536401</v>
+        <v>-0.02660539275385337</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.069749663333046e-13</v>
+        <v>-8.020341599304231e-14</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.928768338961163e-13</v>
+        <v>-3.983480212355062e-13</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.110346483951892e-15</v>
+        <v>-8.557517805408608e-16</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1064215710133851</v>
+        <v>-0.1064215710137182</v>
       </c>
       <c r="U12" t="n">
-        <v>3.401712277050454e-13</v>
+        <v>2.789496519151347e-13</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.68388561730854e-07</v>
+        <v>-1.683885617333849e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.806476028847566e-08</v>
+        <v>-2.806476028889748e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02660539275347493</v>
+        <v>-0.02660539275387482</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.612952057695132</v>
+        <v>-5.612952057779497</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02660539275347493</v>
+        <v>0.02660539275387483</v>
       </c>
       <c r="K13" t="n">
-        <v>1.069827612644598e-13</v>
+        <v>8.017778624435488e-14</v>
       </c>
       <c r="L13" t="n">
-        <v>7.749356711883593e-14</v>
+        <v>1.73749903353837e-13</v>
       </c>
       <c r="M13" t="n">
-        <v>1.108175038367591e-15</v>
+        <v>8.569012298343786e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1064215710122927</v>
+        <v>0.106421571011891</v>
       </c>
       <c r="O13" t="n">
-        <v>3.016968591146563e-13</v>
+        <v>2.022430901330703e-13</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.02660539275347493</v>
+        <v>-0.02660539275387483</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.069827612644598e-13</v>
+        <v>-8.017778624435488e-14</v>
       </c>
       <c r="R13" t="n">
-        <v>-7.749356711883593e-14</v>
+        <v>-1.73749903353837e-13</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.108175038367591e-15</v>
+        <v>-8.569012298343786e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1064215710127581</v>
+        <v>-0.1064215710129344</v>
       </c>
       <c r="U13" t="n">
-        <v>3.401997084721029e-13</v>
+        <v>2.788236273330586e-13</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.590068371235987e-08</v>
+        <v>2.59006837140946e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>4.316780618726646e-09</v>
+        <v>4.316780619015766e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00409230802655286</v>
+        <v>0.004092308026826946</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8633561237453291</v>
+        <v>0.8633561238031532</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.00409230802665661</v>
+        <v>-0.004092308026883984</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.343190697023063e-14</v>
+        <v>-3.362018027011895e-14</v>
       </c>
       <c r="L14" t="n">
-        <v>5.151434834260726e-14</v>
+        <v>3.466116282879739e-13</v>
       </c>
       <c r="M14" t="n">
-        <v>9.659056027357996e-16</v>
+        <v>3.51193307424836e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01636923210654651</v>
+        <v>0.01636923210568808</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.977987715970128e-13</v>
+        <v>-5.810951370820892e-14</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00409230802665661</v>
+        <v>0.004092308026883984</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.343190697023063e-14</v>
+        <v>3.362018027011895e-14</v>
       </c>
       <c r="R14" t="n">
-        <v>-5.151434834260726e-14</v>
+        <v>-3.466116282879739e-13</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.659056027357996e-16</v>
+        <v>-3.51193307424836e-16</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01636923210685914</v>
+        <v>-0.01636923210776953</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.027926702243698e-13</v>
+        <v>-1.436115679125046e-13</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>2.590068371756404e-08</v>
+        <v>2.59006837140946e-08</v>
       </c>
       <c r="G15" t="n">
-        <v>4.316780619594007e-09</v>
+        <v>4.316780619015766e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004092308027375119</v>
+        <v>0.004092308026826946</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8633561239188015</v>
+        <v>0.8633561238031532</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.004092308027338731</v>
+        <v>-0.004092308026883984</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.34905568022101e-14</v>
+        <v>-3.35688615624581e-14</v>
       </c>
       <c r="L15" t="n">
-        <v>3.348432642269472e-13</v>
+        <v>3.634870182622763e-13</v>
       </c>
       <c r="M15" t="n">
-        <v>9.702846761431884e-16</v>
+        <v>3.582742029919923e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01636923210579333</v>
+        <v>0.01636923210576091</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.983017031738155e-13</v>
+        <v>-5.801105008639339e-14</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004092308027338731</v>
+        <v>0.004092308026883984</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.34905568022101e-14</v>
+        <v>3.35688615624581e-14</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.348432642269472e-13</v>
+        <v>-3.634870182622763e-13</v>
       </c>
       <c r="S15" t="n">
-        <v>-9.702846761431884e-16</v>
+        <v>-3.582742029919923e-16</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01636923210780417</v>
+        <v>-0.01636923210794006</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.026416376394475e-13</v>
+        <v>-1.434021192883554e-13</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.590068371440567e-08</v>
+        <v>-2.590068371486095e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.316780619067612e-09</v>
+        <v>-4.316780619143492e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.004092308026876096</v>
+        <v>-0.00409230802694803</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8633561238135223</v>
+        <v>-0.8633561238286983</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004092308026876101</v>
+        <v>0.004092308026948044</v>
       </c>
       <c r="K16" t="n">
-        <v>8.282471645885687e-14</v>
+        <v>3.32663270766845e-14</v>
       </c>
       <c r="L16" t="n">
-        <v>3.352873534367973e-13</v>
+        <v>3.629319067499637e-13</v>
       </c>
       <c r="M16" t="n">
-        <v>9.685082054614662e-16</v>
+        <v>3.536236808885884e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01636923210579155</v>
+        <v>0.01636923210576025</v>
       </c>
       <c r="O16" t="n">
-        <v>1.962785953793687e-13</v>
+        <v>5.70921169700583e-14</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.004092308026876101</v>
+        <v>-0.004092308026948044</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.282471645885687e-14</v>
+        <v>-3.32663270766845e-14</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.352873534367973e-13</v>
+        <v>-3.629319067499637e-13</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.685082054614662e-16</v>
+        <v>-3.536236808885884e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01636923210780417</v>
+        <v>-0.01636923210793961</v>
       </c>
       <c r="U16" t="n">
-        <v>3.006697033737733e-13</v>
+        <v>1.425058454900481e-13</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.590068371385616e-08</v>
+        <v>-2.590068371506487e-08</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.316780618976026e-09</v>
+        <v>-4.316780619177479e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.004092308026789272</v>
+        <v>-0.00409230802698025</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8633561237952051</v>
+        <v>-0.8633561238354956</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004092308026789282</v>
+        <v>0.00409230802698024</v>
       </c>
       <c r="K17" t="n">
-        <v>8.280285128504592e-14</v>
+        <v>3.341636523803729e-14</v>
       </c>
       <c r="L17" t="n">
-        <v>5.10702591327572e-14</v>
+        <v>3.465006059855114e-13</v>
       </c>
       <c r="M17" t="n">
-        <v>9.693603322947123e-16</v>
+        <v>3.547861404194171e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01636923210655006</v>
+        <v>0.01636923210568919</v>
       </c>
       <c r="O17" t="n">
-        <v>1.962474626761518e-13</v>
+        <v>5.73153777575905e-14</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.004092308026789282</v>
+        <v>-0.00409230802698024</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.280285128504592e-14</v>
+        <v>-3.341636523803729e-14</v>
       </c>
       <c r="R17" t="n">
-        <v>-5.10702591327572e-14</v>
+        <v>-3.465006059855114e-13</v>
       </c>
       <c r="S17" t="n">
-        <v>-9.693603322947123e-16</v>
+        <v>-3.547861404194171e-16</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01636923210685737</v>
+        <v>-0.01636923210776908</v>
       </c>
       <c r="U17" t="n">
-        <v>3.005696450341222e-13</v>
+        <v>1.431828136706332e-13</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.538267877460151e-22</v>
+        <v>4.245243044716826e-22</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.192283484682519e-22</v>
+        <v>5.306553805896032e-23</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.130284743479028e-16</v>
+        <v>5.030613007989438e-17</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.384566969365038e-14</v>
+        <v>1.061310761179206e-14</v>
       </c>
       <c r="J18" t="n">
-        <v>1.130284743554885e-16</v>
+        <v>-5.030613008684149e-17</v>
       </c>
       <c r="K18" t="n">
-        <v>1.595945597898663e-16</v>
+        <v>3.885780586188048e-15</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.392048131767468e-13</v>
+        <v>-1.270205090833757e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>-7.228375883960858e-16</v>
+        <v>-7.01804066249867e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>5.568184802129394e-13</v>
+        <v>5.0804263836559e-13</v>
       </c>
       <c r="O18" t="n">
-        <v>6.38378239159465e-16</v>
+        <v>1.551536676913656e-14</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.130284743554885e-16</v>
+        <v>5.030613008684149e-17</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.595945597898663e-16</v>
+        <v>-3.885780586188048e-15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.392048131767468e-13</v>
+        <v>1.270205090833757e-13</v>
       </c>
       <c r="S18" t="n">
-        <v>7.228375883960858e-16</v>
+        <v>7.01804066249867e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>5.568200387535624e-13</v>
+        <v>5.081214343014151e-13</v>
       </c>
       <c r="U18" t="n">
-        <v>6.38378239159465e-16</v>
+        <v>1.554312234475219e-14</v>
       </c>
     </row>
     <row r="19">
@@ -2760,37 +2760,37 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.437719788167601e-16</v>
+        <v>-3.986894838778718e-15</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1381800899579118</v>
+        <v>0.1381800899578367</v>
       </c>
       <c r="M19" t="n">
-        <v>-7.130671584808762e-16</v>
+        <v>-6.517254395557321e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.552720359831647</v>
+        <v>-0.5527203598313468</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.755817814025407e-16</v>
+        <v>-1.594530754352647e-14</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.437719788167601e-16</v>
+        <v>3.986894838778718e-15</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1381800899579118</v>
+        <v>-0.1381800899578367</v>
       </c>
       <c r="S19" t="n">
-        <v>7.130671584808762e-16</v>
+        <v>6.517254395557321e-16</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.552720359831647</v>
+        <v>-0.5527203598313467</v>
       </c>
       <c r="U19" t="n">
-        <v>-9.745940491313308e-16</v>
+        <v>-1.594985116670313e-14</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>2.14003602373681e-22</v>
+        <v>-2.839009265922372e-23</v>
       </c>
       <c r="G20" t="n">
-        <v>2.675045029671012e-23</v>
+        <v>-3.548761582402965e-24</v>
       </c>
       <c r="H20" t="n">
-        <v>2.535942688128119e-17</v>
+        <v>-3.364225980118011e-18</v>
       </c>
       <c r="I20" t="n">
-        <v>5.350090059342024e-15</v>
+        <v>-7.09752316480593e-16</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.535942688962734e-17</v>
+        <v>3.364225984971083e-18</v>
       </c>
       <c r="K20" t="n">
-        <v>1.387778780781446e-16</v>
+        <v>3.934352843515398e-15</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.398438521016052e-13</v>
+        <v>-1.274808412077357e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>-7.231086389392072e-16</v>
+        <v>-7.022919572274855e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>5.593752593286219e-13</v>
+        <v>5.099214167321203e-13</v>
       </c>
       <c r="O20" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>1.568190022283034e-14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.535942688962734e-17</v>
+        <v>-3.364225984971083e-18</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.387778780781446e-16</v>
+        <v>-3.934352843515398e-15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.398438521016052e-13</v>
+        <v>1.274808412077357e-13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.231086389392072e-16</v>
+        <v>7.022919572274855e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>5.593755439316922e-13</v>
+        <v>5.099253264822925e-13</v>
       </c>
       <c r="U20" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>1.576516694967722e-14</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="H21" t="n">
-        <v>1.284779574395323e-14</v>
+        <v>-1.284779574395323e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>2.710505431213761e-12</v>
+        <v>-2.710505431213761e-12</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="K21" t="n">
-        <v>2.564977690112228e-16</v>
+        <v>3.973308852973428e-15</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1381800899581928</v>
+        <v>0.1381800899581102</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.130646993411015e-16</v>
+        <v>-6.515814257910062e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.552720359832771</v>
+        <v>-0.5527203598324407</v>
       </c>
       <c r="O21" t="n">
-        <v>1.034213425664638e-15</v>
+        <v>1.584863837395873e-14</v>
       </c>
       <c r="P21" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.564977690112228e-16</v>
+        <v>-3.973308852973428e-15</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.1381800899581928</v>
+        <v>-0.1381800899581102</v>
       </c>
       <c r="S21" t="n">
-        <v>7.130646993411015e-16</v>
+        <v>6.515814257910062e-16</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.552720359832771</v>
+        <v>-0.5527203598324405</v>
       </c>
       <c r="U21" t="n">
-        <v>1.017768726424953e-15</v>
+        <v>1.593783244982845e-14</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.309926410085742e-21</v>
+        <v>1.128107672762931e-21</v>
       </c>
       <c r="G22" t="n">
-        <v>1.637408012607177e-22</v>
+        <v>1.410134590953663e-22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.552262795951604e-16</v>
+        <v>1.336807592224073e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>3.274816025214354e-14</v>
+        <v>2.820269181907326e-14</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.552262795659536e-16</v>
+        <v>-1.336807591937417e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>4.773959005888173e-15</v>
+        <v>2.142730437526552e-14</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.547650896327468e-13</v>
+        <v>-1.266629055343862e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.387388006347862e-16</v>
+        <v>-7.80191883320569e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>6.190603585309873e-13</v>
+        <v>5.062255883614868e-13</v>
       </c>
       <c r="O22" t="n">
-        <v>1.909583602355269e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.552262795659536e-16</v>
+        <v>1.336807591937417e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.773959005888173e-15</v>
+        <v>-2.142730437526552e-14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.547650896327468e-13</v>
+        <v>1.266629055343862e-13</v>
       </c>
       <c r="S22" t="n">
-        <v>8.387388006347862e-16</v>
+        <v>7.80191883320569e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>6.190603585309873e-13</v>
+        <v>5.061894774939023e-13</v>
       </c>
       <c r="U22" t="n">
-        <v>1.909583602355269e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
     </row>
     <row r="23">
@@ -3028,37 +3028,37 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.813432388082148e-15</v>
+        <v>-2.156674552224533e-14</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1422723979853778</v>
+        <v>-0.1422723979854889</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.909706835739527e-16</v>
+        <v>-6.483837255540837e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5690895919415118</v>
+        <v>0.5690895919419561</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.942378839985497e-14</v>
+        <v>-8.612098424982906e-14</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.813432388082148e-15</v>
+        <v>2.156674552224533e-14</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1422723979853778</v>
+        <v>0.1422723979854889</v>
       </c>
       <c r="S23" t="n">
-        <v>7.909706835739527e-16</v>
+        <v>6.483837255540837e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.569089591941512</v>
+        <v>0.5690895919419559</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.908367070480167e-14</v>
+        <v>-8.641297992813301e-14</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.548538341043327e-21</v>
+        <v>1.497788127626146e-21</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.935672926304159e-22</v>
+        <v>1.872235159532683e-22</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.835017934136342e-16</v>
+        <v>1.774878931236983e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.871345852608317e-14</v>
+        <v>3.744470319065365e-14</v>
       </c>
       <c r="J24" t="n">
-        <v>1.83501793410878e-16</v>
+        <v>-1.774878931412836e-16</v>
       </c>
       <c r="K24" t="n">
-        <v>4.884981308350689e-15</v>
+        <v>2.148281552649678e-14</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.554892282637499e-13</v>
+        <v>-1.270391248829942e-13</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.400398432417688e-16</v>
+        <v>-7.784571598445922e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>6.219577804167375e-13</v>
+        <v>5.081653015142231e-13</v>
       </c>
       <c r="O24" t="n">
-        <v>1.976196983832779e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.83501793410878e-16</v>
+        <v>1.774878931412836e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.884981308350689e-15</v>
+        <v>-2.148281552649678e-14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.554892282637499e-13</v>
+        <v>1.270391248829942e-13</v>
       </c>
       <c r="S24" t="n">
-        <v>8.400398432417688e-16</v>
+        <v>7.784571598445922e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>6.219559372730443e-13</v>
+        <v>5.081478059699478e-13</v>
       </c>
       <c r="U24" t="n">
-        <v>1.953992523340276e-14</v>
+        <v>8.615330671091215e-14</v>
       </c>
     </row>
     <row r="25">
@@ -3162,37 +3162,37 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4.829631977857021e-15</v>
+        <v>2.141473676500339e-14</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1422723979850524</v>
+        <v>-0.1422723979851855</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.903516927150042e-16</v>
+        <v>-6.486090920928102e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5690895919402106</v>
+        <v>0.5690895919407426</v>
       </c>
       <c r="O25" t="n">
-        <v>1.931016027632206e-14</v>
+        <v>8.54625573384283e-14</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.829631977857021e-15</v>
+        <v>-2.141473676500339e-14</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1422723979850524</v>
+        <v>0.1422723979851855</v>
       </c>
       <c r="S25" t="n">
-        <v>7.903516927150042e-16</v>
+        <v>6.486090920928102e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5690895919402106</v>
+        <v>0.5690895919407422</v>
       </c>
       <c r="U25" t="n">
-        <v>1.932689554653355e-14</v>
+        <v>8.585533678159801e-14</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.427057497211222e-20</v>
+        <v>-5.239060668061288e-21</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.783821871514027e-21</v>
+        <v>-6.54882583507661e-22</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.691063134195298e-15</v>
+        <v>-6.208286891652626e-16</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.567643743028054e-13</v>
+        <v>-1.309765167015322e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>1.691063134224552e-15</v>
+        <v>6.208286892050575e-16</v>
       </c>
       <c r="K26" t="n">
-        <v>2.509104035652854e-14</v>
+        <v>4.729550084903167e-14</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.338928967697939e-13</v>
+        <v>-8.408064744864054e-14</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.92081547521073e-16</v>
+        <v>-4.566659550508945e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>5.355715870791755e-13</v>
+        <v>3.361255407452572e-13</v>
       </c>
       <c r="O26" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>1.891820033961267e-13</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.691063134224552e-15</v>
+        <v>-6.208286892050575e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.509104035652854e-14</v>
+        <v>-4.729550084903167e-14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.338928967697939e-13</v>
+        <v>8.408064744864054e-14</v>
       </c>
       <c r="S26" t="n">
-        <v>8.92081547521073e-16</v>
+        <v>4.566659550508945e-16</v>
       </c>
       <c r="T26" t="n">
-        <v>5.346834086594754e-13</v>
+        <v>3.356314604241669e-13</v>
       </c>
       <c r="U26" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.891820033961267e-13</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-2.055647319032516e-13</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-4.336808689942018e-11</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.428299574909421e-14</v>
+        <v>-4.676173038271414e-14</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.02251308472689817</v>
+        <v>-0.02251308472698921</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.792060231468612e-16</v>
+        <v>-4.275943135957665e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.09005233890759357</v>
+        <v>0.09005233890795705</v>
       </c>
       <c r="O27" t="n">
-        <v>-9.683249195355488e-14</v>
+        <v>-1.867563777792461e-13</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.428299574909421e-14</v>
+        <v>4.676173038271414e-14</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02251308472689817</v>
+        <v>0.02251308472698921</v>
       </c>
       <c r="S27" t="n">
-        <v>6.792060231468612e-16</v>
+        <v>4.275943135957665e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>0.09005233890759312</v>
+        <v>0.09005233890795727</v>
       </c>
       <c r="U27" t="n">
-        <v>-9.743147403919787e-14</v>
+        <v>-1.87337465282466e-13</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.659282406385243e-22</v>
+        <v>2.271685965345289e-21</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.082410300798155e-22</v>
+        <v>2.839607456681611e-22</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.026124965156651e-16</v>
+        <v>2.691947868934167e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.164820601596311e-14</v>
+        <v>5.679214913363221e-14</v>
       </c>
       <c r="J28" t="n">
-        <v>1.026124964512247e-16</v>
+        <v>-2.691947868883633e-16</v>
       </c>
       <c r="K28" t="n">
-        <v>2.509104035652854e-14</v>
+        <v>4.662936703425657e-14</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.339430682253256e-13</v>
+        <v>-8.392083454423743e-14</v>
       </c>
       <c r="M28" t="n">
-        <v>-8.946836327350383e-16</v>
+        <v>-4.597017211338539e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>5.357769349706443e-13</v>
+        <v>3.356551736916173e-13</v>
       </c>
       <c r="O28" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.865174681370263e-13</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.026124964512247e-16</v>
+        <v>2.691947868883633e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>-2.509104035652854e-14</v>
+        <v>-4.662936703425657e-14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.339430682253256e-13</v>
+        <v>8.392083454423743e-14</v>
       </c>
       <c r="S28" t="n">
-        <v>8.946836327350383e-16</v>
+        <v>4.597017211338539e-16</v>
       </c>
       <c r="T28" t="n">
-        <v>5.357675024117436e-13</v>
+        <v>3.357113942420649e-13</v>
       </c>
       <c r="U28" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.865174681370263e-13</v>
       </c>
     </row>
     <row r="29">
@@ -3427,40 +3427,40 @@
         <v>4.336808689942018e-11</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="K29" t="n">
-        <v>2.455235447019222e-14</v>
+        <v>4.699066218428263e-14</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.02251308472655245</v>
+        <v>-0.02251308472681168</v>
       </c>
       <c r="M29" t="n">
-        <v>-6.79736818501431e-16</v>
+        <v>-4.277060378933975e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>0.09005233890620934</v>
+        <v>0.09005233890724629</v>
       </c>
       <c r="O29" t="n">
-        <v>9.748393434298417e-14</v>
+        <v>1.878501785844625e-13</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.455235447019222e-14</v>
+        <v>-4.699066218428263e-14</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02251308472655245</v>
+        <v>0.02251308472681168</v>
       </c>
       <c r="S29" t="n">
-        <v>6.79736818501431e-16</v>
+        <v>4.277060378933975e-16</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09005233890621112</v>
+        <v>0.09005233890724762</v>
       </c>
       <c r="U29" t="n">
-        <v>9.893490141855262e-14</v>
+        <v>1.880751188897983e-13</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>5.558909158194926e-21</v>
+        <v>1.521452776224584e-21</v>
       </c>
       <c r="G30" t="n">
-        <v>6.948636447743658e-22</v>
+        <v>1.90181597028073e-22</v>
       </c>
       <c r="H30" t="n">
-        <v>6.587307352460988e-16</v>
+        <v>1.802921539826132e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>1.389727289548732e-13</v>
+        <v>3.80363194056146e-14</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.587307352355628e-16</v>
+        <v>-1.802921540148587e-16</v>
       </c>
       <c r="K30" t="n">
-        <v>8.149037000748649e-14</v>
+        <v>3.308464613382966e-14</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.549516567451064e-14</v>
+        <v>-3.586154729876037e-14</v>
       </c>
       <c r="M30" t="n">
-        <v>-6.149594722337781e-16</v>
+        <v>-1.071191746415678e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>3.019806626980426e-13</v>
+        <v>1.432963679872677e-13</v>
       </c>
       <c r="O30" t="n">
-        <v>3.268496584496461e-13</v>
+        <v>1.323385845353187e-13</v>
       </c>
       <c r="P30" t="n">
-        <v>6.587307352355628e-16</v>
+        <v>1.802921540148587e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>-8.149037000748649e-14</v>
+        <v>-3.308464613382966e-14</v>
       </c>
       <c r="R30" t="n">
-        <v>7.549516567451064e-14</v>
+        <v>3.586154729876037e-14</v>
       </c>
       <c r="S30" t="n">
-        <v>6.149594722337781e-16</v>
+        <v>1.071191746415678e-16</v>
       </c>
       <c r="T30" t="n">
-        <v>3.019806626980426e-13</v>
+        <v>1.435960104028153e-13</v>
       </c>
       <c r="U30" t="n">
-        <v>3.25961480029946e-13</v>
+        <v>1.314504061156185e-13</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4.111294638065033e-13</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>8.673617379884035e-11</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.302864127521905e-14</v>
+        <v>-3.363850098582328e-14</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.004092308026951263</v>
+        <v>-0.004092308026984459</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.781516349833479e-16</v>
+        <v>-1.812412399583363e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>0.01636923210780461</v>
+        <v>0.01636923210793761</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.321614858409899e-13</v>
+        <v>-1.351703120018463e-13</v>
       </c>
       <c r="P31" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.302864127521905e-14</v>
+        <v>3.363850098582328e-14</v>
       </c>
       <c r="R31" t="n">
-        <v>0.004092308026951263</v>
+        <v>0.004092308026984459</v>
       </c>
       <c r="S31" t="n">
-        <v>3.781516349833479e-16</v>
+        <v>1.812412399583363e-16</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01636923210780616</v>
+        <v>0.01636923210793872</v>
       </c>
       <c r="U31" t="n">
-        <v>-3.320676443607612e-13</v>
+        <v>-1.339376958847387e-13</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.37221141352895e-21</v>
+        <v>-5.267053248582775e-21</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.715264266911187e-22</v>
+        <v>-6.583816560728468e-22</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.626070525031805e-16</v>
+        <v>-6.241458099570588e-16</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.430528533822374e-14</v>
+        <v>-1.316763312145694e-13</v>
       </c>
       <c r="J32" t="n">
-        <v>1.62607052525906e-16</v>
+        <v>6.241458099166313e-16</v>
       </c>
       <c r="K32" t="n">
-        <v>8.304468224196171e-14</v>
+        <v>3.352873534367973e-14</v>
       </c>
       <c r="L32" t="n">
-        <v>-7.529960270764857e-14</v>
+        <v>-3.572678161051504e-14</v>
       </c>
       <c r="M32" t="n">
-        <v>-6.205973235307027e-16</v>
+        <v>-1.101549407245273e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>3.011773773084481e-13</v>
+        <v>1.430490993232485e-13</v>
       </c>
       <c r="O32" t="n">
-        <v>3.312905505481467e-13</v>
+        <v>1.341149413747189e-13</v>
       </c>
       <c r="P32" t="n">
-        <v>-1.62607052525906e-16</v>
+        <v>-6.241458099166313e-16</v>
       </c>
       <c r="Q32" t="n">
-        <v>-8.304468224196171e-14</v>
+        <v>-3.352873534367973e-14</v>
       </c>
       <c r="R32" t="n">
-        <v>7.529960270764857e-14</v>
+        <v>3.572678161051504e-14</v>
       </c>
       <c r="S32" t="n">
-        <v>6.205973235307027e-16</v>
+        <v>1.101549407245273e-16</v>
       </c>
       <c r="T32" t="n">
-        <v>3.012195527729578e-13</v>
+        <v>1.427650451406545e-13</v>
       </c>
       <c r="U32" t="n">
-        <v>3.321787289678468e-13</v>
+        <v>1.341149413747189e-13</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.040834085586084e-17</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.301042606982605e-18</v>
+        <v>-4.336808689942018e-19</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.23338839141951e-12</v>
+        <v>-4.111294638065033e-13</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.602085213965211e-10</v>
+        <v>-8.673617379884035e-11</v>
       </c>
       <c r="J33" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="K33" t="n">
-        <v>8.278430025063367e-14</v>
+        <v>3.300334953305864e-14</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.004092308026713454</v>
+        <v>-0.004092308026943159</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.778386247725941e-16</v>
+        <v>-1.805385040703131e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01636923210685359</v>
+        <v>0.0163692321077733</v>
       </c>
       <c r="O33" t="n">
-        <v>3.310853897287379e-13</v>
+        <v>1.326015304135093e-13</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="Q33" t="n">
-        <v>-8.278430025063367e-14</v>
+        <v>-3.300334953305864e-14</v>
       </c>
       <c r="R33" t="n">
-        <v>0.004092308026713454</v>
+        <v>0.004092308026943159</v>
       </c>
       <c r="S33" t="n">
-        <v>3.778386247725941e-16</v>
+        <v>1.805385040703131e-16</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01636923210685604</v>
+        <v>0.01636923210777352</v>
       </c>
       <c r="U33" t="n">
-        <v>3.311890122763301e-13</v>
+        <v>1.314252658509586e-13</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.238154090727605e-08</v>
+        <v>3.23815409079487e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03069770078009769</v>
+        <v>0.03069770078073537</v>
       </c>
       <c r="I2" t="n">
-        <v>6.476308181455209</v>
+        <v>6.476308181589739</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0004978005531852484</v>
+        <v>-0.000497800553184697</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.662109234779601e-16</v>
+        <v>-1.521497120175572e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0004978005531852484</v>
+        <v>0.000497800553184697</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.662109234779601e-16</v>
+        <v>1.521497120175572e-16</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.0306977007800977</v>
+        <v>-0.03069770078073537</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.113145175800432e-13</v>
+        <v>-1.056826096416637e-13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.929179452441758e-14</v>
+        <v>1.311312169960388e-13</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.793077920818111e-16</v>
+        <v>6.448418222140104e-16</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1227908031188893</v>
+        <v>0.1227908031186297</v>
       </c>
       <c r="AM2" t="n">
-        <v>-4.569396361138199e-13</v>
+        <v>-4.296386158179834e-13</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0306977007800977</v>
+        <v>0.03069770078073537</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.113145175800432e-13</v>
+        <v>1.056826096416637e-13</v>
       </c>
       <c r="AP2" t="n">
-        <v>-6.929179452441758e-14</v>
+        <v>-1.311312169960388e-13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-6.793077920818111e-16</v>
+        <v>-6.448418222140104e-16</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.1227908031193052</v>
+        <v>-0.1227908031194165</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2.10947469366439e-13</v>
+        <v>-2.044570420319988e-13</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>3.238154090861119e-08</v>
+        <v>3.238154090847134e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03069770078136341</v>
+        <v>0.03069770078123083</v>
       </c>
       <c r="I3" t="n">
-        <v>6.476308181722239</v>
+        <v>6.476308181694269</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0004978005531833375</v>
+        <v>0.0004978005531828473</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.66212339507947e-16</v>
+        <v>1.522206922017046e-16</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.03069770078136342</v>
+        <v>-0.03069770078123084</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.113132344405785e-13</v>
+        <v>-1.056301890213897e-13</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.900735207589378e-13</v>
+        <v>3.441136264825673e-13</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.792862188998355e-16</v>
+        <v>6.44768254624497e-16</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1227908031179764</v>
+        <v>0.1227908031177474</v>
       </c>
       <c r="AM3" t="n">
-        <v>-4.569368345576162e-13</v>
+        <v>-4.295338792934306e-13</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.03069770078136342</v>
+        <v>0.03069770078123084</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.113132344405785e-13</v>
+        <v>1.056301890213897e-13</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2.900735207589378e-13</v>
+        <v>-3.441136264825673e-13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6.792862188998355e-16</v>
+        <v>-6.44768254624497e-16</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.1227908031197169</v>
+        <v>-0.1227908031198122</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2.109425720858546e-13</v>
+        <v>-2.042472548349078e-13</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.238154090802875e-08</v>
+        <v>-3.238154090849235e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03069770078081126</v>
+        <v>-0.03069770078125074</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.47630818160575</v>
+        <v>-6.476308181698468</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="AC4" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004978005531833375</v>
+        <v>0.0004978005531828473</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.678371401407517e-16</v>
+        <v>-1.530921263289087e-16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03069770078081126</v>
+        <v>0.03069770078125075</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.118832211966489e-13</v>
+        <v>1.060312698528079e-13</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.900318873955143e-13</v>
+        <v>3.440719931191438e-13</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.792836862529862e-16</v>
+        <v>6.447799049403346e-16</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1227908031179765</v>
+        <v>0.1227908031177475</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.598491472941029e-13</v>
+        <v>4.31381983041816e-13</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03069770078081126</v>
+        <v>-0.03069770078125075</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.118832211966489e-13</v>
+        <v>-1.060312698528079e-13</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2.900318873955143e-13</v>
+        <v>-3.440719931191438e-13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-6.792836862529862e-16</v>
+        <v>-6.447799049403346e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.1227908031197167</v>
+        <v>-0.122790803119812</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.114501798857903e-13</v>
+        <v>2.048056360750312e-13</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.238154090783764e-08</v>
+        <v>-3.2381540908444e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03069770078063009</v>
+        <v>-0.03069770078120491</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.476308181567529</v>
+        <v>-6.4763081816888</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="Q5" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004978005531852483</v>
+        <v>0.0004978005531846971</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.678374041412947e-16</v>
+        <v>-1.530956406052565e-16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.03069770078063009</v>
+        <v>0.03069770078120492</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.118830786238024e-13</v>
+        <v>1.06028662285421e-13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.938893903907228e-14</v>
+        <v>1.312283615106935e-13</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.793499579772974e-16</v>
+        <v>6.4461311945537e-16</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1227908031188891</v>
+        <v>0.1227908031186295</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.598489149359651e-13</v>
+        <v>4.313767609041526e-13</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03069770078063009</v>
+        <v>-0.03069770078120492</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.118830786238024e-13</v>
+        <v>-1.06028662285421e-13</v>
       </c>
       <c r="AP5" t="n">
-        <v>-6.938893903907228e-14</v>
+        <v>-1.312283615106935e-13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-6.793499579772974e-16</v>
+        <v>-6.4461311945537e-16</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.1227908031193055</v>
+        <v>-0.1227908031194169</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.11449556806849e-13</v>
+        <v>2.04795212808373e-13</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009998931153223175</v>
+        <v>-0.009998931153223171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001666488525537196</v>
+        <v>-0.001666488525537195</v>
       </c>
       <c r="H6" t="n">
-        <v>-1579.831122209262</v>
+        <v>-1579.831122209261</v>
       </c>
       <c r="I6" t="n">
-        <v>-333297.7051074391</v>
+        <v>-333297.705107439</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0004978005531852484</v>
+        <v>-0.000497800553184697</v>
       </c>
       <c r="K6" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.662109234779601e-16</v>
+        <v>-1.521497120175572e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.837675371856052e-16</v>
+        <v>-1.513191775452895e-16</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004978005531852484</v>
+        <v>0.000497800553184697</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.662109234779601e-16</v>
+        <v>1.521497120175572e-16</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="AE6" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.837675371856052e-16</v>
+        <v>1.513191775452895e-16</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.1688777907381791</v>
+        <v>-0.1688777907386338</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.111710482853654e-13</v>
+        <v>-1.016589946586002e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>7.138734048339757e-14</v>
+        <v>1.297850715786808e-13</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.088707853982457e-15</v>
+        <v>1.003947125286698e-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6755111629520767</v>
+        <v>0.6755111629518569</v>
       </c>
       <c r="AM6" t="n">
-        <v>-3.465050389997536e-13</v>
+        <v>-3.043623884663222e-13</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.1688777907381791</v>
+        <v>0.1688777907386338</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.111710482853654e-13</v>
+        <v>1.016589946586002e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>-7.138734048339757e-14</v>
+        <v>-1.297850715786808e-13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.088707853982457e-15</v>
+        <v>-1.003947125286698e-15</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.6755111629525059</v>
+        <v>-0.6755111629526356</v>
       </c>
       <c r="AS6" t="n">
-        <v>-3.205212507124386e-13</v>
+        <v>-3.055915794852785e-13</v>
       </c>
     </row>
     <row r="7">
@@ -4698,112 +4698,112 @@
         <v>-333297.7051074389</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="K7" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0004978005531833375</v>
+        <v>0.0004978005531828473</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66212339507947e-16</v>
+        <v>1.522206922017046e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.004231960428276507</v>
+        <v>0.004231960428275111</v>
       </c>
       <c r="AE7" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.84055805033667e-16</v>
+        <v>1.511978472574226e-16</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1688777907395433</v>
+        <v>-0.1688777907390886</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.109572406080648e-13</v>
+        <v>-1.016964272859168e-13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.959854583650667e-13</v>
+        <v>3.533839887381873e-13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.089089653757695e-15</v>
+        <v>1.003662332591825e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.6755111629513628</v>
+        <v>0.6755111629511585</v>
       </c>
       <c r="AM7" t="n">
-        <v>-3.46075886313227e-13</v>
+        <v>-3.043323765989816e-13</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1688777907395433</v>
+        <v>0.1688777907390886</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.109572406080648e-13</v>
+        <v>1.016964272859168e-13</v>
       </c>
       <c r="AP7" t="n">
-        <v>-2.959854583650667e-13</v>
+        <v>-3.533839887381873e-13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.089089653757695e-15</v>
+        <v>-1.003662332591825e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.6755111629531396</v>
+        <v>-0.6755111629532795</v>
       </c>
       <c r="AS7" t="n">
-        <v>-3.196675573351616e-13</v>
+        <v>-3.058461871165189e-13</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.068846776828246e-06</v>
+        <v>-1.068846776830474e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.781411294713743e-07</v>
+        <v>-1.781411294717457e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1688777907388628</v>
+        <v>-0.168877790739215</v>
       </c>
       <c r="I8" t="n">
-        <v>-35.62822589427485</v>
+        <v>-35.62822589434915</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0004978005531833375</v>
+        <v>0.0004978005531828473</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.678371401407517e-16</v>
+        <v>-1.530921263289087e-16</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004231960428276507</v>
+        <v>0.004231960428275111</v>
       </c>
       <c r="AE8" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.864890197036802e-16</v>
+        <v>-1.525494836327788e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.1688777907388629</v>
+        <v>0.168877790739215</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.116118975923458e-13</v>
+        <v>1.020563685019457e-13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.955413691552167e-13</v>
+        <v>3.534950110406498e-13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.088220089750561e-15</v>
+        <v>1.004399389143434e-15</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6755111629513639</v>
+        <v>0.6755111629511581</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.486380836536046e-13</v>
+        <v>3.057675499107009e-13</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.1688777907388629</v>
+        <v>-0.168877790739215</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1.116118975923458e-13</v>
+        <v>-1.020563685019457e-13</v>
       </c>
       <c r="AP8" t="n">
-        <v>-2.955413691552167e-13</v>
+        <v>-3.534950110406498e-13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.088220089750561e-15</v>
+        <v>-1.004399389143434e-15</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.6755111629531383</v>
+        <v>-0.6755111629532804</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.210333019004703e-13</v>
+        <v>3.065706611009732e-13</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.068846776827107e-06</v>
+        <v>-1.068846776830301e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.781411294711845e-07</v>
+        <v>-1.781411294717168e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1688777907386829</v>
+        <v>-0.1688777907391875</v>
       </c>
       <c r="I9" t="n">
-        <v>-35.62822589423689</v>
+        <v>-35.62822589434336</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0004978005531852483</v>
+        <v>0.0004978005531846971</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.678374041412947e-16</v>
+        <v>-1.530956406052565e-16</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="AE9" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.864873098520545e-16</v>
+        <v>-1.525337304621532e-16</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1688777907386829</v>
+        <v>0.1688777907391875</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.116125327618011e-13</v>
+        <v>1.020658017410055e-13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.149836278586008e-14</v>
+        <v>1.294520046712933e-13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.088622777137711e-15</v>
+        <v>1.00316870126798e-15</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6755111629520767</v>
+        <v>0.6755111629518573</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.486385285113655e-13</v>
+        <v>3.057815917171203e-13</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1688777907386829</v>
+        <v>-0.1688777907391875</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1.116125327618011e-13</v>
+        <v>-1.020658017410055e-13</v>
       </c>
       <c r="AP9" t="n">
-        <v>-7.149836278586008e-14</v>
+        <v>-1.294520046712933e-13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.088622777137711e-15</v>
+        <v>-1.00316870126798e-15</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.6755111629525063</v>
+        <v>-0.6755111629526342</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.21036668059441e-13</v>
+        <v>3.06613218728913e-13</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.683885617262404e-07</v>
+        <v>1.683885617314446e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.806476028770673e-08</v>
+        <v>2.806476028857409e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02660539275274598</v>
+        <v>0.02660539275356824</v>
       </c>
       <c r="I10" t="n">
-        <v>5.612952057541346</v>
+        <v>5.612952057714819</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="K10" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.837675371856052e-16</v>
+        <v>-1.513191775452895e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.579633952279717e-16</v>
+        <v>-9.957666828069171e-17</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="W10" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="Y10" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.837675371856052e-16</v>
+        <v>1.513191775452895e-16</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.579633952279717e-16</v>
+        <v>9.957666828069171e-17</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.02660539275257179</v>
+        <v>-0.02660539275348128</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.062459638123764e-13</v>
+        <v>-8.004421522552583e-14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7.593925488436071e-14</v>
+        <v>1.729727472365994e-13</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.111852555817223e-15</v>
+        <v>8.564708730707019e-16</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1064215710122962</v>
+        <v>0.1064215710118925</v>
       </c>
       <c r="AM10" t="n">
-        <v>-2.996428263884806e-13</v>
+        <v>-2.018431888207753e-13</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02660539275257179</v>
+        <v>0.02660539275348128</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.062459638123764e-13</v>
+        <v>8.004421522552583e-14</v>
       </c>
       <c r="AP10" t="n">
-        <v>-7.593925488436071e-14</v>
+        <v>-1.729727472365994e-13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.111852555817223e-15</v>
+        <v>-8.564708730707019e-16</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1064215710127527</v>
+        <v>-0.1064215710129304</v>
       </c>
       <c r="AS10" t="n">
-        <v>-3.378329564857779e-13</v>
+        <v>-2.784221025323803e-13</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.683885617331793e-07</v>
+        <v>1.68388561734914e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>2.806476028886322e-08</v>
+        <v>2.806476028915234e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02660539275384233</v>
+        <v>0.02660539275411641</v>
       </c>
       <c r="I11" t="n">
-        <v>5.612952057772643</v>
+        <v>5.612952057830467</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="K11" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="R11" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="W11" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004231960428276507</v>
+        <v>0.004231960428275111</v>
       </c>
       <c r="Y11" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.84055805033667e-16</v>
+        <v>1.511978472574226e-16</v>
       </c>
       <c r="AB11" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01113611787349708</v>
+        <v>0.01113611787349452</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.577061380387217e-16</v>
+        <v>9.957497490218503e-17</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.02660539275370866</v>
+        <v>-0.0266053927541634</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.062191727345148e-13</v>
+        <v>-8.013368217045158e-14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.928768338961163e-13</v>
+        <v>3.987921104453562e-13</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.107938535796261e-15</v>
+        <v>8.550105194513328e-16</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1064215710116265</v>
+        <v>0.1064215710113263</v>
       </c>
       <c r="AM11" t="n">
-        <v>-2.991587646272846e-13</v>
+        <v>-2.022001209684786e-13</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.02660539275370866</v>
+        <v>0.0266053927541634</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.062191727345148e-13</v>
+        <v>8.013368217045158e-14</v>
       </c>
       <c r="AP11" t="n">
-        <v>-2.928768338961163e-13</v>
+        <v>-3.987921104453562e-13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.107938535796261e-15</v>
+        <v>-8.550105194513328e-16</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.1064215710133851</v>
+        <v>-0.1064215710137209</v>
       </c>
       <c r="AS11" t="n">
-        <v>-3.381562717798038e-13</v>
+        <v>-2.786019720542305e-13</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.683885617318994e-07</v>
+        <v>-1.683885617332492e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.80647602886499e-08</v>
+        <v>-2.806476028887486e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02660539275364011</v>
+        <v>-0.02660539275385337</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.61295205772998</v>
+        <v>-5.612952057774971</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004231960428276507</v>
+        <v>0.004231960428275111</v>
       </c>
       <c r="Y12" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.864890197036802e-16</v>
+        <v>-1.525494836327788e-16</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="AC12" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01113611787349708</v>
+        <v>0.01113611787349453</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.604804673994475e-16</v>
+        <v>-1.007394783138497e-16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0266053927536401</v>
+        <v>0.02660539275385337</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.069749663333046e-13</v>
+        <v>8.020341599304231e-14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.928768338961163e-13</v>
+        <v>3.983480212355062e-13</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.110346483951892e-15</v>
+        <v>8.557517805408608e-16</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1064215710116274</v>
+        <v>0.1064215710113285</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.016785702947814e-13</v>
+        <v>2.022708440431196e-13</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0266053927536401</v>
+        <v>-0.02660539275385337</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1.069749663333046e-13</v>
+        <v>-8.020341599304231e-14</v>
       </c>
       <c r="AP12" t="n">
-        <v>-2.928768338961163e-13</v>
+        <v>-3.983480212355062e-13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.110346483951892e-15</v>
+        <v>-8.557517805408608e-16</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.1064215710133851</v>
+        <v>-0.1064215710137182</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.401712277050454e-13</v>
+        <v>2.789496519151347e-13</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.68388561730854e-07</v>
+        <v>-1.683885617333849e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.806476028847566e-08</v>
+        <v>-2.806476028889748e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02660539275347493</v>
+        <v>-0.02660539275387482</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.612952057695132</v>
+        <v>-5.612952057779497</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="X13" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="Y13" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.864873098520545e-16</v>
+        <v>-1.525337304621532e-16</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="AC13" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.60471871097023e-16</v>
+        <v>-1.007901242459449e-16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.02660539275347493</v>
+        <v>0.02660539275387483</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.069827612644598e-13</v>
+        <v>8.017778624435488e-14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.749356711883593e-14</v>
+        <v>1.73749903353837e-13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.108175038367591e-15</v>
+        <v>8.569012298343786e-16</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1064215710122927</v>
+        <v>0.106421571011891</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.016968591146563e-13</v>
+        <v>2.022430901330703e-13</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.02660539275347493</v>
+        <v>-0.02660539275387483</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1.069827612644598e-13</v>
+        <v>-8.017778624435488e-14</v>
       </c>
       <c r="AP13" t="n">
-        <v>-7.749356711883593e-14</v>
+        <v>-1.73749903353837e-13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.108175038367591e-15</v>
+        <v>-8.569012298343786e-16</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.1064215710127581</v>
+        <v>-0.1064215710129344</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.401997084721029e-13</v>
+        <v>2.788236273330586e-13</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.590068371235987e-08</v>
+        <v>2.59006837140946e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>4.316780618726646e-09</v>
+        <v>4.316780619015766e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00409230802655286</v>
+        <v>0.004092308026826946</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8633561237453291</v>
+        <v>0.8633561238031532</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="K14" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.579633952279717e-16</v>
+        <v>-9.957666828069171e-17</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.01853807587191545</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.702157183110913e-17</v>
+        <v>-4.180501003454598e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="W14" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.579633952279717e-16</v>
+        <v>9.957666828069171e-17</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01853807587191545</v>
+        <v>0.01853807587190909</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="AG14" t="n">
-        <v>8.702157183110913e-17</v>
+        <v>4.180501003454598e-17</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.00409230802665661</v>
+        <v>-0.004092308026883984</v>
       </c>
       <c r="AI14" t="n">
-        <v>-8.343190697023063e-14</v>
+        <v>-3.362018027011895e-14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5.151434834260726e-14</v>
+        <v>3.466116282879739e-13</v>
       </c>
       <c r="AK14" t="n">
-        <v>9.659056027357996e-16</v>
+        <v>3.51193307424836e-16</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01636923210654651</v>
+        <v>0.01636923210568808</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1.977987715970128e-13</v>
+        <v>-5.810951370820892e-14</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.00409230802665661</v>
+        <v>0.004092308026883984</v>
       </c>
       <c r="AO14" t="n">
-        <v>8.343190697023063e-14</v>
+        <v>3.362018027011895e-14</v>
       </c>
       <c r="AP14" t="n">
-        <v>-5.151434834260726e-14</v>
+        <v>-3.466116282879739e-13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-9.659056027357996e-16</v>
+        <v>-3.51193307424836e-16</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.01636923210685914</v>
+        <v>-0.01636923210776953</v>
       </c>
       <c r="AS14" t="n">
-        <v>-3.027926702243698e-13</v>
+        <v>-1.436115679125046e-13</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>2.590068371756404e-08</v>
+        <v>2.59006837140946e-08</v>
       </c>
       <c r="G15" t="n">
-        <v>4.316780619594007e-09</v>
+        <v>4.316780619015766e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004092308027375119</v>
+        <v>0.004092308026826946</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8633561239188015</v>
+        <v>0.8633561238031532</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="K15" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="L15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.01853807587190386</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.72061823187002e-17</v>
+        <v>-4.187830652248113e-17</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="V15" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="W15" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01113611787349708</v>
+        <v>0.01113611787349452</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.577061380387217e-16</v>
+        <v>9.957497490218503e-17</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01853807587190386</v>
+        <v>0.01853807587190073</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="AG15" t="n">
-        <v>8.72061823187002e-17</v>
+        <v>4.187830652248113e-17</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.004092308027338731</v>
+        <v>-0.004092308026883984</v>
       </c>
       <c r="AI15" t="n">
-        <v>-8.34905568022101e-14</v>
+        <v>-3.35688615624581e-14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.348432642269472e-13</v>
+        <v>3.634870182622763e-13</v>
       </c>
       <c r="AK15" t="n">
-        <v>9.702846761431884e-16</v>
+        <v>3.582742029919923e-16</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01636923210579333</v>
+        <v>0.01636923210576091</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1.983017031738155e-13</v>
+        <v>-5.801105008639339e-14</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.004092308027338731</v>
+        <v>0.004092308026883984</v>
       </c>
       <c r="AO15" t="n">
-        <v>8.34905568022101e-14</v>
+        <v>3.35688615624581e-14</v>
       </c>
       <c r="AP15" t="n">
-        <v>-3.348432642269472e-13</v>
+        <v>-3.634870182622763e-13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-9.702846761431884e-16</v>
+        <v>-3.582742029919923e-16</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.01636923210780417</v>
+        <v>-0.01636923210794006</v>
       </c>
       <c r="AS15" t="n">
-        <v>-3.026416376394475e-13</v>
+        <v>-1.434021192883554e-13</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.590068371440567e-08</v>
+        <v>-2.590068371486095e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.316780619067612e-09</v>
+        <v>-4.316780619143492e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.004092308026876096</v>
+        <v>-0.00409230802694803</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8633561238135223</v>
+        <v>-0.8633561238286983</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01113611787349708</v>
+        <v>0.01113611787349453</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.604804673994475e-16</v>
+        <v>-1.007394783138497e-16</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.01853807587190385</v>
+        <v>0.01853807587190073</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="AG16" t="n">
-        <v>-8.994593497079611e-17</v>
+        <v>-4.302749958412686e-17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.004092308026876101</v>
+        <v>0.004092308026948044</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.282471645885687e-14</v>
+        <v>3.32663270766845e-14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.352873534367973e-13</v>
+        <v>3.629319067499637e-13</v>
       </c>
       <c r="AK16" t="n">
-        <v>9.685082054614662e-16</v>
+        <v>3.536236808885884e-16</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01636923210579155</v>
+        <v>0.01636923210576025</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.962785953793687e-13</v>
+        <v>5.70921169700583e-14</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.004092308026876101</v>
+        <v>-0.004092308026948044</v>
       </c>
       <c r="AO16" t="n">
-        <v>-8.282471645885687e-14</v>
+        <v>-3.32663270766845e-14</v>
       </c>
       <c r="AP16" t="n">
-        <v>-3.352873534367973e-13</v>
+        <v>-3.629319067499637e-13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-9.685082054614662e-16</v>
+        <v>-3.536236808885884e-16</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.01636923210780417</v>
+        <v>-0.01636923210793961</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.006697033737733e-13</v>
+        <v>1.425058454900481e-13</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.590068371385616e-08</v>
+        <v>-2.590068371506487e-08</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.316780618976026e-09</v>
+        <v>-4.316780619177479e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.004092308026789272</v>
+        <v>-0.00409230802698025</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8633561237952051</v>
+        <v>-0.8633561238354956</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="S17" t="n">
-        <v>8.998391004434036e-17</v>
+        <v>4.277158646686195e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="W17" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.60471871097023e-16</v>
+        <v>-1.007901242459449e-16</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01853807587191546</v>
+        <v>0.01853807587190909</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="AG17" t="n">
-        <v>-8.998391004434036e-17</v>
+        <v>-4.277158646686195e-17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.004092308026789282</v>
+        <v>0.00409230802698024</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.280285128504592e-14</v>
+        <v>3.341636523803729e-14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5.10702591327572e-14</v>
+        <v>3.465006059855114e-13</v>
       </c>
       <c r="AK17" t="n">
-        <v>9.693603322947123e-16</v>
+        <v>3.547861404194171e-16</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01636923210655006</v>
+        <v>0.01636923210568919</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.962474626761518e-13</v>
+        <v>5.73153777575905e-14</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.004092308026789282</v>
+        <v>-0.00409230802698024</v>
       </c>
       <c r="AO17" t="n">
-        <v>-8.280285128504592e-14</v>
+        <v>-3.341636523803729e-14</v>
       </c>
       <c r="AP17" t="n">
-        <v>-5.10702591327572e-14</v>
+        <v>-3.465006059855114e-13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-9.693603322947123e-16</v>
+        <v>-3.547861404194171e-16</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.01636923210685737</v>
+        <v>-0.01636923210776908</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.005696450341222e-13</v>
+        <v>1.431828136706332e-13</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.538267877460151e-22</v>
+        <v>4.245243044716826e-22</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.192283484682519e-22</v>
+        <v>5.306553805896032e-23</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.130284743479028e-16</v>
+        <v>5.030613007989438e-17</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.384566969365038e-14</v>
+        <v>1.061310761179206e-14</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0004978005531852484</v>
+        <v>-0.000497800553184697</v>
       </c>
       <c r="K18" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.662109234779601e-16</v>
+        <v>-1.521497120175572e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="V18" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0004978005531852484</v>
+        <v>0.000497800553184697</v>
       </c>
       <c r="X18" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.662109234779601e-16</v>
+        <v>1.521497120175572e-16</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0004978005531833375</v>
+        <v>0.0004978005531828473</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66212339507947e-16</v>
+        <v>1.522206922017046e-16</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.130284743554885e-16</v>
+        <v>-5.030613008684149e-17</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.595945597898663e-16</v>
+        <v>3.885780586188048e-15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-1.392048131767468e-13</v>
+        <v>-1.270205090833757e-13</v>
       </c>
       <c r="AK18" t="n">
-        <v>-7.228375883960858e-16</v>
+        <v>-7.01804066249867e-16</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.568184802129394e-13</v>
+        <v>5.0804263836559e-13</v>
       </c>
       <c r="AM18" t="n">
-        <v>6.38378239159465e-16</v>
+        <v>1.551536676913656e-14</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1.130284743554885e-16</v>
+        <v>5.030613008684149e-17</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1.595945597898663e-16</v>
+        <v>-3.885780586188048e-15</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.392048131767468e-13</v>
+        <v>1.270205090833757e-13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.228375883960858e-16</v>
+        <v>7.01804066249867e-16</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.568200387535624e-13</v>
+        <v>5.081214343014151e-13</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.38378239159465e-16</v>
+        <v>1.554312234475219e-14</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="K19" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="Q19" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="S19" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="W19" t="n">
-        <v>9.499068878775376e-16</v>
+        <v>8.848925726377748e-16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.942892454516672e-07</v>
+        <v>1.942892454508281e-07</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.66212339507947e-16</v>
+        <v>-1.522206922017046e-16</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0001659335177281712</v>
+        <v>-0.0001659335177280808</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.386681309648071e-16</v>
+        <v>-2.265401975707692e-16</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="AD19" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="AG19" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>-2.437719788167601e-16</v>
+        <v>-3.986894838778718e-15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1381800899579118</v>
+        <v>0.1381800899578367</v>
       </c>
       <c r="AK19" t="n">
-        <v>-7.130671584808762e-16</v>
+        <v>-6.517254395557321e-16</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.552720359831647</v>
+        <v>-0.5527203598313468</v>
       </c>
       <c r="AM19" t="n">
-        <v>-9.755817814025407e-16</v>
+        <v>-1.594530754352647e-14</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.437719788167601e-16</v>
+        <v>3.986894838778718e-15</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.1381800899579118</v>
+        <v>-0.1381800899578367</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.130671584808762e-16</v>
+        <v>6.517254395557321e-16</v>
       </c>
       <c r="AR19" t="n">
-        <v>-0.552720359831647</v>
+        <v>-0.5527203598313467</v>
       </c>
       <c r="AS19" t="n">
-        <v>-9.745940491313308e-16</v>
+        <v>-1.594985116670313e-14</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>2.14003602373681e-22</v>
+        <v>-2.839009265922372e-23</v>
       </c>
       <c r="G20" t="n">
-        <v>2.675045029671012e-23</v>
+        <v>-3.548761582402965e-24</v>
       </c>
       <c r="H20" t="n">
-        <v>2.535942688128119e-17</v>
+        <v>-3.364225980118011e-18</v>
       </c>
       <c r="I20" t="n">
-        <v>5.350090059342024e-15</v>
+        <v>-7.09752316480593e-16</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.570920468951561e-16</v>
+        <v>-8.891328783900011e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="M20" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0001659335177281711</v>
+        <v>-0.0001659335177280807</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="Q20" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="S20" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="V20" t="n">
-        <v>9.570920468951561e-16</v>
+        <v>8.891328783900011e-16</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0004978005531833375</v>
+        <v>-0.0004978005531828473</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.942892454481725e-07</v>
+        <v>-1.942892454509541e-07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0001659335177281711</v>
+        <v>0.0001659335177280807</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.678371401407517e-16</v>
+        <v>1.530921263289087e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.386672411159141e-16</v>
+        <v>-2.265442909249824e-16</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.570922608987584e-16</v>
+        <v>8.891328499999085e-16</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0001659335177285099</v>
+        <v>0.0001659335177284097</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="AG20" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.535942688962734e-17</v>
+        <v>3.364225984971083e-18</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.387778780781446e-16</v>
+        <v>3.934352843515398e-15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-1.398438521016052e-13</v>
+        <v>-1.274808412077357e-13</v>
       </c>
       <c r="AK20" t="n">
-        <v>-7.231086389392072e-16</v>
+        <v>-7.022919572274855e-16</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.593752593286219e-13</v>
+        <v>5.099214167321203e-13</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>1.568190022283034e-14</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.535942688962734e-17</v>
+        <v>-3.364225984971083e-18</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1.387778780781446e-16</v>
+        <v>-3.934352843515398e-15</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.398438521016052e-13</v>
+        <v>1.274808412077357e-13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.231086389392072e-16</v>
+        <v>7.022919572274855e-16</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.593755439316922e-13</v>
+        <v>5.099253264822925e-13</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>1.576516694967722e-14</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="H21" t="n">
-        <v>1.284779574395323e-14</v>
+        <v>-1.284779574395323e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>2.710505431213761e-12</v>
+        <v>-2.710505431213761e-12</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0004978005531852483</v>
+        <v>-0.0004978005531846971</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.942892454470259e-07</v>
+        <v>-1.94289245450664e-07</v>
       </c>
       <c r="M21" t="n">
-        <v>1.678374041412947e-16</v>
+        <v>1.530956406052565e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.386905257758072e-16</v>
+        <v>-2.264856906194544e-16</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.0004978005531852484</v>
+        <v>-0.000497800553184697</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.942892454436563e-07</v>
+        <v>1.942892454476922e-07</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.662109234779601e-16</v>
+        <v>-1.521497120175572e-16</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.386757107314472e-16</v>
+        <v>-2.265660456427604e-16</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0004978005531852483</v>
+        <v>0.0004978005531846971</v>
       </c>
       <c r="W21" t="n">
-        <v>-9.570922608987584e-16</v>
+        <v>-8.891328499999085e-16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.942892454470259e-07</v>
+        <v>1.94289245450664e-07</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.678374041412947e-16</v>
+        <v>-1.530956406052565e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.0001659335177285099</v>
+        <v>-0.0001659335177284097</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.386905257758072e-16</v>
+        <v>2.264856906194544e-16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.0004978005531852484</v>
+        <v>0.000497800553184697</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.499078417043254e-16</v>
+        <v>8.848921481134703e-16</v>
       </c>
       <c r="AD21" t="n">
-        <v>-1.942892454436563e-07</v>
+        <v>-1.942892454476922e-07</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.662109234779601e-16</v>
+        <v>1.521497120175572e-16</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.0001659335177285098</v>
+        <v>-0.0001659335177284096</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.386757107314472e-16</v>
+        <v>2.265660456427604e-16</v>
       </c>
       <c r="AH21" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.564977690112228e-16</v>
+        <v>3.973308852973428e-15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1381800899581928</v>
+        <v>0.1381800899581102</v>
       </c>
       <c r="AK21" t="n">
-        <v>-7.130646993411015e-16</v>
+        <v>-6.515814257910062e-16</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.552720359832771</v>
+        <v>-0.5527203598324407</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.034213425664638e-15</v>
+        <v>1.584863837395873e-14</v>
       </c>
       <c r="AN21" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AO21" t="n">
-        <v>-2.564977690112228e-16</v>
+        <v>-3.973308852973428e-15</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.1381800899581928</v>
+        <v>-0.1381800899581102</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.130646993411015e-16</v>
+        <v>6.515814257910062e-16</v>
       </c>
       <c r="AR21" t="n">
-        <v>-0.552720359832771</v>
+        <v>-0.5527203598324405</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.017768726424953e-15</v>
+        <v>1.593783244982845e-14</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.309926410085742e-21</v>
+        <v>1.128107672762931e-21</v>
       </c>
       <c r="G22" t="n">
-        <v>1.637408012607177e-22</v>
+        <v>1.410134590953663e-22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.552262795951604e-16</v>
+        <v>1.336807592224073e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>3.274816025214354e-14</v>
+        <v>2.820269181907326e-14</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="K22" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.837675371856052e-16</v>
+        <v>-1.513191775452895e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="W22" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.837675371856052e-16</v>
+        <v>1.513191775452895e-16</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.004231960428276507</v>
+        <v>0.004231960428275111</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84055805033667e-16</v>
+        <v>1.511978472574226e-16</v>
       </c>
       <c r="AG22" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="AH22" t="n">
-        <v>-1.552262795659536e-16</v>
+        <v>-1.336807591937417e-16</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.773959005888173e-15</v>
+        <v>2.142730437526552e-14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-1.547650896327468e-13</v>
+        <v>-1.266629055343862e-13</v>
       </c>
       <c r="AK22" t="n">
-        <v>-8.387388006347862e-16</v>
+        <v>-7.80191883320569e-16</v>
       </c>
       <c r="AL22" t="n">
-        <v>6.190603585309873e-13</v>
+        <v>5.062255883614868e-13</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.909583602355269e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.552262795659536e-16</v>
+        <v>1.336807591937417e-16</v>
       </c>
       <c r="AO22" t="n">
-        <v>-4.773959005888173e-15</v>
+        <v>-2.142730437526552e-14</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.547650896327468e-13</v>
+        <v>1.266629055343862e-13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.387388006347862e-16</v>
+        <v>7.80191883320569e-16</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.190603585309873e-13</v>
+        <v>5.061894774939023e-13</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.909583602355269e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
     </row>
     <row r="23">
@@ -6922,112 +6922,112 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="K23" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="S23" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="W23" t="n">
-        <v>2.450537972616156e-15</v>
+        <v>2.20743100433644e-15</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.009998736863977715</v>
+        <v>-0.009998736863977717</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.84055805033667e-16</v>
+        <v>-1.511978472574226e-16</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.001078786440636619</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.213212525553484e-16</v>
+        <v>-5.791783144273565e-16</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="AD23" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="AG23" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>-4.813432388082148e-15</v>
+        <v>-2.156674552224533e-14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.1422723979853778</v>
+        <v>-0.1422723979854889</v>
       </c>
       <c r="AK23" t="n">
-        <v>-7.909706835739527e-16</v>
+        <v>-6.483837255540837e-16</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.5690895919415118</v>
+        <v>0.5690895919419561</v>
       </c>
       <c r="AM23" t="n">
-        <v>-1.942378839985497e-14</v>
+        <v>-8.612098424982906e-14</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>4.813432388082148e-15</v>
+        <v>2.156674552224533e-14</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.1422723979853778</v>
+        <v>0.1422723979854889</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.909706835739527e-16</v>
+        <v>6.483837255540837e-16</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.569089591941512</v>
+        <v>0.5690895919419559</v>
       </c>
       <c r="AS23" t="n">
-        <v>-1.908367070480167e-14</v>
+        <v>-8.641297992813301e-14</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.548538341043327e-21</v>
+        <v>1.497788127626146e-21</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.935672926304159e-22</v>
+        <v>1.872235159532683e-22</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.835017934136342e-16</v>
+        <v>1.774878931236983e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.871345852608317e-14</v>
+        <v>3.744470319065365e-14</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.472551192343367e-15</v>
+        <v>-2.219799742742411e-15</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.001078786440636618</v>
+        <v>-0.001078786440636485</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="S24" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="V24" t="n">
-        <v>2.472551192343367e-15</v>
+        <v>2.219799742742411e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.004231960428276507</v>
+        <v>-0.004231960428275111</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.263136022276418e-06</v>
+        <v>-1.263136022281428e-06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.001078786440636618</v>
+        <v>0.001078786440636485</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.864890197036802e-16</v>
+        <v>1.525494836327788e-16</v>
       </c>
       <c r="AA24" t="n">
-        <v>-6.210148402174625e-16</v>
+        <v>-5.794413735969998e-16</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.472549643805026e-15</v>
+        <v>2.219801240530538e-15</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="AD24" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.001078786440637012</v>
+        <v>0.00107878644063685</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="AG24" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83501793410878e-16</v>
+        <v>-1.774878931412836e-16</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.884981308350689e-15</v>
+        <v>2.148281552649678e-14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-1.554892282637499e-13</v>
+        <v>-1.270391248829942e-13</v>
       </c>
       <c r="AK24" t="n">
-        <v>-8.400398432417688e-16</v>
+        <v>-7.784571598445922e-16</v>
       </c>
       <c r="AL24" t="n">
-        <v>6.219577804167375e-13</v>
+        <v>5.081653015142231e-13</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.976196983832779e-14</v>
+        <v>8.570921750106208e-14</v>
       </c>
       <c r="AN24" t="n">
-        <v>-1.83501793410878e-16</v>
+        <v>1.774878931412836e-16</v>
       </c>
       <c r="AO24" t="n">
-        <v>-4.884981308350689e-15</v>
+        <v>-2.148281552649678e-14</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.554892282637499e-13</v>
+        <v>1.270391248829942e-13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.400398432417688e-16</v>
+        <v>7.784571598445922e-16</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.219559372730443e-13</v>
+        <v>5.081478059699478e-13</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.953992523340276e-14</v>
+        <v>8.615330671091215e-14</v>
       </c>
     </row>
     <row r="25">
@@ -7200,112 +7200,112 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.263136022274133e-06</v>
+        <v>-1.263136022280965e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>1.864873098520545e-16</v>
+        <v>1.525337304621532e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.21179609635003e-16</v>
+        <v>-5.789503694433393e-16</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.004231960428281523</v>
+        <v>-0.00423196042827995</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.009998736863977731</v>
+        <v>-0.009998736863977724</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.837675371856052e-16</v>
+        <v>-1.513191775452895e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.211946864550133e-16</v>
+        <v>-5.793042247975463e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.472549643805026e-15</v>
+        <v>-2.219801240530538e-15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.263136022274133e-06</v>
+        <v>1.263136022280965e-06</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.864873098520545e-16</v>
+        <v>-1.525337304621532e-16</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AA25" t="n">
-        <v>6.21179609635003e-16</v>
+        <v>5.789503694433393e-16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.004231960428281523</v>
+        <v>0.00423196042827995</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.450536662689746e-15</v>
+        <v>2.207429876228768e-15</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.009998736863977731</v>
+        <v>0.009998736863977724</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.837675371856052e-16</v>
+        <v>1.513191775452895e-16</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001078786440637012</v>
+        <v>-0.00107878644063685</v>
       </c>
       <c r="AG25" t="n">
-        <v>6.211946864550133e-16</v>
+        <v>5.793042247975463e-16</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.829631977857021e-15</v>
+        <v>2.141473676500339e-14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0.1422723979850524</v>
+        <v>-0.1422723979851855</v>
       </c>
       <c r="AK25" t="n">
-        <v>-7.903516927150042e-16</v>
+        <v>-6.486090920928102e-16</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.5690895919402106</v>
+        <v>0.5690895919407426</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.931016027632206e-14</v>
+        <v>8.54625573384283e-14</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>-4.829631977857021e-15</v>
+        <v>-2.141473676500339e-14</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1422723979850524</v>
+        <v>0.1422723979851855</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.903516927150042e-16</v>
+        <v>6.486090920928102e-16</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.5690895919402106</v>
+        <v>0.5690895919407422</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.932689554653355e-14</v>
+        <v>8.585533678159801e-14</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.427057497211222e-20</v>
+        <v>-5.239060668061288e-21</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.783821871514027e-21</v>
+        <v>-6.54882583507661e-22</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.691063134195298e-15</v>
+        <v>-6.208286891652626e-16</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.567643743028054e-13</v>
+        <v>-1.309765167015322e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="K26" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.579633952279717e-16</v>
+        <v>-9.957666828069171e-17</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="R26" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="V26" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.579633952279717e-16</v>
+        <v>9.957666828069171e-17</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.01113611787349708</v>
+        <v>0.01113611787349452</v>
       </c>
       <c r="AD26" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.577061380387217e-16</v>
+        <v>9.957497490218503e-17</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.691063134224552e-15</v>
+        <v>6.208286892050575e-16</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.509104035652854e-14</v>
+        <v>4.729550084903167e-14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-1.338928967697939e-13</v>
+        <v>-8.408064744864054e-14</v>
       </c>
       <c r="AK26" t="n">
-        <v>-8.92081547521073e-16</v>
+        <v>-4.566659550508945e-16</v>
       </c>
       <c r="AL26" t="n">
-        <v>5.355715870791755e-13</v>
+        <v>3.361255407452572e-13</v>
       </c>
       <c r="AM26" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>1.891820033961267e-13</v>
       </c>
       <c r="AN26" t="n">
-        <v>-1.691063134224552e-15</v>
+        <v>-6.208286892050575e-16</v>
       </c>
       <c r="AO26" t="n">
-        <v>-2.509104035652854e-14</v>
+        <v>-4.729550084903167e-14</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.338928967697939e-13</v>
+        <v>8.408064744864054e-14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.92081547521073e-16</v>
+        <v>4.566659550508945e-16</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.346834086594754e-13</v>
+        <v>3.356314604241669e-13</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.891820033961267e-13</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-2.055647319032516e-13</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-4.336808689942018e-11</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="K27" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="L27" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="S27" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349452</v>
       </c>
       <c r="W27" t="n">
-        <v>3.906442069675949e-15</v>
+        <v>3.284615749884662e-15</v>
       </c>
       <c r="X27" t="n">
         <v>-0.009998568475415982</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.577061380387217e-16</v>
+        <v>-9.957497490218503e-17</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AA27" t="n">
-        <v>-1.010596954321602e-15</v>
+        <v>-8.795874158562031e-16</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AI27" t="n">
-        <v>-2.428299574909421e-14</v>
+        <v>-4.676173038271414e-14</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.02251308472689817</v>
+        <v>-0.02251308472698921</v>
       </c>
       <c r="AK27" t="n">
-        <v>-6.792060231468612e-16</v>
+        <v>-4.275943135957665e-16</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.09005233890759357</v>
+        <v>0.09005233890795705</v>
       </c>
       <c r="AM27" t="n">
-        <v>-9.683249195355488e-14</v>
+        <v>-1.867563777792461e-13</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AO27" t="n">
-        <v>2.428299574909421e-14</v>
+        <v>4.676173038271414e-14</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.02251308472689817</v>
+        <v>0.02251308472698921</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.792060231468612e-16</v>
+        <v>4.275943135957665e-16</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.09005233890759312</v>
+        <v>0.09005233890795727</v>
       </c>
       <c r="AS27" t="n">
-        <v>-9.743147403919787e-14</v>
+        <v>-1.87337465282466e-13</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.659282406385243e-22</v>
+        <v>2.271685965345289e-21</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.082410300798155e-22</v>
+        <v>2.839607456681611e-22</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.026124965156651e-16</v>
+        <v>2.691947868934167e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.164820601596311e-14</v>
+        <v>5.679214913363221e-14</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.94714194959858e-15</v>
+        <v>-3.304815612337873e-15</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="M28" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.001222599374437302</v>
+        <v>-0.001222599374437192</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="S28" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="V28" t="n">
-        <v>3.94714194959858e-15</v>
+        <v>3.304815612337873e-15</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01113611787349708</v>
+        <v>-0.01113611787349453</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.431524584008318e-06</v>
+        <v>-1.431524584014678e-06</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.001222599374437302</v>
+        <v>0.001222599374437192</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.604804673994475e-16</v>
+        <v>1.007394783138497e-16</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.011136577822181e-15</v>
+        <v>-8.801109181113563e-16</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.947141083670339e-15</v>
+        <v>3.304817884023839e-15</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.001222599374437721</v>
+        <v>0.001222599374437407</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.026124964512247e-16</v>
+        <v>-2.691947868883633e-16</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.509104035652854e-14</v>
+        <v>4.662936703425657e-14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-1.339430682253256e-13</v>
+        <v>-8.392083454423743e-14</v>
       </c>
       <c r="AK28" t="n">
-        <v>-8.946836327350383e-16</v>
+        <v>-4.597017211338539e-16</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.357769349706443e-13</v>
+        <v>3.356551736916173e-13</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.865174681370263e-13</v>
       </c>
       <c r="AN28" t="n">
-        <v>-1.026124964512247e-16</v>
+        <v>2.691947868883633e-16</v>
       </c>
       <c r="AO28" t="n">
-        <v>-2.509104035652854e-14</v>
+        <v>-4.662936703425657e-14</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.339430682253256e-13</v>
+        <v>8.392083454423743e-14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.946836327350383e-16</v>
+        <v>4.597017211338539e-16</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.357675024117436e-13</v>
+        <v>3.357113942420649e-13</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.003641614261142e-13</v>
+        <v>1.865174681370263e-13</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>4.336808689942018e-11</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.431524584004987e-06</v>
+        <v>-1.43152458401435e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>1.60471871097023e-16</v>
+        <v>1.007901242459449e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.010538406899292e-15</v>
+        <v>-8.800237745202832e-16</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.01113611787350541</v>
+        <v>-0.01113611787350202</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.009998568475416005</v>
+        <v>-0.009998568475415992</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.579633952279717e-16</v>
+        <v>-9.957666828069171e-17</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.011845584444849e-15</v>
+        <v>-8.802264234440092e-16</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="W29" t="n">
-        <v>-3.947141083670339e-15</v>
+        <v>-3.304817884023839e-15</v>
       </c>
       <c r="X29" t="n">
-        <v>1.431524584004987e-06</v>
+        <v>1.43152458401435e-06</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.60471871097023e-16</v>
+        <v>-1.007901242459449e-16</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.001222599374437721</v>
+        <v>-0.001222599374437407</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.010538406899292e-15</v>
+        <v>8.800237745202832e-16</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01113611787350541</v>
+        <v>0.01113611787350202</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.906456340250922e-15</v>
+        <v>3.28462098894533e-15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009998568475416005</v>
+        <v>0.009998568475415992</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.579633952279717e-16</v>
+        <v>9.957666828069171e-17</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.00122259937443772</v>
+        <v>-0.001222599374437406</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.011845584444849e-15</v>
+        <v>8.802264234440092e-16</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.455235447019222e-14</v>
+        <v>4.699066218428263e-14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.02251308472655245</v>
+        <v>-0.02251308472681168</v>
       </c>
       <c r="AK29" t="n">
-        <v>-6.79736818501431e-16</v>
+        <v>-4.277060378933975e-16</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.09005233890620934</v>
+        <v>0.09005233890724629</v>
       </c>
       <c r="AM29" t="n">
-        <v>9.748393434298417e-14</v>
+        <v>1.878501785844625e-13</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AO29" t="n">
-        <v>-2.455235447019222e-14</v>
+        <v>-4.699066218428263e-14</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.02251308472655245</v>
+        <v>0.02251308472681168</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.79736818501431e-16</v>
+        <v>4.277060378933975e-16</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.09005233890621112</v>
+        <v>0.09005233890724762</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.893490141855262e-14</v>
+        <v>1.880751188897983e-13</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>5.558909158194926e-21</v>
+        <v>1.521452776224584e-21</v>
       </c>
       <c r="G30" t="n">
-        <v>6.948636447743658e-22</v>
+        <v>1.90181597028073e-22</v>
       </c>
       <c r="H30" t="n">
-        <v>6.587307352460988e-16</v>
+        <v>1.802921539826132e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>1.389727289548732e-13</v>
+        <v>3.80363194056146e-14</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.01853807587191545</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="K30" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="M30" t="n">
-        <v>-8.702157183110913e-17</v>
+        <v>-4.180501003454598e-17</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.01853807587190386</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="S30" t="n">
-        <v>-8.72061823187002e-17</v>
+        <v>-4.187830652248113e-17</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="V30" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01853807587191545</v>
+        <v>0.01853807587190909</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.702157183110913e-17</v>
+        <v>4.180501003454598e-17</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.01853807587190386</v>
+        <v>0.01853807587190073</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.72061823187002e-17</v>
+        <v>4.187830652248113e-17</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="AH30" t="n">
-        <v>-6.587307352355628e-16</v>
+        <v>-1.802921540148587e-16</v>
       </c>
       <c r="AI30" t="n">
-        <v>8.149037000748649e-14</v>
+        <v>3.308464613382966e-14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-7.549516567451064e-14</v>
+        <v>-3.586154729876037e-14</v>
       </c>
       <c r="AK30" t="n">
-        <v>-6.149594722337781e-16</v>
+        <v>-1.071191746415678e-16</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.019806626980426e-13</v>
+        <v>1.432963679872677e-13</v>
       </c>
       <c r="AM30" t="n">
-        <v>3.268496584496461e-13</v>
+        <v>1.323385845353187e-13</v>
       </c>
       <c r="AN30" t="n">
-        <v>6.587307352355628e-16</v>
+        <v>1.802921540148587e-16</v>
       </c>
       <c r="AO30" t="n">
-        <v>-8.149037000748649e-14</v>
+        <v>-3.308464613382966e-14</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.549516567451064e-14</v>
+        <v>3.586154729876037e-14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.149594722337781e-16</v>
+        <v>1.071191746415678e-16</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.019806626980426e-13</v>
+        <v>1.435960104028153e-13</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.25961480029946e-13</v>
+        <v>1.314504061156185e-13</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4.111294638065033e-13</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>8.673617379884035e-11</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.01853807587190386</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="K31" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="M31" t="n">
-        <v>-8.72061823187002e-17</v>
+        <v>-4.187830652248113e-17</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="Q31" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="S31" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.01853807587190386</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="W31" t="n">
-        <v>4.979654261027446e-15</v>
+        <v>3.845065573465923e-15</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.009998542574732264</v>
+        <v>-0.009998542574732268</v>
       </c>
       <c r="Y31" t="n">
-        <v>-8.72061823187002e-17</v>
+        <v>-4.187830652248113e-17</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.001244719958365409</v>
+        <v>-0.001244719958365369</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.35150778648002e-15</v>
+        <v>-1.005467541231768e-15</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="AD31" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="AE31" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="AH31" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-8.302864127521905e-14</v>
+        <v>-3.363850098582328e-14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.004092308026951263</v>
+        <v>-0.004092308026984459</v>
       </c>
       <c r="AK31" t="n">
-        <v>-3.781516349833479e-16</v>
+        <v>-1.812412399583363e-16</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.01636923210780461</v>
+        <v>0.01636923210793761</v>
       </c>
       <c r="AM31" t="n">
-        <v>-3.321614858409899e-13</v>
+        <v>-1.351703120018463e-13</v>
       </c>
       <c r="AN31" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>8.302864127521905e-14</v>
+        <v>3.363850098582328e-14</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.004092308026951263</v>
+        <v>0.004092308026984459</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.781516349833479e-16</v>
+        <v>1.812412399583363e-16</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.01636923210780616</v>
+        <v>0.01636923210793872</v>
       </c>
       <c r="AS31" t="n">
-        <v>-3.320676443607612e-13</v>
+        <v>-1.339376958847387e-13</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.37221141352895e-21</v>
+        <v>-5.267053248582775e-21</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.715264266911187e-22</v>
+        <v>-6.583816560728468e-22</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.626070525031805e-16</v>
+        <v>-6.241458099570588e-16</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.430528533822374e-14</v>
+        <v>-1.316763312145694e-13</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.034197034245217e-15</v>
+        <v>-3.870980034180524e-15</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="M32" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.001244719958365408</v>
+        <v>-0.001244719958365368</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="S32" t="n">
-        <v>8.998391004434036e-17</v>
+        <v>4.277158646686195e-17</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="U32" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="V32" t="n">
-        <v>5.034197034245217e-15</v>
+        <v>3.870980034180524e-15</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.01853807587190385</v>
+        <v>-0.01853807587190073</v>
       </c>
       <c r="X32" t="n">
-        <v>-1.457425267722723e-06</v>
+        <v>-1.457425267729539e-06</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001244719958365408</v>
+        <v>0.001244719958365368</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.994593497079611e-17</v>
+        <v>4.302749958412686e-17</v>
       </c>
       <c r="AA32" t="n">
-        <v>-1.35142324460594e-15</v>
+        <v>-1.004357076261401e-15</v>
       </c>
       <c r="AB32" t="n">
-        <v>5.034195662033804e-15</v>
+        <v>3.870974767127275e-15</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="AD32" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001244719958365699</v>
+        <v>0.001244719958365419</v>
       </c>
       <c r="AF32" t="n">
-        <v>8.998391004434036e-17</v>
+        <v>4.277158646686195e-17</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62607052525906e-16</v>
+        <v>6.241458099166313e-16</v>
       </c>
       <c r="AI32" t="n">
-        <v>8.304468224196171e-14</v>
+        <v>3.352873534367973e-14</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-7.529960270764857e-14</v>
+        <v>-3.572678161051504e-14</v>
       </c>
       <c r="AK32" t="n">
-        <v>-6.205973235307027e-16</v>
+        <v>-1.101549407245273e-16</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.011773773084481e-13</v>
+        <v>1.430490993232485e-13</v>
       </c>
       <c r="AM32" t="n">
-        <v>3.312905505481467e-13</v>
+        <v>1.341149413747189e-13</v>
       </c>
       <c r="AN32" t="n">
-        <v>-1.62607052525906e-16</v>
+        <v>-6.241458099166313e-16</v>
       </c>
       <c r="AO32" t="n">
-        <v>-8.304468224196171e-14</v>
+        <v>-3.352873534367973e-14</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.529960270764857e-14</v>
+        <v>3.572678161051504e-14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.205973235307027e-16</v>
+        <v>1.101549407245273e-16</v>
       </c>
       <c r="AR32" t="n">
-        <v>3.012195527729578e-13</v>
+        <v>1.427650451406545e-13</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.321787289678468e-13</v>
+        <v>1.341149413747189e-13</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.040834085586084e-17</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.301042606982605e-18</v>
+        <v>-4.336808689942018e-19</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.23338839141951e-12</v>
+        <v>-4.111294638065033e-13</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.602085213965211e-10</v>
+        <v>-8.673617379884035e-11</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.01853807587191546</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.457425267718843e-06</v>
+        <v>-1.457425267729414e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>8.998391004434036e-17</v>
+        <v>4.277158646686195e-17</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.351124469597434e-15</v>
+        <v>-1.004678364397376e-15</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.01853807587191545</v>
+        <v>-0.01853807587190909</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.009998542574732292</v>
+        <v>-0.009998542574732278</v>
       </c>
       <c r="S33" t="n">
-        <v>-8.702157183110913e-17</v>
+        <v>-4.180501003454598e-17</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.351217823243913e-15</v>
+        <v>-1.003618666593276e-15</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01853807587191546</v>
+        <v>0.01853807587190909</v>
       </c>
       <c r="W33" t="n">
-        <v>-5.034195662033804e-15</v>
+        <v>-3.870974767127275e-15</v>
       </c>
       <c r="X33" t="n">
-        <v>1.457425267718843e-06</v>
+        <v>1.457425267729414e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>-8.998391004434036e-17</v>
+        <v>-4.277158646686195e-17</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.001244719958365699</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.351124469597434e-15</v>
+        <v>1.004678364397376e-15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.01853807587191545</v>
+        <v>0.01853807587190909</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.979648702118288e-15</v>
+        <v>3.845064052013146e-15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.009998542574732292</v>
+        <v>0.009998542574732278</v>
       </c>
       <c r="AE33" t="n">
-        <v>8.702157183110913e-17</v>
+        <v>4.180501003454598e-17</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001244719958365697</v>
+        <v>-0.001244719958365419</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.351217823243913e-15</v>
+        <v>1.003618666593276e-15</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AI33" t="n">
-        <v>8.278430025063367e-14</v>
+        <v>3.300334953305864e-14</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.004092308026713454</v>
+        <v>-0.004092308026943159</v>
       </c>
       <c r="AK33" t="n">
-        <v>-3.778386247725941e-16</v>
+        <v>-1.805385040703131e-16</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.01636923210685359</v>
+        <v>0.0163692321077733</v>
       </c>
       <c r="AM33" t="n">
-        <v>3.310853897287379e-13</v>
+        <v>1.326015304135093e-13</v>
       </c>
       <c r="AN33" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AO33" t="n">
-        <v>-8.278430025063367e-14</v>
+        <v>-3.300334953305864e-14</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.004092308026713454</v>
+        <v>0.004092308026943159</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.778386247725941e-16</v>
+        <v>1.805385040703131e-16</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.01636923210685604</v>
+        <v>0.01636923210777352</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.311890122763301e-13</v>
+        <v>1.314252658509586e-13</v>
       </c>
     </row>
   </sheetData>
